--- a/test-artifacts/comparison/menuHtmlsComparison.xlsx
+++ b/test-artifacts/comparison/menuHtmlsComparison.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:E514"/>
+  <dimension ref="A1:E359"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -557,16 +557,16 @@
         <v>diversity-equity</v>
       </c>
       <c r="B10" t="str">
-        <v>CHILD_HREF</v>
+        <v>CHILD_TITLE</v>
       </c>
       <c r="C10" t="str">
-        <v>/diversity-equity/Diversity-Equity-Policies</v>
+        <v>Pregnant and Parenting Students' Accommodations</v>
       </c>
       <c r="D10" t="str">
-        <v>/diversity-equity/diversity-equity-policies</v>
+        <v/>
       </c>
       <c r="E10" t="str">
-        <v>❗ HREF Mismatch</v>
+        <v>Missing in WP</v>
       </c>
     </row>
     <row r="11">
@@ -577,13 +577,13 @@
         <v>CHILD_HREF</v>
       </c>
       <c r="C11" t="str">
-        <v>/ReasonableAccommodation</v>
+        <v>/titleix/pregnant-and-parenting-students-accommodations</v>
       </c>
       <c r="D11" t="str">
-        <v>/reasonableaccommodation</v>
+        <v/>
       </c>
       <c r="E11" t="str">
-        <v>❗ HREF Mismatch</v>
+        <v>Missing in WP</v>
       </c>
     </row>
     <row r="12">
@@ -741,33 +741,33 @@
     </row>
     <row r="21">
       <c r="A21" t="str">
-        <v>group-360-menu</v>
+        <v>group-361-menu</v>
       </c>
       <c r="B21" t="str">
-        <v>ITEM_HREF</v>
+        <v>MENU</v>
       </c>
       <c r="C21" t="str">
-        <v>https://cil.geneseo.sunycreate.cloud</v>
+        <v>Presidential Search menu                    [Menu ID: group-361-menu]</v>
       </c>
       <c r="D21" t="str">
-        <v/>
+        <v>group-361-menu                    [Term ID: 1765]</v>
       </c>
       <c r="E21" t="str">
-        <v>❗ HREF Mismatch</v>
+        <v>OK</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="str">
-        <v>group-361-menu</v>
+        <v>group-362-menu</v>
       </c>
       <c r="B22" t="str">
         <v>MENU</v>
       </c>
       <c r="C22" t="str">
-        <v>Presidential Search menu                    [Menu ID: group-361-menu]</v>
+        <v>Kappa Delta Pi menu                    [Menu ID: group-362-menu]</v>
       </c>
       <c r="D22" t="str">
-        <v>group-361-menu                    [Term ID: 1765]</v>
+        <v>group-362-menu                    [Term ID: 1752]</v>
       </c>
       <c r="E22" t="str">
         <v>OK</v>
@@ -775,16 +775,16 @@
     </row>
     <row r="23">
       <c r="A23" t="str">
-        <v>group-362-menu</v>
+        <v>group-451-menu</v>
       </c>
       <c r="B23" t="str">
         <v>MENU</v>
       </c>
       <c r="C23" t="str">
-        <v>Kappa Delta Pi menu                    [Menu ID: group-362-menu]</v>
+        <v>Department of Anthropology                    [Menu ID: group-451-menu]</v>
       </c>
       <c r="D23" t="str">
-        <v>group-362-menu                    [Term ID: 1752]</v>
+        <v>group-451-menu                    [Term ID: 1584]</v>
       </c>
       <c r="E23" t="str">
         <v>OK</v>
@@ -792,16 +792,16 @@
     </row>
     <row r="24">
       <c r="A24" t="str">
-        <v>group-451-menu</v>
+        <v>group-455-menu</v>
       </c>
       <c r="B24" t="str">
         <v>MENU</v>
       </c>
       <c r="C24" t="str">
-        <v>Department of Anthropology                    [Menu ID: group-451-menu]</v>
+        <v>Knot Mosaics                    [Menu ID: group-455-menu]</v>
       </c>
       <c r="D24" t="str">
-        <v>group-451-menu                    [Term ID: 1584]</v>
+        <v>group-455-menu                    [Term ID: 1565]</v>
       </c>
       <c r="E24" t="str">
         <v>OK</v>
@@ -809,67 +809,67 @@
     </row>
     <row r="25">
       <c r="A25" t="str">
-        <v>group-455-menu</v>
+        <v>group-456-menu</v>
       </c>
       <c r="B25" t="str">
         <v>MENU</v>
       </c>
       <c r="C25" t="str">
-        <v>Knot Mosaics                    [Menu ID: group-455-menu]</v>
+        <v>Strategic Initiatives                    [Menu ID: group-456-menu]</v>
       </c>
       <c r="D25" t="str">
-        <v>group-455-menu                    [Term ID: 1565]</v>
+        <v/>
       </c>
       <c r="E25" t="str">
-        <v>OK</v>
+        <v>Missing in WP</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="str">
-        <v>group-455-menu</v>
+        <v>group-460-menu</v>
       </c>
       <c r="B26" t="str">
-        <v>ITEM_HREF</v>
+        <v>MENU</v>
       </c>
       <c r="C26" t="str">
-        <v>https://knotmosaics.azurewebsites.net</v>
+        <v>Wellbeing Initiatives                    [Menu ID: group-460-menu]</v>
       </c>
       <c r="D26" t="str">
-        <v/>
+        <v>group-460-menu                    [Term ID: 1753]</v>
       </c>
       <c r="E26" t="str">
-        <v>❗ HREF Mismatch</v>
+        <v>OK</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="str">
-        <v>group-456-menu</v>
+        <v>group-463-menu</v>
       </c>
       <c r="B27" t="str">
         <v>MENU</v>
       </c>
       <c r="C27" t="str">
-        <v>Strategic Initiatives                    [Menu ID: group-456-menu]</v>
+        <v>Performance As Social Change menu                    [Menu ID: group-463-menu]</v>
       </c>
       <c r="D27" t="str">
-        <v/>
+        <v>group-463-menu                    [Term ID: 1754]</v>
       </c>
       <c r="E27" t="str">
-        <v>Missing in WP</v>
+        <v>OK</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="str">
-        <v>group-460-menu</v>
+        <v>group-464-menu</v>
       </c>
       <c r="B28" t="str">
         <v>MENU</v>
       </c>
       <c r="C28" t="str">
-        <v>Wellbeing Initiatives                    [Menu ID: group-460-menu]</v>
+        <v>Microcredentials menu                    [Menu ID: group-464-menu]</v>
       </c>
       <c r="D28" t="str">
-        <v>group-460-menu                    [Term ID: 1753]</v>
+        <v>group-464-menu                    [Term ID: 1756]</v>
       </c>
       <c r="E28" t="str">
         <v>OK</v>
@@ -877,16 +877,16 @@
     </row>
     <row r="29">
       <c r="A29" t="str">
-        <v>group-463-menu</v>
+        <v>group-465-menu</v>
       </c>
       <c r="B29" t="str">
         <v>MENU</v>
       </c>
       <c r="C29" t="str">
-        <v>Performance As Social Change menu                    [Menu ID: group-463-menu]</v>
+        <v>Human Cognition and Memory Lab menu                    [Menu ID: group-465-menu]</v>
       </c>
       <c r="D29" t="str">
-        <v>group-463-menu                    [Term ID: 1754]</v>
+        <v>group-465-menu                    [Term ID: 1755]</v>
       </c>
       <c r="E29" t="str">
         <v>OK</v>
@@ -894,33 +894,33 @@
     </row>
     <row r="30">
       <c r="A30" t="str">
-        <v>group-464-menu</v>
+        <v>group-466-menu</v>
       </c>
       <c r="B30" t="str">
         <v>MENU</v>
       </c>
       <c r="C30" t="str">
-        <v>Microcredentials menu                    [Menu ID: group-464-menu]</v>
+        <v>WRTG 105 Writing Seminar Resources menu                    [Menu ID: group-466-menu]</v>
       </c>
       <c r="D30" t="str">
-        <v>group-464-menu                    [Term ID: 1756]</v>
+        <v/>
       </c>
       <c r="E30" t="str">
-        <v>OK</v>
+        <v>Missing in WP</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="str">
-        <v>group-465-menu</v>
+        <v>group-467-menu</v>
       </c>
       <c r="B31" t="str">
         <v>MENU</v>
       </c>
       <c r="C31" t="str">
-        <v>Human Cognition and Memory Lab menu                    [Menu ID: group-465-menu]</v>
+        <v>Construction Projects menu                    [Menu ID: group-467-menu]</v>
       </c>
       <c r="D31" t="str">
-        <v>group-465-menu                    [Term ID: 1755]</v>
+        <v>group-467-menu                    [Term ID: 1757]</v>
       </c>
       <c r="E31" t="str">
         <v>OK</v>
@@ -928,33 +928,33 @@
     </row>
     <row r="32">
       <c r="A32" t="str">
-        <v>group-466-menu</v>
+        <v>group-470-menu</v>
       </c>
       <c r="B32" t="str">
         <v>MENU</v>
       </c>
       <c r="C32" t="str">
-        <v>WRTG 105 Writing Seminar Resources menu                    [Menu ID: group-466-menu]</v>
+        <v>School of Arts and Sciences menu                    [Menu ID: group-470-menu]</v>
       </c>
       <c r="D32" t="str">
-        <v/>
+        <v>group-470-menu                    [Term ID: 1759]</v>
       </c>
       <c r="E32" t="str">
-        <v>Missing in WP</v>
+        <v>OK</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="str">
-        <v>group-467-menu</v>
+        <v>group-471-menu</v>
       </c>
       <c r="B33" t="str">
         <v>MENU</v>
       </c>
       <c r="C33" t="str">
-        <v>Construction Projects menu                    [Menu ID: group-467-menu]</v>
+        <v>Army ROTC menu                    [Menu ID: group-471-menu]</v>
       </c>
       <c r="D33" t="str">
-        <v>group-467-menu                    [Term ID: 1757]</v>
+        <v>group-471-menu                    [Term ID: 1545]</v>
       </c>
       <c r="E33" t="str">
         <v>OK</v>
@@ -962,16 +962,16 @@
     </row>
     <row r="34">
       <c r="A34" t="str">
-        <v>group-470-menu</v>
+        <v>group-472-menu</v>
       </c>
       <c r="B34" t="str">
         <v>MENU</v>
       </c>
       <c r="C34" t="str">
-        <v>School of Arts and Sciences menu                    [Menu ID: group-470-menu]</v>
+        <v>Philosophy, Politics, and Economics menu                    [Menu ID: group-472-menu]</v>
       </c>
       <c r="D34" t="str">
-        <v>group-470-menu                    [Term ID: 1759]</v>
+        <v>group-472-menu                    [Term ID: 1760]</v>
       </c>
       <c r="E34" t="str">
         <v>OK</v>
@@ -979,33 +979,33 @@
     </row>
     <row r="35">
       <c r="A35" t="str">
-        <v>group-471-menu</v>
+        <v>group-473-menu</v>
       </c>
       <c r="B35" t="str">
         <v>MENU</v>
       </c>
       <c r="C35" t="str">
-        <v>Army ROTC menu                    [Menu ID: group-471-menu]</v>
+        <v>Geneseo CARE(S) menu                    [Menu ID: group-473-menu]</v>
       </c>
       <c r="D35" t="str">
-        <v>group-471-menu                    [Term ID: 1545]</v>
+        <v/>
       </c>
       <c r="E35" t="str">
-        <v>OK</v>
+        <v>Missing in WP</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="str">
-        <v>group-472-menu</v>
+        <v>group-474-menu</v>
       </c>
       <c r="B36" t="str">
         <v>MENU</v>
       </c>
       <c r="C36" t="str">
-        <v>Philosophy, Politics, and Economics menu                    [Menu ID: group-472-menu]</v>
+        <v>COPLAC 2025 menu                    [Menu ID: group-474-menu]</v>
       </c>
       <c r="D36" t="str">
-        <v>group-472-menu                    [Term ID: 1760]</v>
+        <v>group-474-menu                    [Term ID: 1763]</v>
       </c>
       <c r="E36" t="str">
         <v>OK</v>
@@ -1013,33 +1013,33 @@
     </row>
     <row r="37">
       <c r="A37" t="str">
-        <v>group-473-menu</v>
+        <v>group-475-menu</v>
       </c>
       <c r="B37" t="str">
         <v>MENU</v>
       </c>
       <c r="C37" t="str">
-        <v>Geneseo CARE(S) menu                    [Menu ID: group-473-menu]</v>
+        <v>Writing Program menu                    [Menu ID: group-475-menu]</v>
       </c>
       <c r="D37" t="str">
-        <v/>
+        <v>group-475-menu                    [Term ID: 1573]</v>
       </c>
       <c r="E37" t="str">
-        <v>Missing in WP</v>
+        <v>OK</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="str">
-        <v>group-474-menu</v>
+        <v>group-476-menu</v>
       </c>
       <c r="B38" t="str">
         <v>MENU</v>
       </c>
       <c r="C38" t="str">
-        <v>COPLAC 2025 menu                    [Menu ID: group-474-menu]</v>
+        <v>Club Sports Association menu                    [Menu ID: group-476-menu]</v>
       </c>
       <c r="D38" t="str">
-        <v>group-474-menu                    [Term ID: 1763]</v>
+        <v>group-476-menu                    [Term ID: 1762]</v>
       </c>
       <c r="E38" t="str">
         <v>OK</v>
@@ -1047,16 +1047,16 @@
     </row>
     <row r="39">
       <c r="A39" t="str">
-        <v>group-475-menu</v>
+        <v>group-477-menu</v>
       </c>
       <c r="B39" t="str">
         <v>MENU</v>
       </c>
       <c r="C39" t="str">
-        <v>Writing Program menu                    [Menu ID: group-475-menu]</v>
+        <v>Office of Government and Community Relations menu                    [Menu ID: group-477-menu]</v>
       </c>
       <c r="D39" t="str">
-        <v>group-475-menu                    [Term ID: 1573]</v>
+        <v>group-477-menu                    [Term ID: 1764]</v>
       </c>
       <c r="E39" t="str">
         <v>OK</v>
@@ -1064,16 +1064,16 @@
     </row>
     <row r="40">
       <c r="A40" t="str">
-        <v>group-476-menu</v>
+        <v>group-478-menu</v>
       </c>
       <c r="B40" t="str">
         <v>MENU</v>
       </c>
       <c r="C40" t="str">
-        <v>Club Sports Association menu                    [Menu ID: group-476-menu]</v>
+        <v>CSTEP                    [Menu ID: group-478-menu]</v>
       </c>
       <c r="D40" t="str">
-        <v>group-476-menu                    [Term ID: 1762]</v>
+        <v>group-478-menu                    [Term ID: 1766]</v>
       </c>
       <c r="E40" t="str">
         <v>OK</v>
@@ -1081,16 +1081,16 @@
     </row>
     <row r="41">
       <c r="A41" t="str">
-        <v>group-477-menu</v>
+        <v>group-480-menu</v>
       </c>
       <c r="B41" t="str">
         <v>MENU</v>
       </c>
       <c r="C41" t="str">
-        <v>Office of Government and Community Relations menu                    [Menu ID: group-477-menu]</v>
+        <v>AI At Geneseo menu                    [Menu ID: group-480-menu]</v>
       </c>
       <c r="D41" t="str">
-        <v>group-477-menu                    [Term ID: 1764]</v>
+        <v>group-480-menu                    [Term ID: 1767]</v>
       </c>
       <c r="E41" t="str">
         <v>OK</v>
@@ -1098,16 +1098,16 @@
     </row>
     <row r="42">
       <c r="A42" t="str">
-        <v>group-478-menu</v>
+        <v>group-481-menu</v>
       </c>
       <c r="B42" t="str">
         <v>MENU</v>
       </c>
       <c r="C42" t="str">
-        <v>CSTEP                    [Menu ID: group-478-menu]</v>
+        <v>Department for the Performing Arts menu                    [Menu ID: group-481-menu]</v>
       </c>
       <c r="D42" t="str">
-        <v>group-478-menu                    [Term ID: 1766]</v>
+        <v>group-481-menu                    [Term ID: 1537]</v>
       </c>
       <c r="E42" t="str">
         <v>OK</v>
@@ -1115,16 +1115,16 @@
     </row>
     <row r="43">
       <c r="A43" t="str">
-        <v>group-480-menu</v>
+        <v>group-482-menu</v>
       </c>
       <c r="B43" t="str">
         <v>MENU</v>
       </c>
       <c r="C43" t="str">
-        <v>AI At Geneseo menu                    [Menu ID: group-480-menu]</v>
+        <v>TRIO SSS menu                    [Menu ID: group-482-menu]</v>
       </c>
       <c r="D43" t="str">
-        <v>group-480-menu                    [Term ID: 1767]</v>
+        <v>group-482-menu                    [Term ID: 1768]</v>
       </c>
       <c r="E43" t="str">
         <v>OK</v>
@@ -1132,16 +1132,16 @@
     </row>
     <row r="44">
       <c r="A44" t="str">
-        <v>group-481-menu</v>
+        <v>group-menu-aaron-j-steinhauer</v>
       </c>
       <c r="B44" t="str">
         <v>MENU</v>
       </c>
       <c r="C44" t="str">
-        <v>Department for the Performing Arts menu                    [Menu ID: group-481-menu]</v>
+        <v>Aaron J Steinhauer                    [Menu ID: group-menu-aaron-j-steinhauer]</v>
       </c>
       <c r="D44" t="str">
-        <v>group-481-menu                    [Term ID: 1537]</v>
+        <v>group-menu-aaron-j-steinhauer                    [Term ID: 1684]</v>
       </c>
       <c r="E44" t="str">
         <v>OK</v>
@@ -1149,186 +1149,186 @@
     </row>
     <row r="45">
       <c r="A45" t="str">
-        <v>group-481-menu</v>
+        <v>group-menu-about</v>
       </c>
       <c r="B45" t="str">
-        <v>CHILD_HREF</v>
+        <v>MENU</v>
       </c>
       <c r="C45" t="str">
-        <v>/Dance</v>
+        <v>About Geneseo                    [Menu ID: group-menu-about]</v>
       </c>
       <c r="D45" t="str">
-        <v>/dance</v>
+        <v>group-menu-about                    [Term ID: 1586]</v>
       </c>
       <c r="E45" t="str">
-        <v>❗ HREF Mismatch</v>
+        <v>OK</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="str">
-        <v>group-481-menu</v>
+        <v>group-menu-academic-affairs-comm</v>
       </c>
       <c r="B46" t="str">
-        <v>SUBCHILD_HREF</v>
+        <v>MENU</v>
       </c>
       <c r="C46" t="str">
-        <v>/Dance/Academic_programs</v>
+        <v>Academic Affairs Committee                    [Menu ID: group-menu-academic-affairs-comm]</v>
       </c>
       <c r="D46" t="str">
-        <v>/dance/academic_programs</v>
+        <v>group-menu-academic-affairs-comm                    [Term ID: 1722]</v>
       </c>
       <c r="E46" t="str">
-        <v>❗ HREF Mismatch</v>
+        <v>OK</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="str">
-        <v>group-481-menu</v>
+        <v>group-menu-academics</v>
       </c>
       <c r="B47" t="str">
-        <v>SUBCHILD_HREF</v>
+        <v>MENU</v>
       </c>
       <c r="C47" t="str">
-        <v>/Dance/Audition_information</v>
+        <v>Academics                    [Menu ID: group-menu-academics]</v>
       </c>
       <c r="D47" t="str">
-        <v>/dance/audition_information</v>
+        <v>group-menu-academics                    [Term ID: 1706]</v>
       </c>
       <c r="E47" t="str">
-        <v>❗ HREF Mismatch</v>
+        <v>OK</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="str">
-        <v>group-481-menu</v>
+        <v>group-menu-accounting</v>
       </c>
       <c r="B48" t="str">
-        <v>SUBCHILD_HREF</v>
+        <v>MENU</v>
       </c>
       <c r="C48" t="str">
-        <v>/Dance/Course_registration</v>
+        <v>College Accounting of Department                    [Menu ID: group-menu-accounting]</v>
       </c>
       <c r="D48" t="str">
-        <v>/dance/course_registration</v>
+        <v>group-menu-accounting                    [Term ID: 1669]</v>
       </c>
       <c r="E48" t="str">
-        <v>❗ HREF Mismatch</v>
+        <v>OK</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="str">
-        <v>group-481-menu</v>
+        <v>group-menu-accounting-society</v>
       </c>
       <c r="B49" t="str">
-        <v>SUBCHILD_HREF</v>
+        <v>MENU</v>
       </c>
       <c r="C49" t="str">
-        <v>/Dance/history</v>
+        <v>Accounting Society                    [Menu ID: group-menu-accounting-society]</v>
       </c>
       <c r="D49" t="str">
-        <v>/dance/history</v>
+        <v>group-menu-accounting-society                    [Term ID: 1604]</v>
       </c>
       <c r="E49" t="str">
-        <v>❗ HREF Mismatch</v>
+        <v>OK</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="str">
-        <v>group-481-menu</v>
+        <v>group-menu-actuarial-science-clu</v>
       </c>
       <c r="B50" t="str">
-        <v>SUBCHILD_HREF</v>
+        <v>MENU</v>
       </c>
       <c r="C50" t="str">
-        <v>/performingarts/student-organizations-dance</v>
+        <v>Actuarial Science Club                    [Menu ID: group-menu-actuarial-science-clu]</v>
       </c>
       <c r="D50" t="str">
-        <v>/?page_id=46883</v>
+        <v>group-menu-actuarial-science-clu                    [Term ID: 1653]</v>
       </c>
       <c r="E50" t="str">
-        <v>❗ HREF Mismatch</v>
+        <v>OK</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="str">
-        <v>group-481-menu</v>
+        <v>group-menu-administration-financ</v>
       </c>
       <c r="B51" t="str">
-        <v>SUBCHILD_HREF</v>
+        <v>MENU</v>
       </c>
       <c r="C51" t="str">
-        <v>/musicBA</v>
+        <v>Finance &amp; Administration                    [Menu ID: group-menu-administration-financ]</v>
       </c>
       <c r="D51" t="str">
-        <v>/musicba</v>
+        <v>group-menu-administration-financ                    [Term ID: 1713]</v>
       </c>
       <c r="E51" t="str">
-        <v>❗ HREF Mismatch</v>
+        <v>OK</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="str">
-        <v>group-481-menu</v>
+        <v>group-menu-administrative-system</v>
       </c>
       <c r="B52" t="str">
-        <v>SUBCHILD_HREF</v>
+        <v>MENU</v>
       </c>
       <c r="C52" t="str">
-        <v>/DPA_musiclessonsandensembles</v>
+        <v>Administrative Systems                    [Menu ID: group-menu-administrative-system]</v>
       </c>
       <c r="D52" t="str">
-        <v>/dpa_musiclessonsandensembles</v>
+        <v/>
       </c>
       <c r="E52" t="str">
-        <v>❗ HREF Mismatch</v>
+        <v>Missing in WP</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="str">
-        <v>group-481-menu</v>
+        <v>group-menu-affirmative-action</v>
       </c>
       <c r="B53" t="str">
-        <v>SUBCHILD_HREF</v>
+        <v>MENU</v>
       </c>
       <c r="C53" t="str">
-        <v>/performingarts/student-organizations-theatre</v>
+        <v>Diversity and Equity                    [Menu ID: group-menu-affirmative-action]</v>
       </c>
       <c r="D53" t="str">
-        <v>/?page_id=46884</v>
+        <v/>
       </c>
       <c r="E53" t="str">
-        <v>❗ HREF Mismatch</v>
+        <v>Missing in WP</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="str">
-        <v>group-481-menu</v>
+        <v>group-menu-alpha-chi-rho</v>
       </c>
       <c r="B54" t="str">
-        <v>ITEM_HREF</v>
+        <v>MENU</v>
       </c>
       <c r="C54" t="str">
-        <v>/performingarts/alumni</v>
+        <v>Alpha Chi Rho                    [Menu ID: group-menu-alpha-chi-rho]</v>
       </c>
       <c r="D54" t="str">
-        <v>/?page_id=46882</v>
+        <v>group-menu-alpha-chi-rho                    [Term ID: 1734]</v>
       </c>
       <c r="E54" t="str">
-        <v>❗ HREF Mismatch</v>
+        <v>OK</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="str">
-        <v>group-482-menu</v>
+        <v>group-menu-alpha-kappa-psi</v>
       </c>
       <c r="B55" t="str">
         <v>MENU</v>
       </c>
       <c r="C55" t="str">
-        <v>TRIO SSS menu                    [Menu ID: group-482-menu]</v>
+        <v>Alpha Kappa Psi - Psi Omicron                    [Menu ID: group-menu-alpha-kappa-psi]</v>
       </c>
       <c r="D55" t="str">
-        <v>group-482-menu                    [Term ID: 1768]</v>
+        <v>group-menu-alpha-kappa-psi                    [Term ID: 1600]</v>
       </c>
       <c r="E55" t="str">
         <v>OK</v>
@@ -1336,33 +1336,33 @@
     </row>
     <row r="56">
       <c r="A56" t="str">
-        <v>group-482-menu</v>
+        <v>group-menu-alpha-phi-omega</v>
       </c>
       <c r="B56" t="str">
-        <v>ITEM_HREF</v>
+        <v>MENU</v>
       </c>
       <c r="C56" t="str">
-        <v>/triosss</v>
+        <v>Alpha Phi Omega                    [Menu ID: group-menu-alpha-phi-omega]</v>
       </c>
       <c r="D56" t="str">
-        <v>/?page_id=3202</v>
+        <v>group-menu-alpha-phi-omega                    [Term ID: 1629]</v>
       </c>
       <c r="E56" t="str">
-        <v>❗ HREF Mismatch</v>
+        <v>OK</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="str">
-        <v>group-menu-aaron-j-steinhauer</v>
+        <v>group-menu-alumni</v>
       </c>
       <c r="B57" t="str">
         <v>MENU</v>
       </c>
       <c r="C57" t="str">
-        <v>Aaron J Steinhauer                    [Menu ID: group-menu-aaron-j-steinhauer]</v>
+        <v>Alumni                    [Menu ID: group-menu-alumni]</v>
       </c>
       <c r="D57" t="str">
-        <v>group-menu-aaron-j-steinhauer                    [Term ID: 1684]</v>
+        <v>group-menu-alumni                    [Term ID: 1590]</v>
       </c>
       <c r="E57" t="str">
         <v>OK</v>
@@ -1370,50 +1370,50 @@
     </row>
     <row r="58">
       <c r="A58" t="str">
-        <v>group-menu-aaron-j-steinhauer</v>
+        <v>group-menu-america-reads-counts-</v>
       </c>
       <c r="B58" t="str">
-        <v>ITEM_HREF</v>
+        <v>MENU</v>
       </c>
       <c r="C58" t="str">
-        <v>/sites/default/files/sites/steinhauer/ReferenceLetterForm.pdf</v>
+        <v>America Reads &amp; Counts Program                    [Menu ID: group-menu-america-reads-counts-]</v>
       </c>
       <c r="D58" t="str">
-        <v>/wp-content/uploads/2025/11/ReferenceLetterForm.pdf</v>
+        <v/>
       </c>
       <c r="E58" t="str">
-        <v>❗ HREF Mismatch</v>
+        <v>Missing in WP</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="str">
-        <v>group-menu-aaron-j-steinhauer</v>
+        <v>group-menu-american-studies</v>
       </c>
       <c r="B59" t="str">
-        <v>ITEM_HREF</v>
+        <v>MENU</v>
       </c>
       <c r="C59" t="str">
-        <v>/sites/default/files/sites/steinhauer/Reference_Request_and_Ferpa_Release.pdf</v>
+        <v>American Studies                    [Menu ID: group-menu-american-studies]</v>
       </c>
       <c r="D59" t="str">
-        <v>/wp-content/uploads/2025/11/Reference_Request_and_Ferpa_Release.pdf</v>
+        <v>group-menu-american-studies                    [Term ID: 1699]</v>
       </c>
       <c r="E59" t="str">
-        <v>❗ HREF Mismatch</v>
+        <v>OK</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="str">
-        <v>group-menu-about</v>
+        <v>group-menu-annmarie-urso</v>
       </c>
       <c r="B60" t="str">
         <v>MENU</v>
       </c>
       <c r="C60" t="str">
-        <v>About Geneseo                    [Menu ID: group-menu-about]</v>
+        <v>Annmarie Urso                    [Menu ID: group-menu-annmarie-urso]</v>
       </c>
       <c r="D60" t="str">
-        <v>group-menu-about                    [Term ID: 1586]</v>
+        <v>group-menu-annmarie-urso                    [Term ID: 1686]</v>
       </c>
       <c r="E60" t="str">
         <v>OK</v>
@@ -1421,16 +1421,16 @@
     </row>
     <row r="61">
       <c r="A61" t="str">
-        <v>group-menu-academic-affairs-comm</v>
+        <v>group-menu-anthropology</v>
       </c>
       <c r="B61" t="str">
         <v>MENU</v>
       </c>
       <c r="C61" t="str">
-        <v>Academic Affairs Committee                    [Menu ID: group-menu-academic-affairs-comm]</v>
+        <v>Anthropology Major                    [Menu ID: group-menu-anthropology]</v>
       </c>
       <c r="D61" t="str">
-        <v>group-menu-academic-affairs-comm                    [Term ID: 1722]</v>
+        <v>group-menu-anthropology                    [Term ID: 1698]</v>
       </c>
       <c r="E61" t="str">
         <v>OK</v>
@@ -1438,16 +1438,16 @@
     </row>
     <row r="62">
       <c r="A62" t="str">
-        <v>group-menu-academics</v>
+        <v>group-menu-aop</v>
       </c>
       <c r="B62" t="str">
         <v>MENU</v>
       </c>
       <c r="C62" t="str">
-        <v>Academics                    [Menu ID: group-menu-academics]</v>
+        <v>AOP                    [Menu ID: group-menu-aop]</v>
       </c>
       <c r="D62" t="str">
-        <v>group-menu-academics                    [Term ID: 1706]</v>
+        <v>group-menu-aop                    [Term ID: 1589]</v>
       </c>
       <c r="E62" t="str">
         <v>OK</v>
@@ -1455,33 +1455,33 @@
     </row>
     <row r="63">
       <c r="A63" t="str">
-        <v>group-menu-academics</v>
+        <v>group-menu-art-galleries</v>
       </c>
       <c r="B63" t="str">
-        <v>ITEM_HREF</v>
+        <v>MENU</v>
       </c>
       <c r="C63" t="str">
-        <v>https://bulletin.geneseo.edu</v>
+        <v>Art Galleries                    [Menu ID: group-menu-art-galleries]</v>
       </c>
       <c r="D63" t="str">
         <v/>
       </c>
       <c r="E63" t="str">
-        <v>❗ HREF Mismatch</v>
+        <v>Missing in WP</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="str">
-        <v>group-menu-accounting</v>
+        <v>group-menu-art-history</v>
       </c>
       <c r="B64" t="str">
         <v>MENU</v>
       </c>
       <c r="C64" t="str">
-        <v>College Accounting of Department                    [Menu ID: group-menu-accounting]</v>
+        <v>Art History                    [Menu ID: group-menu-art-history]</v>
       </c>
       <c r="D64" t="str">
-        <v>group-menu-accounting                    [Term ID: 1669]</v>
+        <v>group-menu-art-history                    [Term ID: 1572]</v>
       </c>
       <c r="E64" t="str">
         <v>OK</v>
@@ -1489,16 +1489,16 @@
     </row>
     <row r="65">
       <c r="A65" t="str">
-        <v>group-menu-accounting-society</v>
+        <v>group-menu-asian-studies</v>
       </c>
       <c r="B65" t="str">
         <v>MENU</v>
       </c>
       <c r="C65" t="str">
-        <v>Accounting Society                    [Menu ID: group-menu-accounting-society]</v>
+        <v>Asian Studies                    [Menu ID: group-menu-asian-studies]</v>
       </c>
       <c r="D65" t="str">
-        <v>group-menu-accounting-society                    [Term ID: 1604]</v>
+        <v>group-menu-asian-studies                    [Term ID: 1697]</v>
       </c>
       <c r="E65" t="str">
         <v>OK</v>
@@ -1506,64 +1506,64 @@
     </row>
     <row r="66">
       <c r="A66" t="str">
-        <v>group-menu-accounting-society</v>
+        <v>group-menu-assessment-</v>
       </c>
       <c r="B66" t="str">
-        <v>ITEM_HREF</v>
+        <v>MENU</v>
       </c>
       <c r="C66" t="str">
-        <v>/sites/default/files/sites/accounting_society/Student_Membership_Form.pdf</v>
+        <v>Assessment                     [Menu ID: group-menu-assessment-]</v>
       </c>
       <c r="D66" t="str">
-        <v>/wp-content/uploads/2025/11/Student_Membership_Form.pdf</v>
+        <v>group-menu-assessment-                    [Term ID: 1730]</v>
       </c>
       <c r="E66" t="str">
-        <v>❗ HREF Mismatch</v>
+        <v>OK</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="str">
-        <v>group-menu-actuarial-science-clu</v>
+        <v>group-menu-assessment-</v>
       </c>
       <c r="B67" t="str">
-        <v>MENU</v>
+        <v>ITEM_TITLE</v>
       </c>
       <c r="C67" t="str">
-        <v>Actuarial Science Club                    [Menu ID: group-menu-actuarial-science-clu]</v>
+        <v>Institutional Effectiveness Plan</v>
       </c>
       <c r="D67" t="str">
-        <v>group-menu-actuarial-science-clu                    [Term ID: 1653]</v>
+        <v/>
       </c>
       <c r="E67" t="str">
-        <v>OK</v>
+        <v>Missing in WP</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="str">
-        <v>group-menu-administration-financ</v>
+        <v>group-menu-assessment-</v>
       </c>
       <c r="B68" t="str">
-        <v>MENU</v>
+        <v>ITEM_HREF</v>
       </c>
       <c r="C68" t="str">
-        <v>Finance &amp; Administration                    [Menu ID: group-menu-administration-financ]</v>
+        <v>/sites/default/files/sites/assessment/IEPlan.pdf</v>
       </c>
       <c r="D68" t="str">
-        <v>group-menu-administration-financ                    [Term ID: 1713]</v>
+        <v/>
       </c>
       <c r="E68" t="str">
-        <v>OK</v>
+        <v>Missing in WP</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="str">
-        <v>group-menu-administrative-system</v>
+        <v>group-menu-assesstivus</v>
       </c>
       <c r="B69" t="str">
         <v>MENU</v>
       </c>
       <c r="C69" t="str">
-        <v>Administrative Systems                    [Menu ID: group-menu-administrative-system]</v>
+        <v>Assesstivus                    [Menu ID: group-menu-assesstivus]</v>
       </c>
       <c r="D69" t="str">
         <v/>
@@ -1574,33 +1574,33 @@
     </row>
     <row r="70">
       <c r="A70" t="str">
-        <v>group-menu-affirmative-action</v>
+        <v>group-menu-behavioral-toxicology</v>
       </c>
       <c r="B70" t="str">
         <v>MENU</v>
       </c>
       <c r="C70" t="str">
-        <v>Diversity and Equity                    [Menu ID: group-menu-affirmative-action]</v>
+        <v>Behavioral Toxicology Lab                    [Menu ID: group-menu-behavioral-toxicology]</v>
       </c>
       <c r="D70" t="str">
-        <v/>
+        <v>group-menu-behavioral-toxicology                    [Term ID: 1623]</v>
       </c>
       <c r="E70" t="str">
-        <v>Missing in WP</v>
+        <v>OK</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="str">
-        <v>group-menu-alpha-chi-rho</v>
+        <v>group-menu-biochemistry</v>
       </c>
       <c r="B71" t="str">
         <v>MENU</v>
       </c>
       <c r="C71" t="str">
-        <v>Alpha Chi Rho                    [Menu ID: group-menu-alpha-chi-rho]</v>
+        <v>Biochemistry                    [Menu ID: group-menu-biochemistry]</v>
       </c>
       <c r="D71" t="str">
-        <v>group-menu-alpha-chi-rho                    [Term ID: 1734]</v>
+        <v>group-menu-biochemistry                    [Term ID: 1696]</v>
       </c>
       <c r="E71" t="str">
         <v>OK</v>
@@ -1608,33 +1608,33 @@
     </row>
     <row r="72">
       <c r="A72" t="str">
-        <v>group-menu-alpha-chi-rho</v>
+        <v>group-menu-biology</v>
       </c>
       <c r="B72" t="str">
-        <v>ITEM_HREF</v>
+        <v>MENU</v>
       </c>
       <c r="C72" t="str">
-        <v>/alphachirho/rush</v>
+        <v>Department of Biology                    [Menu ID: group-menu-biology]</v>
       </c>
       <c r="D72" t="str">
-        <v>/rush</v>
+        <v>group-menu-biology                    [Term ID: 1556]</v>
       </c>
       <c r="E72" t="str">
-        <v>❗ HREF Mismatch</v>
+        <v>OK</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="str">
-        <v>group-menu-alpha-kappa-psi</v>
+        <v>group-menu-biology-club</v>
       </c>
       <c r="B73" t="str">
         <v>MENU</v>
       </c>
       <c r="C73" t="str">
-        <v>Alpha Kappa Psi - Psi Omicron                    [Menu ID: group-menu-alpha-kappa-psi]</v>
+        <v>Biology Club                    [Menu ID: group-menu-biology-club]</v>
       </c>
       <c r="D73" t="str">
-        <v>group-menu-alpha-kappa-psi                    [Term ID: 1600]</v>
+        <v>group-menu-biology-club                    [Term ID: 1628]</v>
       </c>
       <c r="E73" t="str">
         <v>OK</v>
@@ -1642,135 +1642,135 @@
     </row>
     <row r="74">
       <c r="A74" t="str">
-        <v>group-menu-alpha-kappa-psi</v>
+        <v>group-menu-biophysics</v>
       </c>
       <c r="B74" t="str">
-        <v>ITEM_HREF</v>
+        <v>MENU</v>
       </c>
       <c r="C74" t="str">
-        <v>/akpsi.geneseo</v>
+        <v>Biophysics                    [Menu ID: group-menu-biophysics]</v>
       </c>
       <c r="D74" t="str">
-        <v>/akpsi-geneseo</v>
+        <v>group-menu-biophysics                    [Term ID: 1695]</v>
       </c>
       <c r="E74" t="str">
-        <v>❗ HREF Mismatch</v>
+        <v>OK</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="str">
-        <v>group-menu-alpha-kappa-psi</v>
+        <v>group-menu-black-studies</v>
       </c>
       <c r="B75" t="str">
-        <v>ITEM_HREF</v>
+        <v>MENU</v>
       </c>
       <c r="C75" t="str">
-        <v>/akpsi.geneseo/recruitment</v>
+        <v>Black and Africana Studies                    [Menu ID: group-menu-black-studies]</v>
       </c>
       <c r="D75" t="str">
-        <v>/akpsigeneseo/recruitment</v>
+        <v>group-menu-black-studies                    [Term ID: 1607]</v>
       </c>
       <c r="E75" t="str">
-        <v>❗ HREF Mismatch</v>
+        <v>OK</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="str">
-        <v>group-menu-alpha-kappa-psi</v>
+        <v>group-menu-bridge</v>
       </c>
       <c r="B76" t="str">
-        <v>ITEM_HREF</v>
+        <v>MENU</v>
       </c>
       <c r="C76" t="str">
-        <v>/akpsi.geneseo/brothers</v>
+        <v>Bridge                    [Menu ID: group-menu-bridge]</v>
       </c>
       <c r="D76" t="str">
-        <v>/akpsigeneseo/brothers</v>
+        <v/>
       </c>
       <c r="E76" t="str">
-        <v>❗ HREF Mismatch</v>
+        <v>Missing in WP</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="str">
-        <v>group-menu-alpha-kappa-psi</v>
+        <v>group-menu-brodie-box-office</v>
       </c>
       <c r="B77" t="str">
-        <v>ITEM_HREF</v>
+        <v>MENU</v>
       </c>
       <c r="C77" t="str">
-        <v>/akpsi.geneseo/alumni</v>
+        <v>Brodie Box Office                    [Menu ID: group-menu-brodie-box-office]</v>
       </c>
       <c r="D77" t="str">
-        <v>/akpsigeneseo/alumni</v>
+        <v>group-menu-brodie-box-office                    [Term ID: 1654]</v>
       </c>
       <c r="E77" t="str">
-        <v>❗ HREF Mismatch</v>
+        <v>OK</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="str">
-        <v>group-menu-alpha-kappa-psi</v>
+        <v>group-menu-budget-office</v>
       </c>
       <c r="B78" t="str">
-        <v>ITEM_HREF</v>
+        <v>MENU</v>
       </c>
       <c r="C78" t="str">
-        <v>/akpsi.geneseo/executive-board-and-chairs</v>
+        <v>Budget Office                    [Menu ID: group-menu-budget-office]</v>
       </c>
       <c r="D78" t="str">
-        <v>/akpsigeneseo/executive-board-and-chairs</v>
+        <v>group-menu-budget-office                    [Term ID: 1631]</v>
       </c>
       <c r="E78" t="str">
-        <v>❗ HREF Mismatch</v>
+        <v>OK</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="str">
-        <v>group-menu-alpha-kappa-psi</v>
+        <v>group-menu-calendar</v>
       </c>
       <c r="B79" t="str">
-        <v>CHILD_HREF</v>
+        <v>MENU</v>
       </c>
       <c r="C79" t="str">
-        <v>/akpsi.geneseo/descriptions-and-events</v>
+        <v>Calendar                    [Menu ID: group-menu-calendar]</v>
       </c>
       <c r="D79" t="str">
-        <v>/akpsigeneseo/descriptions-and-events</v>
+        <v/>
       </c>
       <c r="E79" t="str">
-        <v>❗ HREF Mismatch</v>
+        <v>Missing in WP</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="str">
-        <v>group-menu-alpha-kappa-psi</v>
+        <v>group-menu-campus-life</v>
       </c>
       <c r="B80" t="str">
-        <v>ITEM_HREF</v>
+        <v>MENU</v>
       </c>
       <c r="C80" t="str">
-        <v>/akpsi.geneseo/q%26a</v>
+        <v>Student &amp; Campus Life                    [Menu ID: group-menu-campus-life]</v>
       </c>
       <c r="D80" t="str">
-        <v>/akpsigeneseo/qa</v>
+        <v>group-menu-campus-life                    [Term ID: 1717]</v>
       </c>
       <c r="E80" t="str">
-        <v>❗ HREF Mismatch</v>
+        <v>OK</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="str">
-        <v>group-menu-alpha-phi-omega</v>
+        <v>group-menu-campus-living</v>
       </c>
       <c r="B81" t="str">
         <v>MENU</v>
       </c>
       <c r="C81" t="str">
-        <v>Alpha Phi Omega                    [Menu ID: group-menu-alpha-phi-omega]</v>
+        <v>Residence Life                    [Menu ID: group-menu-campus-living]</v>
       </c>
       <c r="D81" t="str">
-        <v>group-menu-alpha-phi-omega                    [Term ID: 1629]</v>
+        <v>group-menu-campus-living                    [Term ID: 1574]</v>
       </c>
       <c r="E81" t="str">
         <v>OK</v>
@@ -1778,16 +1778,16 @@
     </row>
     <row r="82">
       <c r="A82" t="str">
-        <v>group-menu-alumni</v>
+        <v>group-menu-campus-personal-safet</v>
       </c>
       <c r="B82" t="str">
         <v>MENU</v>
       </c>
       <c r="C82" t="str">
-        <v>Alumni                    [Menu ID: group-menu-alumni]</v>
+        <v>Advisory Committee on Campus Safety                    [Menu ID: group-menu-campus-personal-safet]</v>
       </c>
       <c r="D82" t="str">
-        <v>group-menu-alumni                    [Term ID: 1590]</v>
+        <v>group-menu-campus-personal-safet                    [Term ID: 1619]</v>
       </c>
       <c r="E82" t="str">
         <v>OK</v>
@@ -1795,47 +1795,47 @@
     </row>
     <row r="83">
       <c r="A83" t="str">
-        <v>group-menu-alumni</v>
+        <v>group-menu-campus-scheduling-spe</v>
       </c>
       <c r="B83" t="str">
-        <v>ITEM_HREF</v>
+        <v>MENU</v>
       </c>
       <c r="C83" t="str">
-        <v>http://uknight.geneseo.edu/s/1648/Alumni/index.aspx?sid=1648&amp;gid=2&amp;pgid=460</v>
+        <v>Campus Scheduling &amp; Special Events                    [Menu ID: group-menu-campus-scheduling-spe]</v>
       </c>
       <c r="D83" t="str">
-        <v>https://uknight.geneseo.edu/s/1648/Alumni/index.aspx?sid=1648&amp;gid=2&amp;pgid=460</v>
+        <v>group-menu-campus-scheduling-spe                    [Term ID: 1588]</v>
       </c>
       <c r="E83" t="str">
-        <v>❗ HREF Mismatch</v>
+        <v>OK</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="str">
-        <v>group-menu-alumni</v>
+        <v>group-menu-career-development</v>
       </c>
       <c r="B84" t="str">
-        <v>ITEM_TITLE</v>
+        <v>MENU</v>
       </c>
       <c r="C84" t="str">
-        <v>U-Knight Community</v>
+        <v>Career Design                    [Menu ID: group-menu-career-development]</v>
       </c>
       <c r="D84" t="str">
-        <v/>
+        <v>group-menu-career-development                    [Term ID: 1580]</v>
       </c>
       <c r="E84" t="str">
-        <v>Missing in WP</v>
+        <v>OK</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="str">
-        <v>group-menu-alumni</v>
+        <v>group-menu-cesar-aguilar</v>
       </c>
       <c r="B85" t="str">
-        <v>ITEM_HREF</v>
+        <v>MENU</v>
       </c>
       <c r="C85" t="str">
-        <v>http://uknight.geneseo.edu/s/1648/Alumni/index.aspx?sid=1648&amp;gid=2&amp;pgid=531</v>
+        <v>Cesar Aguilar                    [Menu ID: group-menu-cesar-aguilar]</v>
       </c>
       <c r="D85" t="str">
         <v/>
@@ -1846,33 +1846,33 @@
     </row>
     <row r="86">
       <c r="A86" t="str">
-        <v>group-menu-america-reads-counts-</v>
+        <v>group-menu-charlie-freeman</v>
       </c>
       <c r="B86" t="str">
         <v>MENU</v>
       </c>
       <c r="C86" t="str">
-        <v>America Reads &amp; Counts Program                    [Menu ID: group-menu-america-reads-counts-]</v>
+        <v>Charlie Freeman                    [Menu ID: group-menu-charlie-freeman]</v>
       </c>
       <c r="D86" t="str">
-        <v/>
+        <v>group-menu-charlie-freeman                    [Term ID: 1691]</v>
       </c>
       <c r="E86" t="str">
-        <v>Missing in WP</v>
+        <v>OK</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="str">
-        <v>group-menu-american-studies</v>
+        <v>group-menu-chemistry</v>
       </c>
       <c r="B87" t="str">
         <v>MENU</v>
       </c>
       <c r="C87" t="str">
-        <v>American Studies                    [Menu ID: group-menu-american-studies]</v>
+        <v>Department of Chemistry and Biochemistry                    [Menu ID: group-menu-chemistry]</v>
       </c>
       <c r="D87" t="str">
-        <v>group-menu-american-studies                    [Term ID: 1699]</v>
+        <v>group-menu-chemistry                    [Term ID: 1577]</v>
       </c>
       <c r="E87" t="str">
         <v>OK</v>
@@ -1880,16 +1880,16 @@
     </row>
     <row r="88">
       <c r="A88" t="str">
-        <v>group-menu-annmarie-urso</v>
+        <v>group-menu-chemistry-stockroom</v>
       </c>
       <c r="B88" t="str">
         <v>MENU</v>
       </c>
       <c r="C88" t="str">
-        <v>Annmarie Urso                    [Menu ID: group-menu-annmarie-urso]</v>
+        <v>Chemistry Stockroom                    [Menu ID: group-menu-chemistry-stockroom]</v>
       </c>
       <c r="D88" t="str">
-        <v>group-menu-annmarie-urso                    [Term ID: 1686]</v>
+        <v>group-menu-chemistry-stockroom                    [Term ID: 1561]</v>
       </c>
       <c r="E88" t="str">
         <v>OK</v>
@@ -1897,16 +1897,16 @@
     </row>
     <row r="89">
       <c r="A89" t="str">
-        <v>group-menu-anthropology</v>
+        <v>group-menu-cidd</v>
       </c>
       <c r="B89" t="str">
         <v>MENU</v>
       </c>
       <c r="C89" t="str">
-        <v>Anthropology Major                    [Menu ID: group-menu-anthropology]</v>
+        <v>Center for Integrative Learning                    [Menu ID: group-menu-cidd]</v>
       </c>
       <c r="D89" t="str">
-        <v>group-menu-anthropology                    [Term ID: 1698]</v>
+        <v>group-menu-cidd                    [Term ID: 1581]</v>
       </c>
       <c r="E89" t="str">
         <v>OK</v>
@@ -1914,16 +1914,16 @@
     </row>
     <row r="90">
       <c r="A90" t="str">
-        <v>group-menu-aop</v>
+        <v>group-menu-cit</v>
       </c>
       <c r="B90" t="str">
         <v>MENU</v>
       </c>
       <c r="C90" t="str">
-        <v>AOP                    [Menu ID: group-menu-aop]</v>
+        <v>CIT                    [Menu ID: group-menu-cit]</v>
       </c>
       <c r="D90" t="str">
-        <v>group-menu-aop                    [Term ID: 1589]</v>
+        <v>group-menu-cit                    [Term ID: 1715]</v>
       </c>
       <c r="E90" t="str">
         <v>OK</v>
@@ -1931,13 +1931,13 @@
     </row>
     <row r="91">
       <c r="A91" t="str">
-        <v>group-menu-art-galleries</v>
+        <v>group-menu-college-senate</v>
       </c>
       <c r="B91" t="str">
         <v>MENU</v>
       </c>
       <c r="C91" t="str">
-        <v>Art Galleries                    [Menu ID: group-menu-art-galleries]</v>
+        <v>College Senate                    [Menu ID: group-menu-college-senate]</v>
       </c>
       <c r="D91" t="str">
         <v/>
@@ -1948,16 +1948,16 @@
     </row>
     <row r="92">
       <c r="A92" t="str">
-        <v>group-menu-art-history</v>
+        <v>group-menu-commencement</v>
       </c>
       <c r="B92" t="str">
         <v>MENU</v>
       </c>
       <c r="C92" t="str">
-        <v>Art History                    [Menu ID: group-menu-art-history]</v>
+        <v>Commencement                    [Menu ID: group-menu-commencement]</v>
       </c>
       <c r="D92" t="str">
-        <v>group-menu-art-history                    [Term ID: 1572]</v>
+        <v>group-menu-commencement                    [Term ID: 1655]</v>
       </c>
       <c r="E92" t="str">
         <v>OK</v>
@@ -1965,16 +1965,16 @@
     </row>
     <row r="93">
       <c r="A93" t="str">
-        <v>group-menu-asian-studies</v>
+        <v>group-menu-communication</v>
       </c>
       <c r="B93" t="str">
         <v>MENU</v>
       </c>
       <c r="C93" t="str">
-        <v>Asian Studies                    [Menu ID: group-menu-asian-studies]</v>
+        <v>Communication                    [Menu ID: group-menu-communication]</v>
       </c>
       <c r="D93" t="str">
-        <v>group-menu-asian-studies                    [Term ID: 1697]</v>
+        <v>group-menu-communication                    [Term ID: 1554]</v>
       </c>
       <c r="E93" t="str">
         <v>OK</v>
@@ -1982,16 +1982,16 @@
     </row>
     <row r="94">
       <c r="A94" t="str">
-        <v>group-menu-assessment-</v>
+        <v>group-menu-communications-market</v>
       </c>
       <c r="B94" t="str">
         <v>MENU</v>
       </c>
       <c r="C94" t="str">
-        <v>Assessment                     [Menu ID: group-menu-assessment-]</v>
+        <v>Communications and Marketing                    [Menu ID: group-menu-communications-market]</v>
       </c>
       <c r="D94" t="str">
-        <v>group-menu-assessment-                    [Term ID: 1730]</v>
+        <v>group-menu-communications-market                    [Term ID: 1707]</v>
       </c>
       <c r="E94" t="str">
         <v>OK</v>
@@ -1999,67 +1999,67 @@
     </row>
     <row r="95">
       <c r="A95" t="str">
-        <v>group-menu-assessment-</v>
+        <v>group-menu-community-resource-ne</v>
       </c>
       <c r="B95" t="str">
-        <v>ITEM_TITLE</v>
+        <v>MENU</v>
       </c>
       <c r="C95" t="str">
-        <v>Institutional Effectiveness Plan</v>
+        <v>Community Resource Network                    [Menu ID: group-menu-community-resource-ne]</v>
       </c>
       <c r="D95" t="str">
-        <v/>
+        <v>group-menu-community-resource-ne                    [Term ID: 1733]</v>
       </c>
       <c r="E95" t="str">
-        <v>Missing in WP</v>
+        <v>OK</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="str">
-        <v>group-menu-assessment-</v>
+        <v>group-menu-comparative-literatur</v>
       </c>
       <c r="B96" t="str">
-        <v>ITEM_HREF</v>
+        <v>MENU</v>
       </c>
       <c r="C96" t="str">
-        <v>/sites/default/files/sites/assessment/IEPlan.pdf</v>
+        <v>Comparative Literature &amp; Literary Translation                    [Menu ID: group-menu-comparative-literatur]</v>
       </c>
       <c r="D96" t="str">
-        <v/>
+        <v>group-menu-comparative-literatur                    [Term ID: 1693]</v>
       </c>
       <c r="E96" t="str">
-        <v>Missing in WP</v>
+        <v>OK</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="str">
-        <v>group-menu-assesstivus</v>
+        <v>group-menu-credit-union</v>
       </c>
       <c r="B97" t="str">
         <v>MENU</v>
       </c>
       <c r="C97" t="str">
-        <v>Assesstivus                    [Menu ID: group-menu-assesstivus]</v>
+        <v>Credit Union                    [Menu ID: group-menu-credit-union]</v>
       </c>
       <c r="D97" t="str">
-        <v/>
+        <v>group-menu-credit-union                    [Term ID: 1716]</v>
       </c>
       <c r="E97" t="str">
-        <v>Missing in WP</v>
+        <v>OK</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="str">
-        <v>group-menu-behavioral-toxicology</v>
+        <v>group-menu-crew</v>
       </c>
       <c r="B98" t="str">
         <v>MENU</v>
       </c>
       <c r="C98" t="str">
-        <v>Behavioral Toxicology Lab                    [Menu ID: group-menu-behavioral-toxicology]</v>
+        <v>Crew                    [Menu ID: group-menu-crew]</v>
       </c>
       <c r="D98" t="str">
-        <v>group-menu-behavioral-toxicology                    [Term ID: 1623]</v>
+        <v>group-menu-crew                    [Term ID: 1630]</v>
       </c>
       <c r="E98" t="str">
         <v>OK</v>
@@ -2067,16 +2067,16 @@
     </row>
     <row r="99">
       <c r="A99" t="str">
-        <v>group-menu-biochemistry</v>
+        <v>group-menu-curriculum-and-assess</v>
       </c>
       <c r="B99" t="str">
         <v>MENU</v>
       </c>
       <c r="C99" t="str">
-        <v>Biochemistry                    [Menu ID: group-menu-biochemistry]</v>
+        <v>Curriculum                    [Menu ID: group-menu-curriculum-and-assess]</v>
       </c>
       <c r="D99" t="str">
-        <v>group-menu-biochemistry                    [Term ID: 1696]</v>
+        <v>group-menu-curriculum-and-assess                    [Term ID: 1609]</v>
       </c>
       <c r="E99" t="str">
         <v>OK</v>
@@ -2084,33 +2084,33 @@
     </row>
     <row r="100">
       <c r="A100" t="str">
-        <v>group-menu-biology</v>
+        <v>group-menu-dance-at-geneseo</v>
       </c>
       <c r="B100" t="str">
         <v>MENU</v>
       </c>
       <c r="C100" t="str">
-        <v>Department of Biology                    [Menu ID: group-menu-biology]</v>
+        <v>Dance at Geneseo                    [Menu ID: group-menu-dance-at-geneseo]</v>
       </c>
       <c r="D100" t="str">
-        <v>group-menu-biology                    [Term ID: 1556]</v>
+        <v/>
       </c>
       <c r="E100" t="str">
-        <v>OK</v>
+        <v>Missing in WP</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="str">
-        <v>group-menu-biology-club</v>
+        <v>group-menu-david-geiger</v>
       </c>
       <c r="B101" t="str">
         <v>MENU</v>
       </c>
       <c r="C101" t="str">
-        <v>Biology Club                    [Menu ID: group-menu-biology-club]</v>
+        <v>David Geiger                    [Menu ID: group-menu-david-geiger]</v>
       </c>
       <c r="D101" t="str">
-        <v>group-menu-biology-club                    [Term ID: 1628]</v>
+        <v>group-menu-david-geiger                    [Term ID: 1679]</v>
       </c>
       <c r="E101" t="str">
         <v>OK</v>
@@ -2118,16 +2118,16 @@
     </row>
     <row r="102">
       <c r="A102" t="str">
-        <v>group-menu-biophysics</v>
+        <v>group-menu-dean-of-students</v>
       </c>
       <c r="B102" t="str">
         <v>MENU</v>
       </c>
       <c r="C102" t="str">
-        <v>Biophysics                    [Menu ID: group-menu-biophysics]</v>
+        <v>Dean of Students                    [Menu ID: group-menu-dean-of-students]</v>
       </c>
       <c r="D102" t="str">
-        <v>group-menu-biophysics                    [Term ID: 1695]</v>
+        <v>group-menu-dean-of-students                    [Term ID: 1674]</v>
       </c>
       <c r="E102" t="str">
         <v>OK</v>
@@ -2135,16 +2135,16 @@
     </row>
     <row r="103">
       <c r="A103" t="str">
-        <v>group-menu-black-studies</v>
+        <v>group-menu-dennis-showers</v>
       </c>
       <c r="B103" t="str">
         <v>MENU</v>
       </c>
       <c r="C103" t="str">
-        <v>Black and Africana Studies                    [Menu ID: group-menu-black-studies]</v>
+        <v>Dennis Showers                    [Menu ID: group-menu-dennis-showers]</v>
       </c>
       <c r="D103" t="str">
-        <v>group-menu-black-studies                    [Term ID: 1607]</v>
+        <v>group-menu-dennis-showers                    [Term ID: 1683]</v>
       </c>
       <c r="E103" t="str">
         <v>OK</v>
@@ -2152,237 +2152,237 @@
     </row>
     <row r="104">
       <c r="A104" t="str">
-        <v>group-menu-black-studies</v>
+        <v>group-menu-department-of-music</v>
       </c>
       <c r="B104" t="str">
-        <v>CHILD_HREF</v>
+        <v>MENU</v>
       </c>
       <c r="C104" t="str">
-        <v>/2013MLK</v>
+        <v>Department of Music &amp; Musical Theatre                    [Menu ID: group-menu-department-of-music]</v>
       </c>
       <c r="D104" t="str">
-        <v>/2013mlk</v>
+        <v/>
       </c>
       <c r="E104" t="str">
-        <v>❗ HREF Mismatch</v>
+        <v>Missing in WP</v>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="str">
-        <v>group-menu-black-studies</v>
+        <v>group-menu-diasporas-of-color-un</v>
       </c>
       <c r="B105" t="str">
-        <v>CHILD_HREF</v>
+        <v>MENU</v>
       </c>
       <c r="C105" t="str">
-        <v>/2012MLK</v>
+        <v>Diasporas of Color Undergraduate                     [Menu ID: group-menu-diasporas-of-color-un]</v>
       </c>
       <c r="D105" t="str">
-        <v>/2012mlk</v>
+        <v>group-menu-diasporas-of-color-un                    [Term ID: 1661]</v>
       </c>
       <c r="E105" t="str">
-        <v>❗ HREF Mismatch</v>
+        <v>OK</v>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="str">
-        <v>group-menu-black-studies</v>
+        <v>group-menu-discovery-cafe</v>
       </c>
       <c r="B106" t="str">
-        <v>CHILD_HREF</v>
+        <v>MENU</v>
       </c>
       <c r="C106" t="str">
-        <v>/2011MLK</v>
+        <v>Discovery Cafe                    [Menu ID: group-menu-discovery-cafe]</v>
       </c>
       <c r="D106" t="str">
-        <v>/2011mlk</v>
+        <v/>
       </c>
       <c r="E106" t="str">
-        <v>❗ HREF Mismatch</v>
+        <v>Missing in WP</v>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="str">
-        <v>group-menu-black-studies</v>
+        <v>group-menu-diversity-at-geneseo</v>
       </c>
       <c r="B107" t="str">
-        <v>CHILD_HREF</v>
+        <v>MENU</v>
       </c>
       <c r="C107" t="str">
-        <v>/2010MLK</v>
+        <v>Diversity at Geneseo                    [Menu ID: group-menu-diversity-at-geneseo]</v>
       </c>
       <c r="D107" t="str">
-        <v>/2010mlk</v>
+        <v>group-menu-diversity-at-geneseo                    [Term ID: 1551]</v>
       </c>
       <c r="E107" t="str">
-        <v>❗ HREF Mismatch</v>
+        <v>OK</v>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="str">
-        <v>group-menu-black-studies</v>
+        <v>group-menu-dr-kokjo-adabra</v>
       </c>
       <c r="B108" t="str">
-        <v>CHILD_HREF</v>
+        <v>MENU</v>
       </c>
       <c r="C108" t="str">
-        <v>/2009MLK</v>
+        <v>Dr. Kodjo Adabra                    [Menu ID: group-menu-dr-kokjo-adabra]</v>
       </c>
       <c r="D108" t="str">
-        <v>/2009mlk</v>
+        <v>group-menu-dr-kokjo-adabra                    [Term ID: 1712]</v>
       </c>
       <c r="E108" t="str">
-        <v>❗ HREF Mismatch</v>
+        <v>OK</v>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="str">
-        <v>group-menu-black-studies</v>
+        <v>group-menu-dr-shuo-chen</v>
       </c>
       <c r="B109" t="str">
-        <v>CHILD_HREF</v>
+        <v>MENU</v>
       </c>
       <c r="C109" t="str">
-        <v>/2008MLK</v>
+        <v>Dr. Shuo Chen                    [Menu ID: group-menu-dr-shuo-chen]</v>
       </c>
       <c r="D109" t="str">
-        <v>/2008mlk</v>
+        <v/>
       </c>
       <c r="E109" t="str">
-        <v>❗ HREF Mismatch</v>
+        <v>Missing in WP</v>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="str">
-        <v>group-menu-bridge</v>
+        <v>group-menu-duplicating-center</v>
       </c>
       <c r="B110" t="str">
         <v>MENU</v>
       </c>
       <c r="C110" t="str">
-        <v>Bridge                    [Menu ID: group-menu-bridge]</v>
+        <v>Duplicating Center                    [Menu ID: group-menu-duplicating-center]</v>
       </c>
       <c r="D110" t="str">
-        <v/>
+        <v>group-menu-duplicating-center                    [Term ID: 1566]</v>
       </c>
       <c r="E110" t="str">
-        <v>Missing in WP</v>
+        <v>OK</v>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="str">
-        <v>group-menu-brodie-box-office</v>
+        <v>group-menu-ed-beary</v>
       </c>
       <c r="B111" t="str">
         <v>MENU</v>
       </c>
       <c r="C111" t="str">
-        <v>Brodie Box Office                    [Menu ID: group-menu-brodie-box-office]</v>
+        <v>Ed Beary                    [Menu ID: group-menu-ed-beary]</v>
       </c>
       <c r="D111" t="str">
-        <v>group-menu-brodie-box-office                    [Term ID: 1654]</v>
+        <v/>
       </c>
       <c r="E111" t="str">
-        <v>OK</v>
+        <v>Missing in WP</v>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="str">
-        <v>group-menu-budget-office</v>
+        <v>group-menu-ed-pogozelski</v>
       </c>
       <c r="B112" t="str">
         <v>MENU</v>
       </c>
       <c r="C112" t="str">
-        <v>Budget Office                    [Menu ID: group-menu-budget-office]</v>
+        <v>Ed Pogozelski                    [Menu ID: group-menu-ed-pogozelski]</v>
       </c>
       <c r="D112" t="str">
-        <v>group-menu-budget-office                    [Term ID: 1631]</v>
+        <v/>
       </c>
       <c r="E112" t="str">
-        <v>OK</v>
+        <v>Missing in WP</v>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="str">
-        <v>group-menu-budget-office</v>
+        <v>group-menu-edgar-fellows-program</v>
       </c>
       <c r="B113" t="str">
-        <v>ITEM_HREF</v>
+        <v>MENU</v>
       </c>
       <c r="C113" t="str">
-        <v>/sites/default/files/sites/budget/UA3_Form.xls</v>
+        <v>Edgar Fellows Program                    [Menu ID: group-menu-edgar-fellows-program]</v>
       </c>
       <c r="D113" t="str">
-        <v>/wp-content/uploads/2025/11/UA3_Form.xls</v>
+        <v>group-menu-edgar-fellows-program                    [Term ID: 1688]</v>
       </c>
       <c r="E113" t="str">
-        <v>❗ HREF Mismatch</v>
+        <v>OK</v>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="str">
-        <v>group-menu-calendar</v>
+        <v>group-menu-emergencies</v>
       </c>
       <c r="B114" t="str">
         <v>MENU</v>
       </c>
       <c r="C114" t="str">
-        <v>Calendar                    [Menu ID: group-menu-calendar]</v>
+        <v>Emergencies                    [Menu ID: group-menu-emergencies]</v>
       </c>
       <c r="D114" t="str">
-        <v/>
+        <v>group-menu-emergencies                    [Term ID: 1569]</v>
       </c>
       <c r="E114" t="str">
-        <v>Missing in WP</v>
+        <v>OK</v>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="str">
-        <v>group-menu-campus-life</v>
+        <v>group-menu-emergency</v>
       </c>
       <c r="B115" t="str">
         <v>MENU</v>
       </c>
       <c r="C115" t="str">
-        <v>Student &amp; Campus Life                    [Menu ID: group-menu-campus-life]</v>
+        <v>Emergency                    [Menu ID: group-menu-emergency]</v>
       </c>
       <c r="D115" t="str">
-        <v>group-menu-campus-life                    [Term ID: 1717]</v>
+        <v/>
       </c>
       <c r="E115" t="str">
-        <v>OK</v>
+        <v>Missing in WP</v>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="str">
-        <v>group-menu-campus-life</v>
+        <v>group-menu-employee-assistance</v>
       </c>
       <c r="B116" t="str">
-        <v>ITEM_HREF</v>
+        <v>MENU</v>
       </c>
       <c r="C116" t="str">
-        <v>http://gold.geneseo.edu</v>
+        <v>Employee Assistance                    [Menu ID: group-menu-employee-assistance]</v>
       </c>
       <c r="D116" t="str">
         <v/>
       </c>
       <c r="E116" t="str">
-        <v>❗ HREF Mismatch</v>
+        <v>Missing in WP</v>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="str">
-        <v>group-menu-campus-living</v>
+        <v>group-menu-english</v>
       </c>
       <c r="B117" t="str">
         <v>MENU</v>
       </c>
       <c r="C117" t="str">
-        <v>Residence Life                    [Menu ID: group-menu-campus-living]</v>
+        <v>English                    [Menu ID: group-menu-english]</v>
       </c>
       <c r="D117" t="str">
-        <v>group-menu-campus-living                    [Term ID: 1574]</v>
+        <v>group-menu-english                    [Term ID: 1564]</v>
       </c>
       <c r="E117" t="str">
         <v>OK</v>
@@ -2390,16 +2390,16 @@
     </row>
     <row r="118">
       <c r="A118" t="str">
-        <v>group-menu-campus-personal-safet</v>
+        <v>group-menu-english-for-speakers-</v>
       </c>
       <c r="B118" t="str">
         <v>MENU</v>
       </c>
       <c r="C118" t="str">
-        <v>Advisory Committee on Campus Safety                    [Menu ID: group-menu-campus-personal-safet]</v>
+        <v>English for Speakers of Other Languages                    [Menu ID: group-menu-english-for-speakers-]</v>
       </c>
       <c r="D118" t="str">
-        <v>group-menu-campus-personal-safet                    [Term ID: 1619]</v>
+        <v>group-menu-english-for-speakers-                    [Term ID: 1742]</v>
       </c>
       <c r="E118" t="str">
         <v>OK</v>
@@ -2407,50 +2407,50 @@
     </row>
     <row r="119">
       <c r="A119" t="str">
-        <v>group-menu-campus-personal-safet</v>
+        <v>group-menu-environmental-health-</v>
       </c>
       <c r="B119" t="str">
-        <v>ITEM_HREF</v>
+        <v>MENU</v>
       </c>
       <c r="C119" t="str">
-        <v>/safety/final_reports</v>
+        <v>Environmental Health &amp; Safety                    [Menu ID: group-menu-environmental-health-]</v>
       </c>
       <c r="D119" t="str">
-        <v>/?page_id=42799</v>
+        <v>group-menu-environmental-health-                    [Term ID: 1708]</v>
       </c>
       <c r="E119" t="str">
-        <v>❗ HREF Mismatch</v>
+        <v>OK</v>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="str">
-        <v>group-menu-campus-scheduling-spe</v>
+        <v>group-menu-externship-program</v>
       </c>
       <c r="B120" t="str">
         <v>MENU</v>
       </c>
       <c r="C120" t="str">
-        <v>Campus Scheduling &amp; Special Events                    [Menu ID: group-menu-campus-scheduling-spe]</v>
+        <v>Externship Program                    [Menu ID: group-menu-externship-program]</v>
       </c>
       <c r="D120" t="str">
-        <v>group-menu-campus-scheduling-spe                    [Term ID: 1588]</v>
+        <v/>
       </c>
       <c r="E120" t="str">
-        <v>OK</v>
+        <v>Missing in WP</v>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="str">
-        <v>group-menu-career-development</v>
+        <v>group-menu-facilities-planning</v>
       </c>
       <c r="B121" t="str">
         <v>MENU</v>
       </c>
       <c r="C121" t="str">
-        <v>Career Design                    [Menu ID: group-menu-career-development]</v>
+        <v>Planning &amp; Construction                    [Menu ID: group-menu-facilities-planning]</v>
       </c>
       <c r="D121" t="str">
-        <v>group-menu-career-development                    [Term ID: 1580]</v>
+        <v>group-menu-facilities-planning                    [Term ID: 1642]</v>
       </c>
       <c r="E121" t="str">
         <v>OK</v>
@@ -2458,33 +2458,33 @@
     </row>
     <row r="122">
       <c r="A122" t="str">
-        <v>group-menu-cesar-aguilar</v>
+        <v>group-menu-facilities-services</v>
       </c>
       <c r="B122" t="str">
         <v>MENU</v>
       </c>
       <c r="C122" t="str">
-        <v>Cesar Aguilar                    [Menu ID: group-menu-cesar-aguilar]</v>
+        <v>Facilities Services                    [Menu ID: group-menu-facilities-services]</v>
       </c>
       <c r="D122" t="str">
-        <v/>
+        <v>group-menu-facilities-services                    [Term ID: 1549]</v>
       </c>
       <c r="E122" t="str">
-        <v>Missing in WP</v>
+        <v>OK</v>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="str">
-        <v>group-menu-charlie-freeman</v>
+        <v>group-menu-faculty-and-staff</v>
       </c>
       <c r="B123" t="str">
         <v>MENU</v>
       </c>
       <c r="C123" t="str">
-        <v>Charlie Freeman                    [Menu ID: group-menu-charlie-freeman]</v>
+        <v>Employees                    [Menu ID: group-menu-faculty-and-staff]</v>
       </c>
       <c r="D123" t="str">
-        <v>group-menu-charlie-freeman                    [Term ID: 1691]</v>
+        <v>group-menu-faculty-and-staff                    [Term ID: 1705]</v>
       </c>
       <c r="E123" t="str">
         <v>OK</v>
@@ -2492,33 +2492,33 @@
     </row>
     <row r="124">
       <c r="A124" t="str">
-        <v>group-menu-charlie-freeman</v>
+        <v>group-menu-fellowships-scholarsh</v>
       </c>
       <c r="B124" t="str">
-        <v>ITEM_HREF</v>
+        <v>MENU</v>
       </c>
       <c r="C124" t="str">
-        <v>/sites/default/files/sites/freeman/letter_of_rec_form.pdf</v>
+        <v>Fellowships &amp; Scholarships                    [Menu ID: group-menu-fellowships-scholarsh]</v>
       </c>
       <c r="D124" t="str">
-        <v>/wp-content/uploads/2025/11/letter_of_rec_form.pdf</v>
+        <v>group-menu-fellowships-scholarsh                    [Term ID: 1659]</v>
       </c>
       <c r="E124" t="str">
-        <v>❗ HREF Mismatch</v>
+        <v>OK</v>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="str">
-        <v>group-menu-chemistry</v>
+        <v>group-menu-financial-aid</v>
       </c>
       <c r="B125" t="str">
         <v>MENU</v>
       </c>
       <c r="C125" t="str">
-        <v>Department of Chemistry and Biochemistry                    [Menu ID: group-menu-chemistry]</v>
+        <v>Financial Aid                    [Menu ID: group-menu-financial-aid]</v>
       </c>
       <c r="D125" t="str">
-        <v>group-menu-chemistry                    [Term ID: 1577]</v>
+        <v>group-menu-financial-aid                    [Term ID: 1531]</v>
       </c>
       <c r="E125" t="str">
         <v>OK</v>
@@ -2526,33 +2526,33 @@
     </row>
     <row r="126">
       <c r="A126" t="str">
-        <v>group-menu-chemistry-stockroom</v>
+        <v>group-menu-first-year-institute</v>
       </c>
       <c r="B126" t="str">
         <v>MENU</v>
       </c>
       <c r="C126" t="str">
-        <v>Chemistry Stockroom                    [Menu ID: group-menu-chemistry-stockroom]</v>
+        <v>First Year Institute                    [Menu ID: group-menu-first-year-institute]</v>
       </c>
       <c r="D126" t="str">
-        <v>group-menu-chemistry-stockroom                    [Term ID: 1561]</v>
+        <v/>
       </c>
       <c r="E126" t="str">
-        <v>OK</v>
+        <v>Missing in WP</v>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="str">
-        <v>group-menu-cidd</v>
+        <v>group-menu-general-education</v>
       </c>
       <c r="B127" t="str">
         <v>MENU</v>
       </c>
       <c r="C127" t="str">
-        <v>Center for Integrative Learning                    [Menu ID: group-menu-cidd]</v>
+        <v>General Education                    [Menu ID: group-menu-general-education]</v>
       </c>
       <c r="D127" t="str">
-        <v>group-menu-cidd                    [Term ID: 1581]</v>
+        <v>group-menu-general-education                    [Term ID: 1656]</v>
       </c>
       <c r="E127" t="str">
         <v>OK</v>
@@ -2560,67 +2560,67 @@
     </row>
     <row r="128">
       <c r="A128" t="str">
-        <v>group-menu-cidd</v>
+        <v>group-menu-general-information</v>
       </c>
       <c r="B128" t="str">
-        <v>CHILD_HREF</v>
+        <v>MENU</v>
       </c>
       <c r="C128" t="str">
-        <v>https://portal.geneseo.sunycreate.cloud</v>
+        <v>Admissions                    [Menu ID: group-menu-general-information]</v>
       </c>
       <c r="D128" t="str">
-        <v/>
+        <v>group-menu-general-information                    [Term ID: 1558]</v>
       </c>
       <c r="E128" t="str">
-        <v>❗ HREF Mismatch</v>
+        <v>OK</v>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="str">
-        <v>group-menu-cidd</v>
+        <v>group-menu-geneseo-5k-race-walk</v>
       </c>
       <c r="B129" t="str">
-        <v>CHILD_HREF</v>
+        <v>MENU</v>
       </c>
       <c r="C129" t="str">
-        <v>/cil/ICM</v>
+        <v>Geneseo 5K Race/Walk                    [Menu ID: group-menu-geneseo-5k-race-walk]</v>
       </c>
       <c r="D129" t="str">
-        <v>/cil/icm</v>
+        <v/>
       </c>
       <c r="E129" t="str">
-        <v>❗ HREF Mismatch</v>
+        <v>Missing in WP</v>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="str">
-        <v>group-menu-cidd</v>
+        <v>group-menu-geneseo-area-gaming-g</v>
       </c>
       <c r="B130" t="str">
-        <v>CHILD_HREF</v>
+        <v>MENU</v>
       </c>
       <c r="C130" t="str">
-        <v>/IBHM</v>
+        <v>Geneseo Area Gaming Group                    [Menu ID: group-menu-geneseo-area-gaming-g]</v>
       </c>
       <c r="D130" t="str">
-        <v>/ibhm</v>
+        <v>group-menu-geneseo-area-gaming-g                    [Term ID: 1596]</v>
       </c>
       <c r="E130" t="str">
-        <v>❗ HREF Mismatch</v>
+        <v>OK</v>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="str">
-        <v>group-menu-cit</v>
+        <v>group-menu-geneseo-first-respons</v>
       </c>
       <c r="B131" t="str">
         <v>MENU</v>
       </c>
       <c r="C131" t="str">
-        <v>CIT                    [Menu ID: group-menu-cit]</v>
+        <v>Geneseo First Response                    [Menu ID: group-menu-geneseo-first-respons]</v>
       </c>
       <c r="D131" t="str">
-        <v>group-menu-cit                    [Term ID: 1715]</v>
+        <v>group-menu-geneseo-first-respons                    [Term ID: 1709]</v>
       </c>
       <c r="E131" t="str">
         <v>OK</v>
@@ -2628,13 +2628,13 @@
     </row>
     <row r="132">
       <c r="A132" t="str">
-        <v>group-menu-college-senate</v>
+        <v>group-menu-geneseo-food-project</v>
       </c>
       <c r="B132" t="str">
         <v>MENU</v>
       </c>
       <c r="C132" t="str">
-        <v>College Senate                    [Menu ID: group-menu-college-senate]</v>
+        <v>Geneseo Food Project                    [Menu ID: group-menu-geneseo-food-project]</v>
       </c>
       <c r="D132" t="str">
         <v/>
@@ -2645,67 +2645,67 @@
     </row>
     <row r="133">
       <c r="A133" t="str">
-        <v>group-menu-commencement</v>
+        <v>group-menu-geneseo-interfaith-se</v>
       </c>
       <c r="B133" t="str">
         <v>MENU</v>
       </c>
       <c r="C133" t="str">
-        <v>Commencement                    [Menu ID: group-menu-commencement]</v>
+        <v>Geneseo Interfaith Service Project                    [Menu ID: group-menu-geneseo-interfaith-se]</v>
       </c>
       <c r="D133" t="str">
-        <v>group-menu-commencement                    [Term ID: 1655]</v>
+        <v/>
       </c>
       <c r="E133" t="str">
-        <v>OK</v>
+        <v>Missing in WP</v>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="str">
-        <v>group-menu-commencement</v>
+        <v>group-menu-geneseo-marketing-ass</v>
       </c>
       <c r="B134" t="str">
-        <v>ITEM_HREF</v>
+        <v>MENU</v>
       </c>
       <c r="C134" t="str">
-        <v>/commencement/faculty-staff-RSVP-regalia-rental</v>
+        <v>Geneseo Marketing Assocation                    [Menu ID: group-menu-geneseo-marketing-ass]</v>
       </c>
       <c r="D134" t="str">
-        <v>/commencement/faculty-staff-rsvp-regalia-rental</v>
+        <v/>
       </c>
       <c r="E134" t="str">
-        <v>❗ HREF Mismatch</v>
+        <v>Missing in WP</v>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="str">
-        <v>group-menu-communication</v>
+        <v>group-menu-geneseo-organization-</v>
       </c>
       <c r="B135" t="str">
         <v>MENU</v>
       </c>
       <c r="C135" t="str">
-        <v>Communication                    [Menu ID: group-menu-communication]</v>
+        <v>Gestures: Organization for Deaf Awareness                    [Menu ID: group-menu-geneseo-organization-]</v>
       </c>
       <c r="D135" t="str">
-        <v>group-menu-communication                    [Term ID: 1554]</v>
+        <v/>
       </c>
       <c r="E135" t="str">
-        <v>OK</v>
+        <v>Missing in WP</v>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="str">
-        <v>group-menu-communications-market</v>
+        <v>group-menu-geography</v>
       </c>
       <c r="B136" t="str">
         <v>MENU</v>
       </c>
       <c r="C136" t="str">
-        <v>Communications and Marketing                    [Menu ID: group-menu-communications-market]</v>
+        <v>Geography and Sustainability Studies                    [Menu ID: group-menu-geography]</v>
       </c>
       <c r="D136" t="str">
-        <v>group-menu-communications-market                    [Term ID: 1707]</v>
+        <v>group-menu-geography                    [Term ID: 1578]</v>
       </c>
       <c r="E136" t="str">
         <v>OK</v>
@@ -2713,16 +2713,16 @@
     </row>
     <row r="137">
       <c r="A137" t="str">
-        <v>group-menu-community-resource-ne</v>
+        <v>group-menu-geography-club</v>
       </c>
       <c r="B137" t="str">
         <v>MENU</v>
       </c>
       <c r="C137" t="str">
-        <v>Community Resource Network                    [Menu ID: group-menu-community-resource-ne]</v>
+        <v>Geography Club                    [Menu ID: group-menu-geography-club]</v>
       </c>
       <c r="D137" t="str">
-        <v>group-menu-community-resource-ne                    [Term ID: 1733]</v>
+        <v>group-menu-geography-club                    [Term ID: 1675]</v>
       </c>
       <c r="E137" t="str">
         <v>OK</v>
@@ -2730,50 +2730,50 @@
     </row>
     <row r="138">
       <c r="A138" t="str">
-        <v>group-menu-community-resource-ne</v>
+        <v>group-menu-geological-sciences</v>
       </c>
       <c r="B138" t="str">
-        <v>ITEM_HREF</v>
+        <v>MENU</v>
       </c>
       <c r="C138" t="str">
-        <v>/crn/about-us</v>
+        <v>Geological, Environmental, and Planetary Sciences                    [Menu ID: group-menu-geological-sciences]</v>
       </c>
       <c r="D138" t="str">
-        <v>/about-us</v>
+        <v>group-menu-geological-sciences                    [Term ID: 1532]</v>
       </c>
       <c r="E138" t="str">
-        <v>❗ HREF Mismatch</v>
+        <v>OK</v>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="str">
-        <v>group-menu-community-resource-ne</v>
+        <v>group-menu-george-a-marcus</v>
       </c>
       <c r="B139" t="str">
-        <v>ITEM_HREF</v>
+        <v>MENU</v>
       </c>
       <c r="C139" t="str">
-        <v>/crn/membership</v>
+        <v>George A Marcus                    [Menu ID: group-menu-george-a-marcus]</v>
       </c>
       <c r="D139" t="str">
-        <v>/membership</v>
+        <v>group-menu-george-a-marcus                    [Term ID: 1681]</v>
       </c>
       <c r="E139" t="str">
-        <v>❗ HREF Mismatch</v>
+        <v>OK</v>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="str">
-        <v>group-menu-comparative-literatur</v>
+        <v>group-menu-gold-program</v>
       </c>
       <c r="B140" t="str">
         <v>MENU</v>
       </c>
       <c r="C140" t="str">
-        <v>Comparative Literature &amp; Literary Translation                    [Menu ID: group-menu-comparative-literatur]</v>
+        <v>GOLD Program                    [Menu ID: group-menu-gold-program]</v>
       </c>
       <c r="D140" t="str">
-        <v>group-menu-comparative-literatur                    [Term ID: 1693]</v>
+        <v>group-menu-gold-program                    [Term ID: 1714]</v>
       </c>
       <c r="E140" t="str">
         <v>OK</v>
@@ -2781,67 +2781,67 @@
     </row>
     <row r="141">
       <c r="A141" t="str">
-        <v>group-menu-comparative-literatur</v>
+        <v>group-menu-governance</v>
       </c>
       <c r="B141" t="str">
-        <v>ITEM_HREF</v>
+        <v>MENU</v>
       </c>
       <c r="C141" t="str">
-        <v>/CMLT</v>
+        <v>Governance                    [Menu ID: group-menu-governance]</v>
       </c>
       <c r="D141" t="str">
-        <v>/cmlt</v>
+        <v>group-menu-governance                    [Term ID: 1587]</v>
       </c>
       <c r="E141" t="str">
-        <v>❗ HREF Mismatch</v>
+        <v>OK</v>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="str">
-        <v>group-menu-comparative-literatur</v>
+        <v>group-menu-graduate-admissions</v>
       </c>
       <c r="B142" t="str">
-        <v>ITEM_HREF</v>
+        <v>MENU</v>
       </c>
       <c r="C142" t="str">
-        <v>/CMLT_Programs</v>
+        <v>Graduate Admissions                    [Menu ID: group-menu-graduate-admissions]</v>
       </c>
       <c r="D142" t="str">
-        <v>/cmlt_programs</v>
+        <v>group-menu-graduate-admissions                    [Term ID: 1711]</v>
       </c>
       <c r="E142" t="str">
-        <v>❗ HREF Mismatch</v>
+        <v>OK</v>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="str">
-        <v>group-menu-comparative-literatur</v>
+        <v>group-menu-grants-management</v>
       </c>
       <c r="B143" t="str">
-        <v>ITEM_HREF</v>
+        <v>MENU</v>
       </c>
       <c r="C143" t="str">
-        <v>/CMLT_Tracks</v>
+        <v>Grants Management - The Research Foundation                    [Menu ID: group-menu-grants-management]</v>
       </c>
       <c r="D143" t="str">
-        <v>/cmlt_tracks</v>
+        <v/>
       </c>
       <c r="E143" t="str">
-        <v>❗ HREF Mismatch</v>
+        <v>Missing in WP</v>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="str">
-        <v>group-menu-credit-union</v>
+        <v>group-menu-great-day</v>
       </c>
       <c r="B144" t="str">
         <v>MENU</v>
       </c>
       <c r="C144" t="str">
-        <v>Credit Union                    [Menu ID: group-menu-credit-union]</v>
+        <v>Great Day                    [Menu ID: group-menu-great-day]</v>
       </c>
       <c r="D144" t="str">
-        <v>group-menu-credit-union                    [Term ID: 1716]</v>
+        <v>group-menu-great-day                    [Term ID: 1547]</v>
       </c>
       <c r="E144" t="str">
         <v>OK</v>
@@ -2849,16 +2849,16 @@
     </row>
     <row r="145">
       <c r="A145" t="str">
-        <v>group-menu-crew</v>
+        <v>group-menu-greek-affairs</v>
       </c>
       <c r="B145" t="str">
         <v>MENU</v>
       </c>
       <c r="C145" t="str">
-        <v>Crew                    [Menu ID: group-menu-crew]</v>
+        <v>Greek Affairs                    [Menu ID: group-menu-greek-affairs]</v>
       </c>
       <c r="D145" t="str">
-        <v>group-menu-crew                    [Term ID: 1630]</v>
+        <v>group-menu-greek-affairs                    [Term ID: 1598]</v>
       </c>
       <c r="E145" t="str">
         <v>OK</v>
@@ -2866,16 +2866,16 @@
     </row>
     <row r="146">
       <c r="A146" t="str">
-        <v>group-menu-curriculum-and-assess</v>
+        <v>group-menu-grow-stem</v>
       </c>
       <c r="B146" t="str">
         <v>MENU</v>
       </c>
       <c r="C146" t="str">
-        <v>Curriculum                    [Menu ID: group-menu-curriculum-and-assess]</v>
+        <v>GROW STEM                    [Menu ID: group-menu-grow-stem]</v>
       </c>
       <c r="D146" t="str">
-        <v>group-menu-curriculum-and-assess                    [Term ID: 1609]</v>
+        <v>group-menu-grow-stem                    [Term ID: 1728]</v>
       </c>
       <c r="E146" t="str">
         <v>OK</v>
@@ -2883,13 +2883,13 @@
     </row>
     <row r="147">
       <c r="A147" t="str">
-        <v>group-menu-curriculum-and-assess</v>
+        <v>group-menu-habitat-for-humanity</v>
       </c>
       <c r="B147" t="str">
-        <v>CHILD_TITLE</v>
+        <v>MENU</v>
       </c>
       <c r="C147" t="str">
-        <v>SUNY Gen Ed Site</v>
+        <v>Habitat for Humanity                    [Menu ID: group-menu-habitat-for-humanity]</v>
       </c>
       <c r="D147" t="str">
         <v/>
@@ -2900,84 +2900,84 @@
     </row>
     <row r="148">
       <c r="A148" t="str">
-        <v>group-menu-curriculum-and-assess</v>
+        <v>group-menu-health-counseling</v>
       </c>
       <c r="B148" t="str">
-        <v>CHILD_HREF</v>
+        <v>MENU</v>
       </c>
       <c r="C148" t="str">
-        <v>https://system.suny.edu/academic-affairs/acaproplan/general-education/suny-ge</v>
+        <v>SHC Home                    [Menu ID: group-menu-health-counseling]</v>
       </c>
       <c r="D148" t="str">
-        <v/>
+        <v>group-menu-health-counseling                    [Term ID: 1546]</v>
       </c>
       <c r="E148" t="str">
-        <v>Missing in WP</v>
+        <v>OK</v>
       </c>
     </row>
     <row r="149">
       <c r="A149" t="str">
-        <v>group-menu-dance-at-geneseo</v>
+        <v>group-menu-hillel-</v>
       </c>
       <c r="B149" t="str">
         <v>MENU</v>
       </c>
       <c r="C149" t="str">
-        <v>Dance at Geneseo                    [Menu ID: group-menu-dance-at-geneseo]</v>
+        <v>Hillel                     [Menu ID: group-menu-hillel-]</v>
       </c>
       <c r="D149" t="str">
-        <v/>
+        <v>group-menu-hillel-                    [Term ID: 1724]</v>
       </c>
       <c r="E149" t="str">
-        <v>Missing in WP</v>
+        <v>OK</v>
       </c>
     </row>
     <row r="150">
       <c r="A150" t="str">
-        <v>group-menu-david-geiger</v>
+        <v>group-menu-hippies-for-hope</v>
       </c>
       <c r="B150" t="str">
         <v>MENU</v>
       </c>
       <c r="C150" t="str">
-        <v>David Geiger                    [Menu ID: group-menu-david-geiger]</v>
+        <v>Hippies for Hope                    [Menu ID: group-menu-hippies-for-hope]</v>
       </c>
       <c r="D150" t="str">
-        <v>group-menu-david-geiger                    [Term ID: 1679]</v>
+        <v/>
       </c>
       <c r="E150" t="str">
-        <v>OK</v>
+        <v>Missing in WP</v>
       </c>
     </row>
     <row r="151">
       <c r="A151" t="str">
-        <v>group-menu-david-geiger</v>
+        <v>group-menu-history</v>
       </c>
       <c r="B151" t="str">
-        <v>ITEM_HREF</v>
+        <v>MENU</v>
       </c>
       <c r="C151" t="str">
-        <v>http://geneseo.edu/geiger</v>
+        <v>History                    [Menu ID: group-menu-history]</v>
       </c>
       <c r="D151" t="str">
-        <v>/geiger</v>
+        <v>group-menu-history                    [Term ID: 1593]</v>
       </c>
       <c r="E151" t="str">
-        <v>❗ HREF Mismatch</v>
+        <v>OK</v>
       </c>
     </row>
     <row r="152">
       <c r="A152" t="str">
-        <v>group-menu-dean-of-students</v>
+        <v>group-menu-homecoming</v>
       </c>
       <c r="B152" t="str">
         <v>MENU</v>
       </c>
       <c r="C152" t="str">
-        <v>Dean of Students                    [Menu ID: group-menu-dean-of-students]</v>
+        <v>Family Weekend                    [Menu ID: group-menu-homecoming]</v>
       </c>
       <c r="D152" t="str">
-        <v>group-menu-dean-of-students                    [Term ID: 1674]</v>
+        <v>group-menu-homecoming                    [Term ID: 1671]</v>
       </c>
       <c r="E152" t="str">
         <v>OK</v>
@@ -2985,33 +2985,33 @@
     </row>
     <row r="153">
       <c r="A153" t="str">
-        <v>group-menu-dean-of-students</v>
+        <v>group-menu-human-resources</v>
       </c>
       <c r="B153" t="str">
-        <v>ITEM_HREF</v>
+        <v>MENU</v>
       </c>
       <c r="C153" t="str">
-        <v>/sites/default/files/documents/ILOA.pdf</v>
+        <v>Human Resources &amp; Payroll Services                    [Menu ID: group-menu-human-resources]</v>
       </c>
       <c r="D153" t="str">
-        <v>/wp-content/uploads/2025/11/ILOA.pdf</v>
+        <v>group-menu-human-resources                    [Term ID: 1538]</v>
       </c>
       <c r="E153" t="str">
-        <v>❗ HREF Mismatch</v>
+        <v>OK</v>
       </c>
     </row>
     <row r="154">
       <c r="A154" t="str">
-        <v>group-menu-dennis-showers</v>
+        <v>group-menu-incoming-exchange-stu</v>
       </c>
       <c r="B154" t="str">
         <v>MENU</v>
       </c>
       <c r="C154" t="str">
-        <v>Dennis Showers                    [Menu ID: group-menu-dennis-showers]</v>
+        <v>Incoming Exchange Students                    [Menu ID: group-menu-incoming-exchange-stu]</v>
       </c>
       <c r="D154" t="str">
-        <v>group-menu-dennis-showers                    [Term ID: 1683]</v>
+        <v>group-menu-incoming-exchange-stu                    [Term ID: 1718]</v>
       </c>
       <c r="E154" t="str">
         <v>OK</v>
@@ -3019,13 +3019,13 @@
     </row>
     <row r="155">
       <c r="A155" t="str">
-        <v>group-menu-department-of-music</v>
+        <v>group-menu-information-security-</v>
       </c>
       <c r="B155" t="str">
         <v>MENU</v>
       </c>
       <c r="C155" t="str">
-        <v>Department of Music &amp; Musical Theatre                    [Menu ID: group-menu-department-of-music]</v>
+        <v>Information Security Program                    [Menu ID: group-menu-information-security-]</v>
       </c>
       <c r="D155" t="str">
         <v/>
@@ -3036,16 +3036,16 @@
     </row>
     <row r="156">
       <c r="A156" t="str">
-        <v>group-menu-diasporas-of-color-un</v>
+        <v>group-menu-insomnia-film-festiva</v>
       </c>
       <c r="B156" t="str">
         <v>MENU</v>
       </c>
       <c r="C156" t="str">
-        <v>Diasporas of Color Undergraduate                     [Menu ID: group-menu-diasporas-of-color-un]</v>
+        <v>Insomnia Film Festival                    [Menu ID: group-menu-insomnia-film-festiva]</v>
       </c>
       <c r="D156" t="str">
-        <v>group-menu-diasporas-of-color-un                    [Term ID: 1661]</v>
+        <v>group-menu-insomnia-film-festiva                    [Term ID: 1720]</v>
       </c>
       <c r="E156" t="str">
         <v>OK</v>
@@ -3053,84 +3053,84 @@
     </row>
     <row r="157">
       <c r="A157" t="str">
-        <v>group-menu-diasporas-of-color-un</v>
+        <v>group-menu-institutional-researc</v>
       </c>
       <c r="B157" t="str">
-        <v>ITEM_HREF</v>
+        <v>MENU</v>
       </c>
       <c r="C157" t="str">
-        <v>/sites/default/files/sites/diasporas_of_color_conference/PosterGuidelinesAsOf-11-16-13.pdf</v>
+        <v>Institutional Research &amp; Effectiveness                    [Menu ID: group-menu-institutional-researc]</v>
       </c>
       <c r="D157" t="str">
-        <v>/wp-content/uploads/2025/11/PosterGuidelinesAsOf-11-16-13.pdf</v>
+        <v>group-menu-institutional-researc                    [Term ID: 1670]</v>
       </c>
       <c r="E157" t="str">
-        <v>❗ HREF Mismatch</v>
+        <v>OK</v>
       </c>
     </row>
     <row r="158">
       <c r="A158" t="str">
-        <v>group-menu-diasporas-of-color-un</v>
+        <v>group-menu-inter-greek-council</v>
       </c>
       <c r="B158" t="str">
-        <v>ITEM_HREF</v>
+        <v>MENU</v>
       </c>
       <c r="C158" t="str">
-        <v>/sites/default/files/sites/diasporas_of_color_conference/Lodging%20Options.pdf</v>
+        <v>Inter Greek Council                    [Menu ID: group-menu-inter-greek-council]</v>
       </c>
       <c r="D158" t="str">
-        <v>/wp-content/uploads/2025/11/Lodging-Options.pdf</v>
+        <v>group-menu-inter-greek-council                    [Term ID: 1576]</v>
       </c>
       <c r="E158" t="str">
-        <v>❗ HREF Mismatch</v>
+        <v>OK</v>
       </c>
     </row>
     <row r="159">
       <c r="A159" t="str">
-        <v>group-menu-diasporas-of-color-un</v>
+        <v>group-menu-interfaith-center</v>
       </c>
       <c r="B159" t="str">
-        <v>ITEM_HREF</v>
+        <v>MENU</v>
       </c>
       <c r="C159" t="str">
-        <v>/sites/default/files/sites/diasporas_of_color_conference/POSTER%20for%20PUBLICITY.pdf</v>
+        <v>Interfaith Center                    [Menu ID: group-menu-interfaith-center]</v>
       </c>
       <c r="D159" t="str">
-        <v>/wp-content/uploads/2025/11/POSTER-for-PUBLICITY.pdf</v>
+        <v/>
       </c>
       <c r="E159" t="str">
-        <v>❗ HREF Mismatch</v>
+        <v>Missing in WP</v>
       </c>
     </row>
     <row r="160">
       <c r="A160" t="str">
-        <v>group-menu-discovery-cafe</v>
+        <v>group-menu-internal-controls</v>
       </c>
       <c r="B160" t="str">
         <v>MENU</v>
       </c>
       <c r="C160" t="str">
-        <v>Discovery Cafe                    [Menu ID: group-menu-discovery-cafe]</v>
+        <v>Internal Controls                    [Menu ID: group-menu-internal-controls]</v>
       </c>
       <c r="D160" t="str">
-        <v/>
+        <v>group-menu-internal-controls                    [Term ID: 1643]</v>
       </c>
       <c r="E160" t="str">
-        <v>Missing in WP</v>
+        <v>OK</v>
       </c>
     </row>
     <row r="161">
       <c r="A161" t="str">
-        <v>group-menu-diversity-at-geneseo</v>
+        <v>group-menu-intramural-sports</v>
       </c>
       <c r="B161" t="str">
         <v>MENU</v>
       </c>
       <c r="C161" t="str">
-        <v>Diversity at Geneseo                    [Menu ID: group-menu-diversity-at-geneseo]</v>
+        <v>Intramural Sports                    [Menu ID: group-menu-intramural-sports]</v>
       </c>
       <c r="D161" t="str">
-        <v>group-menu-diversity-at-geneseo                    [Term ID: 1551]</v>
+        <v>group-menu-intramural-sports                    [Term ID: 1644]</v>
       </c>
       <c r="E161" t="str">
         <v>OK</v>
@@ -3138,16 +3138,16 @@
     </row>
     <row r="162">
       <c r="A162" t="str">
-        <v>group-menu-dr-kokjo-adabra</v>
+        <v>group-menu-isss</v>
       </c>
       <c r="B162" t="str">
         <v>MENU</v>
       </c>
       <c r="C162" t="str">
-        <v>Dr. Kodjo Adabra                    [Menu ID: group-menu-dr-kokjo-adabra]</v>
+        <v>International Student &amp; Scholar Services                    [Menu ID: group-menu-isss]</v>
       </c>
       <c r="D162" t="str">
-        <v>group-menu-dr-kokjo-adabra                    [Term ID: 1712]</v>
+        <v>group-menu-isss                    [Term ID: 1548]</v>
       </c>
       <c r="E162" t="str">
         <v>OK</v>
@@ -3155,169 +3155,169 @@
     </row>
     <row r="163">
       <c r="A163" t="str">
-        <v>group-menu-dr-kokjo-adabra</v>
+        <v>group-menu-jennifer-apple</v>
       </c>
       <c r="B163" t="str">
-        <v>ITEM_HREF</v>
+        <v>MENU</v>
       </c>
       <c r="C163" t="str">
-        <v>/adabra/Teaching-experience</v>
+        <v>Jennifer Apple                    [Menu ID: group-menu-jennifer-apple]</v>
       </c>
       <c r="D163" t="str">
-        <v>/adabra/teaching-experience</v>
+        <v/>
       </c>
       <c r="E163" t="str">
-        <v>❗ HREF Mismatch</v>
+        <v>Missing in WP</v>
       </c>
     </row>
     <row r="164">
       <c r="A164" t="str">
-        <v>group-menu-dr-shuo-chen</v>
+        <v>group-menu-joe-dolce</v>
       </c>
       <c r="B164" t="str">
         <v>MENU</v>
       </c>
       <c r="C164" t="str">
-        <v>Dr. Shuo Chen                    [Menu ID: group-menu-dr-shuo-chen]</v>
+        <v>Joe Dolce                    [Menu ID: group-menu-joe-dolce]</v>
       </c>
       <c r="D164" t="str">
-        <v/>
+        <v>group-menu-joe-dolce                    [Term ID: 1702]</v>
       </c>
       <c r="E164" t="str">
-        <v>Missing in WP</v>
+        <v>OK</v>
       </c>
     </row>
     <row r="165">
       <c r="A165" t="str">
-        <v>group-menu-duplicating-center</v>
+        <v>group-menu-kappa-sigma</v>
       </c>
       <c r="B165" t="str">
         <v>MENU</v>
       </c>
       <c r="C165" t="str">
-        <v>Duplicating Center                    [Menu ID: group-menu-duplicating-center]</v>
+        <v>Kappa Sigma                    [Menu ID: group-menu-kappa-sigma]</v>
       </c>
       <c r="D165" t="str">
-        <v>group-menu-duplicating-center                    [Term ID: 1566]</v>
+        <v/>
       </c>
       <c r="E165" t="str">
-        <v>OK</v>
+        <v>Missing in WP</v>
       </c>
     </row>
     <row r="166">
       <c r="A166" t="str">
-        <v>group-menu-ed-beary</v>
+        <v>group-menu-knighline</v>
       </c>
       <c r="B166" t="str">
         <v>MENU</v>
       </c>
       <c r="C166" t="str">
-        <v>Ed Beary                    [Menu ID: group-menu-ed-beary]</v>
+        <v>Geneseo Knightline Dance Team                    [Menu ID: group-menu-knighline]</v>
       </c>
       <c r="D166" t="str">
-        <v/>
+        <v>group-menu-knighline                    [Term ID: 1615]</v>
       </c>
       <c r="E166" t="str">
-        <v>Missing in WP</v>
+        <v>OK</v>
       </c>
     </row>
     <row r="167">
       <c r="A167" t="str">
-        <v>group-menu-ed-pogozelski</v>
+        <v>group-menu-kurt-fletcher</v>
       </c>
       <c r="B167" t="str">
         <v>MENU</v>
       </c>
       <c r="C167" t="str">
-        <v>Ed Pogozelski                    [Menu ID: group-menu-ed-pogozelski]</v>
+        <v>Kurt Fletcher                    [Menu ID: group-menu-kurt-fletcher]</v>
       </c>
       <c r="D167" t="str">
-        <v/>
+        <v>group-menu-kurt-fletcher                    [Term ID: 1678]</v>
       </c>
       <c r="E167" t="str">
-        <v>Missing in WP</v>
+        <v>OK</v>
       </c>
     </row>
     <row r="168">
       <c r="A168" t="str">
-        <v>group-menu-edgar-fellows-program</v>
+        <v>group-menu-kurt-fletcher</v>
       </c>
       <c r="B168" t="str">
-        <v>MENU</v>
+        <v>ITEM_TITLE</v>
       </c>
       <c r="C168" t="str">
-        <v>Edgar Fellows Program                    [Menu ID: group-menu-edgar-fellows-program]</v>
+        <v>Vita</v>
       </c>
       <c r="D168" t="str">
-        <v>group-menu-edgar-fellows-program                    [Term ID: 1688]</v>
+        <v/>
       </c>
       <c r="E168" t="str">
-        <v>OK</v>
+        <v>Missing in WP</v>
       </c>
     </row>
     <row r="169">
       <c r="A169" t="str">
-        <v>group-menu-emergencies</v>
+        <v>group-menu-kurt-fletcher</v>
       </c>
       <c r="B169" t="str">
-        <v>MENU</v>
+        <v>ITEM_HREF</v>
       </c>
       <c r="C169" t="str">
-        <v>Emergencies                    [Menu ID: group-menu-emergencies]</v>
+        <v>/sites/default/files/sites/fletcher/RESUME.pdf</v>
       </c>
       <c r="D169" t="str">
-        <v>group-menu-emergencies                    [Term ID: 1569]</v>
+        <v/>
       </c>
       <c r="E169" t="str">
-        <v>OK</v>
+        <v>Missing in WP</v>
       </c>
     </row>
     <row r="170">
       <c r="A170" t="str">
-        <v>group-menu-emergency</v>
+        <v>group-menu-languages-literatures</v>
       </c>
       <c r="B170" t="str">
         <v>MENU</v>
       </c>
       <c r="C170" t="str">
-        <v>Emergency                    [Menu ID: group-menu-emergency]</v>
+        <v>Global Languages and Cultures                    [Menu ID: group-menu-languages-literatures]</v>
       </c>
       <c r="D170" t="str">
-        <v/>
+        <v>group-menu-languages-literatures                    [Term ID: 1579]</v>
       </c>
       <c r="E170" t="str">
-        <v>Missing in WP</v>
+        <v>OK</v>
       </c>
     </row>
     <row r="171">
       <c r="A171" t="str">
-        <v>group-menu-employee-assistance</v>
+        <v>group-menu-latin-american-studie</v>
       </c>
       <c r="B171" t="str">
         <v>MENU</v>
       </c>
       <c r="C171" t="str">
-        <v>Employee Assistance                    [Menu ID: group-menu-employee-assistance]</v>
+        <v>Latin American &amp; Caribbean Studies                    [Menu ID: group-menu-latin-american-studie]</v>
       </c>
       <c r="D171" t="str">
-        <v/>
+        <v>group-menu-latin-american-studie                    [Term ID: 1543]</v>
       </c>
       <c r="E171" t="str">
-        <v>Missing in WP</v>
+        <v>OK</v>
       </c>
     </row>
     <row r="172">
       <c r="A172" t="str">
-        <v>group-menu-english</v>
+        <v>group-menu-lgbtq</v>
       </c>
       <c r="B172" t="str">
         <v>MENU</v>
       </c>
       <c r="C172" t="str">
-        <v>English                    [Menu ID: group-menu-english]</v>
+        <v>Office of LGBTQ+ Life                    [Menu ID: group-menu-lgbtq]</v>
       </c>
       <c r="D172" t="str">
-        <v>group-menu-english                    [Term ID: 1564]</v>
+        <v>group-menu-lgbtq                    [Term ID: 1735]</v>
       </c>
       <c r="E172" t="str">
         <v>OK</v>
@@ -3325,16 +3325,16 @@
     </row>
     <row r="173">
       <c r="A173" t="str">
-        <v>group-menu-english-for-speakers-</v>
+        <v>group-menu-linda-ware-ph-d-</v>
       </c>
       <c r="B173" t="str">
         <v>MENU</v>
       </c>
       <c r="C173" t="str">
-        <v>English for Speakers of Other Languages                    [Menu ID: group-menu-english-for-speakers-]</v>
+        <v>Linda Ware Ph.D.                    [Menu ID: group-menu-linda-ware-ph-d-]</v>
       </c>
       <c r="D173" t="str">
-        <v>group-menu-english-for-speakers-                    [Term ID: 1742]</v>
+        <v>group-menu-linda-ware-ph-d-                    [Term ID: 1621]</v>
       </c>
       <c r="E173" t="str">
         <v>OK</v>
@@ -3342,16 +3342,16 @@
     </row>
     <row r="174">
       <c r="A174" t="str">
-        <v>group-menu-environmental-health-</v>
+        <v>group-menu-linguistics-minor</v>
       </c>
       <c r="B174" t="str">
         <v>MENU</v>
       </c>
       <c r="C174" t="str">
-        <v>Environmental Health &amp; Safety                    [Menu ID: group-menu-environmental-health-]</v>
+        <v>Linguistics Minor                    [Menu ID: group-menu-linguistics-minor]</v>
       </c>
       <c r="D174" t="str">
-        <v>group-menu-environmental-health-                    [Term ID: 1708]</v>
+        <v>group-menu-linguistics-minor                    [Term ID: 1719]</v>
       </c>
       <c r="E174" t="str">
         <v>OK</v>
@@ -3359,13 +3359,13 @@
     </row>
     <row r="175">
       <c r="A175" t="str">
-        <v>group-menu-externship-program</v>
+        <v>group-menu-livingston-cares</v>
       </c>
       <c r="B175" t="str">
         <v>MENU</v>
       </c>
       <c r="C175" t="str">
-        <v>Externship Program                    [Menu ID: group-menu-externship-program]</v>
+        <v>Livingston Cares                    [Menu ID: group-menu-livingston-cares]</v>
       </c>
       <c r="D175" t="str">
         <v/>
@@ -3376,16 +3376,16 @@
     </row>
     <row r="176">
       <c r="A176" t="str">
-        <v>group-menu-facilities-planning</v>
+        <v>group-menu-mail-services</v>
       </c>
       <c r="B176" t="str">
         <v>MENU</v>
       </c>
       <c r="C176" t="str">
-        <v>Planning &amp; Construction                    [Menu ID: group-menu-facilities-planning]</v>
+        <v>Mail Services                    [Menu ID: group-menu-mail-services]</v>
       </c>
       <c r="D176" t="str">
-        <v>group-menu-facilities-planning                    [Term ID: 1642]</v>
+        <v>group-menu-mail-services                    [Term ID: 1657]</v>
       </c>
       <c r="E176" t="str">
         <v>OK</v>
@@ -3393,50 +3393,50 @@
     </row>
     <row r="177">
       <c r="A177" t="str">
-        <v>group-menu-facilities-services</v>
+        <v>group-menu-make-your-mark</v>
       </c>
       <c r="B177" t="str">
         <v>MENU</v>
       </c>
       <c r="C177" t="str">
-        <v>Facilities Services                    [Menu ID: group-menu-facilities-services]</v>
+        <v>Make Your Mark                    [Menu ID: group-menu-make-your-mark]</v>
       </c>
       <c r="D177" t="str">
-        <v>group-menu-facilities-services                    [Term ID: 1549]</v>
+        <v/>
       </c>
       <c r="E177" t="str">
-        <v>OK</v>
+        <v>Missing in WP</v>
       </c>
     </row>
     <row r="178">
       <c r="A178" t="str">
-        <v>group-menu-faculty-and-staff</v>
+        <v>group-menu-maria-h-lima</v>
       </c>
       <c r="B178" t="str">
         <v>MENU</v>
       </c>
       <c r="C178" t="str">
-        <v>Employees                    [Menu ID: group-menu-faculty-and-staff]</v>
+        <v>Maria H. Lima                    [Menu ID: group-menu-maria-h-lima]</v>
       </c>
       <c r="D178" t="str">
-        <v>group-menu-faculty-and-staff                    [Term ID: 1705]</v>
+        <v/>
       </c>
       <c r="E178" t="str">
-        <v>OK</v>
+        <v>Missing in WP</v>
       </c>
     </row>
     <row r="179">
       <c r="A179" t="str">
-        <v>group-menu-fellowships-scholarsh</v>
+        <v>group-menu-master-teacher</v>
       </c>
       <c r="B179" t="str">
         <v>MENU</v>
       </c>
       <c r="C179" t="str">
-        <v>Fellowships &amp; Scholarships                    [Menu ID: group-menu-fellowships-scholarsh]</v>
+        <v>Master Teacher                    [Menu ID: group-menu-master-teacher]</v>
       </c>
       <c r="D179" t="str">
-        <v>group-menu-fellowships-scholarsh                    [Term ID: 1659]</v>
+        <v>group-menu-master-teacher                    [Term ID: 1663]</v>
       </c>
       <c r="E179" t="str">
         <v>OK</v>
@@ -3444,101 +3444,101 @@
     </row>
     <row r="180">
       <c r="A180" t="str">
-        <v>group-menu-fellowships-scholarsh</v>
+        <v>group-menu-mathematics</v>
       </c>
       <c r="B180" t="str">
-        <v>ITEM_HREF</v>
+        <v>MENU</v>
       </c>
       <c r="C180" t="str">
-        <v>/fellowships_and_scholarships/FellowshipScholarshipInternational</v>
+        <v>Mathematics                    [Menu ID: group-menu-mathematics]</v>
       </c>
       <c r="D180" t="str">
-        <v>/fellowships_and_scholarships/fellowshipscholarshipinternational</v>
+        <v>group-menu-mathematics                    [Term ID: 1553]</v>
       </c>
       <c r="E180" t="str">
-        <v>❗ HREF Mismatch</v>
+        <v>OK</v>
       </c>
     </row>
     <row r="181">
       <c r="A181" t="str">
-        <v>group-menu-fellowships-scholarsh</v>
+        <v>group-menu-michael-teres</v>
       </c>
       <c r="B181" t="str">
-        <v>ITEM_HREF</v>
+        <v>MENU</v>
       </c>
       <c r="C181" t="str">
-        <v>/fellowships_and_scholarships/FellowshipScholarshipHints</v>
+        <v>Michael Teres                    [Menu ID: group-menu-michael-teres]</v>
       </c>
       <c r="D181" t="str">
-        <v>/fellowships_and_scholarships/fellowshipscholarshiphints</v>
+        <v/>
       </c>
       <c r="E181" t="str">
-        <v>❗ HREF Mismatch</v>
+        <v>Missing in WP</v>
       </c>
     </row>
     <row r="182">
       <c r="A182" t="str">
-        <v>group-menu-fellowships-scholarsh</v>
+        <v>group-menu-migration-and-electio</v>
       </c>
       <c r="B182" t="str">
-        <v>ITEM_HREF</v>
+        <v>MENU</v>
       </c>
       <c r="C182" t="str">
-        <v>/fellowships_and_scholarships/RecentRecipients</v>
+        <v>Migration and Elections Databa                    [Menu ID: group-menu-migration-and-electio]</v>
       </c>
       <c r="D182" t="str">
-        <v>/fellowships_and_scholarships/recentrecipients</v>
+        <v/>
       </c>
       <c r="E182" t="str">
-        <v>❗ HREF Mismatch</v>
+        <v>Missing in WP</v>
       </c>
     </row>
     <row r="183">
       <c r="A183" t="str">
-        <v>group-menu-financial-aid</v>
+        <v>group-menu-miles</v>
       </c>
       <c r="B183" t="str">
         <v>MENU</v>
       </c>
       <c r="C183" t="str">
-        <v>Financial Aid                    [Menu ID: group-menu-financial-aid]</v>
+        <v>MILES                    [Menu ID: group-menu-miles]</v>
       </c>
       <c r="D183" t="str">
-        <v>group-menu-financial-aid                    [Term ID: 1531]</v>
+        <v/>
       </c>
       <c r="E183" t="str">
-        <v>OK</v>
+        <v>Missing in WP</v>
       </c>
     </row>
     <row r="184">
       <c r="A184" t="str">
-        <v>group-menu-first-year-institute</v>
+        <v>group-menu-milne-library</v>
       </c>
       <c r="B184" t="str">
         <v>MENU</v>
       </c>
       <c r="C184" t="str">
-        <v>First Year Institute                    [Menu ID: group-menu-first-year-institute]</v>
+        <v>Fraser Hall Library                    [Menu ID: group-menu-milne-library]</v>
       </c>
       <c r="D184" t="str">
-        <v/>
+        <v>group-menu-milne-library                    [Term ID: 1703]</v>
       </c>
       <c r="E184" t="str">
-        <v>Missing in WP</v>
+        <v>OK</v>
       </c>
     </row>
     <row r="185">
       <c r="A185" t="str">
-        <v>group-menu-general-education</v>
+        <v>group-menu-ming-mei-chang</v>
       </c>
       <c r="B185" t="str">
         <v>MENU</v>
       </c>
       <c r="C185" t="str">
-        <v>General Education                    [Menu ID: group-menu-general-education]</v>
+        <v>Ming-Mei Chang                    [Menu ID: group-menu-ming-mei-chang]</v>
       </c>
       <c r="D185" t="str">
-        <v>group-menu-general-education                    [Term ID: 1656]</v>
+        <v>group-menu-ming-mei-chang                    [Term ID: 1677]</v>
       </c>
       <c r="E185" t="str">
         <v>OK</v>
@@ -3546,30 +3546,30 @@
     </row>
     <row r="186">
       <c r="A186" t="str">
-        <v>group-menu-general-information</v>
+        <v>group-menu-minority-association-</v>
       </c>
       <c r="B186" t="str">
         <v>MENU</v>
       </c>
       <c r="C186" t="str">
-        <v>Admissions                    [Menu ID: group-menu-general-information]</v>
+        <v>Minority Association for PreHealth                    [Menu ID: group-menu-minority-association-]</v>
       </c>
       <c r="D186" t="str">
-        <v>group-menu-general-information                    [Term ID: 1558]</v>
+        <v/>
       </c>
       <c r="E186" t="str">
-        <v>OK</v>
+        <v>Missing in WP</v>
       </c>
     </row>
     <row r="187">
       <c r="A187" t="str">
-        <v>group-menu-geneseo-5k-race-walk</v>
+        <v>group-menu-mlk</v>
       </c>
       <c r="B187" t="str">
         <v>MENU</v>
       </c>
       <c r="C187" t="str">
-        <v>Geneseo 5K Race/Walk                    [Menu ID: group-menu-geneseo-5k-race-walk]</v>
+        <v>mlk                    [Menu ID: group-menu-mlk]</v>
       </c>
       <c r="D187" t="str">
         <v/>
@@ -3580,16 +3580,16 @@
     </row>
     <row r="188">
       <c r="A188" t="str">
-        <v>group-menu-geneseo-area-gaming-g</v>
+        <v>group-menu-msche-accreditation</v>
       </c>
       <c r="B188" t="str">
         <v>MENU</v>
       </c>
       <c r="C188" t="str">
-        <v>Geneseo Area Gaming Group                    [Menu ID: group-menu-geneseo-area-gaming-g]</v>
+        <v>MSCHE Accreditation                    [Menu ID: group-menu-msche-accreditation]</v>
       </c>
       <c r="D188" t="str">
-        <v>group-menu-geneseo-area-gaming-g                    [Term ID: 1596]</v>
+        <v>group-menu-msche-accreditation                    [Term ID: 1731]</v>
       </c>
       <c r="E188" t="str">
         <v>OK</v>
@@ -3597,16 +3597,16 @@
     </row>
     <row r="189">
       <c r="A189" t="str">
-        <v>group-menu-geneseo-first-respons</v>
+        <v>group-menu-multicultural-program</v>
       </c>
       <c r="B189" t="str">
         <v>MENU</v>
       </c>
       <c r="C189" t="str">
-        <v>Geneseo First Response                    [Menu ID: group-menu-geneseo-first-respons]</v>
+        <v>Multicultural Affairs                    [Menu ID: group-menu-multicultural-program]</v>
       </c>
       <c r="D189" t="str">
-        <v>group-menu-geneseo-first-respons                    [Term ID: 1709]</v>
+        <v>group-menu-multicultural-program                    [Term ID: 1550]</v>
       </c>
       <c r="E189" t="str">
         <v>OK</v>
@@ -3614,84 +3614,84 @@
     </row>
     <row r="190">
       <c r="A190" t="str">
-        <v>group-menu-geneseo-food-project</v>
+        <v>group-menu-mycourses</v>
       </c>
       <c r="B190" t="str">
         <v>MENU</v>
       </c>
       <c r="C190" t="str">
-        <v>Geneseo Food Project                    [Menu ID: group-menu-geneseo-food-project]</v>
+        <v>myCourses                    [Menu ID: group-menu-mycourses]</v>
       </c>
       <c r="D190" t="str">
-        <v/>
+        <v>group-menu-mycourses                    [Term ID: 1611]</v>
       </c>
       <c r="E190" t="str">
-        <v>Missing in WP</v>
+        <v>OK</v>
       </c>
     </row>
     <row r="191">
       <c r="A191" t="str">
-        <v>group-menu-geneseo-interfaith-se</v>
+        <v>group-menu-native-american-studi</v>
       </c>
       <c r="B191" t="str">
         <v>MENU</v>
       </c>
       <c r="C191" t="str">
-        <v>Geneseo Interfaith Service Project                    [Menu ID: group-menu-geneseo-interfaith-se]</v>
+        <v>Native American Studies                    [Menu ID: group-menu-native-american-studi]</v>
       </c>
       <c r="D191" t="str">
-        <v/>
+        <v>group-menu-native-american-studi                    [Term ID: 1692]</v>
       </c>
       <c r="E191" t="str">
-        <v>Missing in WP</v>
+        <v>OK</v>
       </c>
     </row>
     <row r="192">
       <c r="A192" t="str">
-        <v>group-menu-geneseo-marketing-ass</v>
+        <v>group-menu-ncate</v>
       </c>
       <c r="B192" t="str">
         <v>MENU</v>
       </c>
       <c r="C192" t="str">
-        <v>Geneseo Marketing Assocation                    [Menu ID: group-menu-geneseo-marketing-ass]</v>
+        <v>CAEP Accreditation                    [Menu ID: group-menu-ncate]</v>
       </c>
       <c r="D192" t="str">
-        <v/>
+        <v>group-menu-ncate                    [Term ID: 1673]</v>
       </c>
       <c r="E192" t="str">
-        <v>Missing in WP</v>
+        <v>OK</v>
       </c>
     </row>
     <row r="193">
       <c r="A193" t="str">
-        <v>group-menu-geneseo-organization-</v>
+        <v>group-menu-neh-seminar</v>
       </c>
       <c r="B193" t="str">
         <v>MENU</v>
       </c>
       <c r="C193" t="str">
-        <v>Gestures: Organization for Deaf Awareness                    [Menu ID: group-menu-geneseo-organization-]</v>
+        <v>NEH Seminar                    [Menu ID: group-menu-neh-seminar]</v>
       </c>
       <c r="D193" t="str">
-        <v/>
+        <v>group-menu-neh-seminar                    [Term ID: 1620]</v>
       </c>
       <c r="E193" t="str">
-        <v>Missing in WP</v>
+        <v>OK</v>
       </c>
     </row>
     <row r="194">
       <c r="A194" t="str">
-        <v>group-menu-geography</v>
+        <v>group-menu-neuroscience</v>
       </c>
       <c r="B194" t="str">
         <v>MENU</v>
       </c>
       <c r="C194" t="str">
-        <v>Geography and Sustainability Studies                    [Menu ID: group-menu-geography]</v>
+        <v>Neuroscience                    [Menu ID: group-menu-neuroscience]</v>
       </c>
       <c r="D194" t="str">
-        <v>group-menu-geography                    [Term ID: 1578]</v>
+        <v>group-menu-neuroscience                    [Term ID: 1687]</v>
       </c>
       <c r="E194" t="str">
         <v>OK</v>
@@ -3699,101 +3699,101 @@
     </row>
     <row r="195">
       <c r="A195" t="str">
-        <v>group-menu-geography</v>
+        <v>group-menu-new-student-programs</v>
       </c>
       <c r="B195" t="str">
-        <v>CHILD_HREF</v>
+        <v>MENU</v>
       </c>
       <c r="C195" t="str">
-        <v>/node/6664</v>
+        <v>More Information                     [Menu ID: group-menu-new-student-programs]</v>
       </c>
       <c r="D195" t="str">
-        <v>/geography-and-sustainability-career-information</v>
+        <v/>
       </c>
       <c r="E195" t="str">
-        <v>❗ HREF Mismatch</v>
+        <v>Missing in WP</v>
       </c>
     </row>
     <row r="196">
       <c r="A196" t="str">
-        <v>group-menu-geography</v>
+        <v>group-menu-noyce-scholarship-pro</v>
       </c>
       <c r="B196" t="str">
-        <v>SUBCHILD_HREF</v>
+        <v>MENU</v>
       </c>
       <c r="C196" t="str">
-        <v>/sites/default/files/2022-08/Jobs%20for%20Geographers.pdf</v>
+        <v>Noyce Scholarship Program                    [Menu ID: group-menu-noyce-scholarship-pro]</v>
       </c>
       <c r="D196" t="str">
-        <v>/wp-content/uploads/2025/11/Jobs-for-Geographers.pdf</v>
+        <v>group-menu-noyce-scholarship-pro                    [Term ID: 1645]</v>
       </c>
       <c r="E196" t="str">
-        <v>❗ HREF Mismatch</v>
+        <v>OK</v>
       </c>
     </row>
     <row r="197">
       <c r="A197" t="str">
-        <v>group-menu-geography</v>
+        <v>group-menu-nuclear-physics</v>
       </c>
       <c r="B197" t="str">
-        <v>SUBCHILD_HREF</v>
+        <v>MENU</v>
       </c>
       <c r="C197" t="str">
-        <v>/sites/default/files/2022-08/Jobs%20in%20Sustainability%20Studies.pdf</v>
+        <v>Nuclear Physics                    [Menu ID: group-menu-nuclear-physics]</v>
       </c>
       <c r="D197" t="str">
-        <v>/wp-content/uploads/2025/11/Jobs-for-Geographers.pdf</v>
+        <v>group-menu-nuclear-physics                    [Term ID: 1664]</v>
       </c>
       <c r="E197" t="str">
-        <v>❗ HREF Mismatch</v>
+        <v>OK</v>
       </c>
     </row>
     <row r="198">
       <c r="A198" t="str">
-        <v>group-menu-geography</v>
+        <v>group-menu-ny-alert</v>
       </c>
       <c r="B198" t="str">
-        <v>CHILD_HREF</v>
+        <v>MENU</v>
       </c>
       <c r="C198" t="str">
-        <v>/geography/AwardsInternships</v>
+        <v>NY Alert                    [Menu ID: group-menu-ny-alert]</v>
       </c>
       <c r="D198" t="str">
-        <v>/geography/awardsinternships</v>
+        <v>group-menu-ny-alert                    [Term ID: 1710]</v>
       </c>
       <c r="E198" t="str">
-        <v>❗ HREF Mismatch</v>
+        <v>OK</v>
       </c>
     </row>
     <row r="199">
       <c r="A199" t="str">
-        <v>group-menu-geography-club</v>
+        <v>group-menu-nyalert</v>
       </c>
       <c r="B199" t="str">
         <v>MENU</v>
       </c>
       <c r="C199" t="str">
-        <v>Geography Club                    [Menu ID: group-menu-geography-club]</v>
+        <v>nyalert                    [Menu ID: group-menu-nyalert]</v>
       </c>
       <c r="D199" t="str">
-        <v>group-menu-geography-club                    [Term ID: 1675]</v>
+        <v/>
       </c>
       <c r="E199" t="str">
-        <v>OK</v>
+        <v>Missing in WP</v>
       </c>
     </row>
     <row r="200">
       <c r="A200" t="str">
-        <v>group-menu-geological-sciences</v>
+        <v>group-menu-nysacac</v>
       </c>
       <c r="B200" t="str">
         <v>MENU</v>
       </c>
       <c r="C200" t="str">
-        <v>Geological, Environmental, and Planetary Sciences                    [Menu ID: group-menu-geological-sciences]</v>
+        <v>NYSACAC                    [Menu ID: group-menu-nysacac]</v>
       </c>
       <c r="D200" t="str">
-        <v>group-menu-geological-sciences                    [Term ID: 1532]</v>
+        <v>group-menu-nysacac                    [Term ID: 1727]</v>
       </c>
       <c r="E200" t="str">
         <v>OK</v>
@@ -3801,16 +3801,16 @@
     </row>
     <row r="201">
       <c r="A201" t="str">
-        <v>group-menu-george-a-marcus</v>
+        <v>group-menu-off-campus-living</v>
       </c>
       <c r="B201" t="str">
         <v>MENU</v>
       </c>
       <c r="C201" t="str">
-        <v>George A Marcus                    [Menu ID: group-menu-george-a-marcus]</v>
+        <v>Off-Campus Living                    [Menu ID: group-menu-off-campus-living]</v>
       </c>
       <c r="D201" t="str">
-        <v>group-menu-george-a-marcus                    [Term ID: 1681]</v>
+        <v>group-menu-off-campus-living                    [Term ID: 1646]</v>
       </c>
       <c r="E201" t="str">
         <v>OK</v>
@@ -3818,16 +3818,16 @@
     </row>
     <row r="202">
       <c r="A202" t="str">
-        <v>group-menu-gold-program</v>
+        <v>group-menu-office-of-the-dean</v>
       </c>
       <c r="B202" t="str">
         <v>MENU</v>
       </c>
       <c r="C202" t="str">
-        <v>GOLD Program                    [Menu ID: group-menu-gold-program]</v>
+        <v>Office of the Advising Director                    [Menu ID: group-menu-office-of-the-dean]</v>
       </c>
       <c r="D202" t="str">
-        <v>group-menu-gold-program                    [Term ID: 1714]</v>
+        <v>group-menu-office-of-the-dean                    [Term ID: 1723]</v>
       </c>
       <c r="E202" t="str">
         <v>OK</v>
@@ -3835,33 +3835,33 @@
     </row>
     <row r="203">
       <c r="A203" t="str">
-        <v>group-menu-gold-program</v>
+        <v>group-menu-office-of-the-preside</v>
       </c>
       <c r="B203" t="str">
-        <v>ITEM_HREF</v>
+        <v>MENU</v>
       </c>
       <c r="C203" t="str">
-        <v>/gold/Leadership</v>
+        <v>Office of the President                    [Menu ID: group-menu-office-of-the-preside]</v>
       </c>
       <c r="D203" t="str">
-        <v>/gold/leadership</v>
+        <v>group-menu-office-of-the-preside                    [Term ID: 1529]</v>
       </c>
       <c r="E203" t="str">
-        <v>❗ HREF Mismatch</v>
+        <v>OK</v>
       </c>
     </row>
     <row r="204">
       <c r="A204" t="str">
-        <v>group-menu-governance</v>
+        <v>group-menu-office-of-the-provost</v>
       </c>
       <c r="B204" t="str">
         <v>MENU</v>
       </c>
       <c r="C204" t="str">
-        <v>Governance                    [Menu ID: group-menu-governance]</v>
+        <v>Office of the Provost                    [Menu ID: group-menu-office-of-the-provost]</v>
       </c>
       <c r="D204" t="str">
-        <v>group-menu-governance                    [Term ID: 1587]</v>
+        <v>group-menu-office-of-the-provost                    [Term ID: 1676]</v>
       </c>
       <c r="E204" t="str">
         <v>OK</v>
@@ -3869,67 +3869,67 @@
     </row>
     <row r="205">
       <c r="A205" t="str">
-        <v>group-menu-graduate-admissions</v>
+        <v>group-menu-offices</v>
       </c>
       <c r="B205" t="str">
         <v>MENU</v>
       </c>
       <c r="C205" t="str">
-        <v>Graduate Admissions                    [Menu ID: group-menu-graduate-admissions]</v>
+        <v>Offices                    [Menu ID: group-menu-offices]</v>
       </c>
       <c r="D205" t="str">
-        <v>group-menu-graduate-admissions                    [Term ID: 1711]</v>
+        <v/>
       </c>
       <c r="E205" t="str">
-        <v>OK</v>
+        <v>Missing in WP</v>
       </c>
     </row>
     <row r="206">
       <c r="A206" t="str">
-        <v>group-menu-grants-management</v>
+        <v>group-menu-oip</v>
       </c>
       <c r="B206" t="str">
         <v>MENU</v>
       </c>
       <c r="C206" t="str">
-        <v>Grants Management - The Research Foundation                    [Menu ID: group-menu-grants-management]</v>
+        <v>Center for Global Engagement                    [Menu ID: group-menu-oip]</v>
       </c>
       <c r="D206" t="str">
-        <v/>
+        <v>group-menu-oip                    [Term ID: 1665]</v>
       </c>
       <c r="E206" t="str">
-        <v>Missing in WP</v>
+        <v>OK</v>
       </c>
     </row>
     <row r="207">
       <c r="A207" t="str">
-        <v>group-menu-great-day</v>
+        <v>group-menu-orlando-furioso</v>
       </c>
       <c r="B207" t="str">
         <v>MENU</v>
       </c>
       <c r="C207" t="str">
-        <v>Great Day                    [Menu ID: group-menu-great-day]</v>
+        <v>Orlando furioso                    [Menu ID: group-menu-orlando-furioso]</v>
       </c>
       <c r="D207" t="str">
-        <v>group-menu-great-day                    [Term ID: 1547]</v>
+        <v/>
       </c>
       <c r="E207" t="str">
-        <v>OK</v>
+        <v>Missing in WP</v>
       </c>
     </row>
     <row r="208">
       <c r="A208" t="str">
-        <v>group-menu-greek-affairs</v>
+        <v>group-menu-parents</v>
       </c>
       <c r="B208" t="str">
         <v>MENU</v>
       </c>
       <c r="C208" t="str">
-        <v>Greek Affairs                    [Menu ID: group-menu-greek-affairs]</v>
+        <v>Parent and Family Resources                    [Menu ID: group-menu-parents]</v>
       </c>
       <c r="D208" t="str">
-        <v>group-menu-greek-affairs                    [Term ID: 1598]</v>
+        <v>group-menu-parents                    [Term ID: 1701]</v>
       </c>
       <c r="E208" t="str">
         <v>OK</v>
@@ -3937,67 +3937,67 @@
     </row>
     <row r="209">
       <c r="A209" t="str">
-        <v>group-menu-greek-affairs</v>
+        <v>group-menu-parking-transportatio</v>
       </c>
       <c r="B209" t="str">
-        <v>ITEM_HREF</v>
+        <v>MENU</v>
       </c>
       <c r="C209" t="str">
-        <v>/sites/default/files/sites/greek/Recognition%20policy%208-13.pdf</v>
+        <v>Parking &amp; Transportation                    [Menu ID: group-menu-parking-transportatio]</v>
       </c>
       <c r="D209" t="str">
-        <v>/wp-content/uploads/2025/11/Recognition-policy-8-13.pdf</v>
+        <v>group-menu-parking-transportatio                    [Term ID: 1667]</v>
       </c>
       <c r="E209" t="str">
-        <v>❗ HREF Mismatch</v>
+        <v>OK</v>
       </c>
     </row>
     <row r="210">
       <c r="A210" t="str">
-        <v>group-menu-greek-affairs</v>
+        <v>group-menu-pathways</v>
       </c>
       <c r="B210" t="str">
-        <v>ITEM_HREF</v>
+        <v>MENU</v>
       </c>
       <c r="C210" t="str">
-        <v>/sites/default/files/sites/greek/relationship_statement_04.pdf</v>
+        <v>Pathways                    [Menu ID: group-menu-pathways]</v>
       </c>
       <c r="D210" t="str">
-        <v>/wp-content/uploads/2025/11/relationship_statement_04.pdf</v>
+        <v>group-menu-pathways                    [Term ID: 1647]</v>
       </c>
       <c r="E210" t="str">
-        <v>❗ HREF Mismatch</v>
+        <v>OK</v>
       </c>
     </row>
     <row r="211">
       <c r="A211" t="str">
-        <v>group-menu-greek-affairs</v>
+        <v>group-menu-peace-action-geneseo</v>
       </c>
       <c r="B211" t="str">
-        <v>ITEM_HREF</v>
+        <v>MENU</v>
       </c>
       <c r="C211" t="str">
-        <v>http://offcampus.geneseo.edu</v>
+        <v>Peace Action Geneseo                    [Menu ID: group-menu-peace-action-geneseo]</v>
       </c>
       <c r="D211" t="str">
         <v/>
       </c>
       <c r="E211" t="str">
-        <v>❗ HREF Mismatch</v>
+        <v>Missing in WP</v>
       </c>
     </row>
     <row r="212">
       <c r="A212" t="str">
-        <v>group-menu-grow-stem</v>
+        <v>group-menu-peace-poetry</v>
       </c>
       <c r="B212" t="str">
         <v>MENU</v>
       </c>
       <c r="C212" t="str">
-        <v>GROW STEM                    [Menu ID: group-menu-grow-stem]</v>
+        <v>Peace Poetry                    [Menu ID: group-menu-peace-poetry]</v>
       </c>
       <c r="D212" t="str">
-        <v>group-menu-grow-stem                    [Term ID: 1728]</v>
+        <v>group-menu-peace-poetry                    [Term ID: 1641]</v>
       </c>
       <c r="E212" t="str">
         <v>OK</v>
@@ -4005,13 +4005,13 @@
     </row>
     <row r="213">
       <c r="A213" t="str">
-        <v>group-menu-habitat-for-humanity</v>
+        <v>group-menu-pep-band</v>
       </c>
       <c r="B213" t="str">
         <v>MENU</v>
       </c>
       <c r="C213" t="str">
-        <v>Habitat for Humanity                    [Menu ID: group-menu-habitat-for-humanity]</v>
+        <v>Pep Band                    [Menu ID: group-menu-pep-band]</v>
       </c>
       <c r="D213" t="str">
         <v/>
@@ -4022,16 +4022,16 @@
     </row>
     <row r="214">
       <c r="A214" t="str">
-        <v>group-menu-health-counseling</v>
+        <v>group-menu-phi-beta-kappa</v>
       </c>
       <c r="B214" t="str">
         <v>MENU</v>
       </c>
       <c r="C214" t="str">
-        <v>SHC Home                    [Menu ID: group-menu-health-counseling]</v>
+        <v>Phi Beta Kappa                    [Menu ID: group-menu-phi-beta-kappa]</v>
       </c>
       <c r="D214" t="str">
-        <v>group-menu-health-counseling                    [Term ID: 1546]</v>
+        <v>group-menu-phi-beta-kappa                    [Term ID: 1618]</v>
       </c>
       <c r="E214" t="str">
         <v>OK</v>
@@ -4039,67 +4039,67 @@
     </row>
     <row r="215">
       <c r="A215" t="str">
-        <v>group-menu-hillel-</v>
+        <v>group-menu-phi-beta-lambda</v>
       </c>
       <c r="B215" t="str">
         <v>MENU</v>
       </c>
       <c r="C215" t="str">
-        <v>Hillel                     [Menu ID: group-menu-hillel-]</v>
+        <v>Phi Beta Lambda                    [Menu ID: group-menu-phi-beta-lambda]</v>
       </c>
       <c r="D215" t="str">
-        <v>group-menu-hillel-                    [Term ID: 1724]</v>
+        <v/>
       </c>
       <c r="E215" t="str">
-        <v>OK</v>
+        <v>Missing in WP</v>
       </c>
     </row>
     <row r="216">
       <c r="A216" t="str">
-        <v>group-menu-hillel-</v>
+        <v>group-menu-phi-eta-sigma</v>
       </c>
       <c r="B216" t="str">
-        <v>ITEM_HREF</v>
+        <v>MENU</v>
       </c>
       <c r="C216" t="str">
-        <v>/hillel-/about-us</v>
+        <v>Phi Eta Sigma                    [Menu ID: group-menu-phi-eta-sigma]</v>
       </c>
       <c r="D216" t="str">
-        <v>/hillel/about-us</v>
+        <v/>
       </c>
       <c r="E216" t="str">
-        <v>❗ HREF Mismatch</v>
+        <v>Missing in WP</v>
       </c>
     </row>
     <row r="217">
       <c r="A217" t="str">
-        <v>group-menu-hippies-for-hope</v>
+        <v>group-menu-philosophy</v>
       </c>
       <c r="B217" t="str">
         <v>MENU</v>
       </c>
       <c r="C217" t="str">
-        <v>Hippies for Hope                    [Menu ID: group-menu-hippies-for-hope]</v>
+        <v>Philosophy                    [Menu ID: group-menu-philosophy]</v>
       </c>
       <c r="D217" t="str">
-        <v/>
+        <v>group-menu-philosophy                    [Term ID: 1541]</v>
       </c>
       <c r="E217" t="str">
-        <v>Missing in WP</v>
+        <v>OK</v>
       </c>
     </row>
     <row r="218">
       <c r="A218" t="str">
-        <v>group-menu-history</v>
+        <v>group-menu-physics-astronomy</v>
       </c>
       <c r="B218" t="str">
         <v>MENU</v>
       </c>
       <c r="C218" t="str">
-        <v>History                    [Menu ID: group-menu-history]</v>
+        <v>Physics &amp; Astronomy                    [Menu ID: group-menu-physics-astronomy]</v>
       </c>
       <c r="D218" t="str">
-        <v>group-menu-history                    [Term ID: 1593]</v>
+        <v>group-menu-physics-astronomy                    [Term ID: 1557]</v>
       </c>
       <c r="E218" t="str">
         <v>OK</v>
@@ -4107,16 +4107,16 @@
     </row>
     <row r="219">
       <c r="A219" t="str">
-        <v>group-menu-homecoming</v>
+        <v>group-menu-phystec-geneseo</v>
       </c>
       <c r="B219" t="str">
         <v>MENU</v>
       </c>
       <c r="C219" t="str">
-        <v>Family Weekend                    [Menu ID: group-menu-homecoming]</v>
+        <v>PhysTEC Geneseo                    [Menu ID: group-menu-phystec-geneseo]</v>
       </c>
       <c r="D219" t="str">
-        <v>group-menu-homecoming                    [Term ID: 1671]</v>
+        <v>group-menu-phystec-geneseo                    [Term ID: 1602]</v>
       </c>
       <c r="E219" t="str">
         <v>OK</v>
@@ -4124,16 +4124,16 @@
     </row>
     <row r="220">
       <c r="A220" t="str">
-        <v>group-menu-human-resources</v>
+        <v>group-menu-police</v>
       </c>
       <c r="B220" t="str">
         <v>MENU</v>
       </c>
       <c r="C220" t="str">
-        <v>Human Resources &amp; Payroll Services                    [Menu ID: group-menu-human-resources]</v>
+        <v>Police                    [Menu ID: group-menu-police]</v>
       </c>
       <c r="D220" t="str">
-        <v>group-menu-human-resources                    [Term ID: 1538]</v>
+        <v>group-menu-police                    [Term ID: 1666]</v>
       </c>
       <c r="E220" t="str">
         <v>OK</v>
@@ -4141,16 +4141,16 @@
     </row>
     <row r="221">
       <c r="A221" t="str">
-        <v>group-menu-incoming-exchange-stu</v>
+        <v>group-menu-political-science</v>
       </c>
       <c r="B221" t="str">
         <v>MENU</v>
       </c>
       <c r="C221" t="str">
-        <v>Incoming Exchange Students                    [Menu ID: group-menu-incoming-exchange-stu]</v>
+        <v>Political Science                    [Menu ID: group-menu-political-science]</v>
       </c>
       <c r="D221" t="str">
-        <v>group-menu-incoming-exchange-stu                    [Term ID: 1718]</v>
+        <v>group-menu-political-science                    [Term ID: 1533]</v>
       </c>
       <c r="E221" t="str">
         <v>OK</v>
@@ -4158,33 +4158,33 @@
     </row>
     <row r="222">
       <c r="A222" t="str">
-        <v>group-menu-information-security-</v>
+        <v>group-menu-poll-everywhere</v>
       </c>
       <c r="B222" t="str">
         <v>MENU</v>
       </c>
       <c r="C222" t="str">
-        <v>Information Security Program                    [Menu ID: group-menu-information-security-]</v>
+        <v>Poll Everywhere                    [Menu ID: group-menu-poll-everywhere]</v>
       </c>
       <c r="D222" t="str">
-        <v/>
+        <v>group-menu-poll-everywhere                    [Term ID: 1617]</v>
       </c>
       <c r="E222" t="str">
-        <v>Missing in WP</v>
+        <v>OK</v>
       </c>
     </row>
     <row r="223">
       <c r="A223" t="str">
-        <v>group-menu-insomnia-film-festiva</v>
+        <v>group-menu-power-of-physical-sci</v>
       </c>
       <c r="B223" t="str">
         <v>MENU</v>
       </c>
       <c r="C223" t="str">
-        <v>Insomnia Film Festival                    [Menu ID: group-menu-insomnia-film-festiva]</v>
+        <v>Power of Physical Science                    [Menu ID: group-menu-power-of-physical-sci]</v>
       </c>
       <c r="D223" t="str">
-        <v>group-menu-insomnia-film-festiva                    [Term ID: 1720]</v>
+        <v>group-menu-power-of-physical-sci                    [Term ID: 1535]</v>
       </c>
       <c r="E223" t="str">
         <v>OK</v>
@@ -4192,16 +4192,16 @@
     </row>
     <row r="224">
       <c r="A224" t="str">
-        <v>group-menu-institutional-researc</v>
+        <v>group-menu-pre-law</v>
       </c>
       <c r="B224" t="str">
         <v>MENU</v>
       </c>
       <c r="C224" t="str">
-        <v>Institutional Research &amp; Effectiveness                    [Menu ID: group-menu-institutional-researc]</v>
+        <v>Pre-Law                    [Menu ID: group-menu-pre-law]</v>
       </c>
       <c r="D224" t="str">
-        <v>group-menu-institutional-researc                    [Term ID: 1670]</v>
+        <v>group-menu-pre-law                    [Term ID: 1689]</v>
       </c>
       <c r="E224" t="str">
         <v>OK</v>
@@ -4209,16 +4209,16 @@
     </row>
     <row r="225">
       <c r="A225" t="str">
-        <v>group-menu-inter-greek-council</v>
+        <v>group-menu-premed</v>
       </c>
       <c r="B225" t="str">
         <v>MENU</v>
       </c>
       <c r="C225" t="str">
-        <v>Inter Greek Council                    [Menu ID: group-menu-inter-greek-council]</v>
+        <v>Pre-Med/Pre-Health                    [Menu ID: group-menu-premed]</v>
       </c>
       <c r="D225" t="str">
-        <v>group-menu-inter-greek-council                    [Term ID: 1576]</v>
+        <v>group-menu-premed                    [Term ID: 1690]</v>
       </c>
       <c r="E225" t="str">
         <v>OK</v>
@@ -4226,33 +4226,33 @@
     </row>
     <row r="226">
       <c r="A226" t="str">
-        <v>group-menu-interfaith-center</v>
+        <v>group-menu-prism-math-club</v>
       </c>
       <c r="B226" t="str">
         <v>MENU</v>
       </c>
       <c r="C226" t="str">
-        <v>Interfaith Center                    [Menu ID: group-menu-interfaith-center]</v>
+        <v>PRISM Math Club                    [Menu ID: group-menu-prism-math-club]</v>
       </c>
       <c r="D226" t="str">
-        <v/>
+        <v>group-menu-prism-math-club                    [Term ID: 1627]</v>
       </c>
       <c r="E226" t="str">
-        <v>Missing in WP</v>
+        <v>OK</v>
       </c>
     </row>
     <row r="227">
       <c r="A227" t="str">
-        <v>group-menu-internal-controls</v>
+        <v>group-menu-prof-gu</v>
       </c>
       <c r="B227" t="str">
         <v>MENU</v>
       </c>
       <c r="C227" t="str">
-        <v>Internal Controls                    [Menu ID: group-menu-internal-controls]</v>
+        <v>Prof Gu                    [Menu ID: group-menu-prof-gu]</v>
       </c>
       <c r="D227" t="str">
-        <v>group-menu-internal-controls                    [Term ID: 1643]</v>
+        <v>group-menu-prof-gu                    [Term ID: 1595]</v>
       </c>
       <c r="E227" t="str">
         <v>OK</v>
@@ -4260,16 +4260,16 @@
     </row>
     <row r="228">
       <c r="A228" t="str">
-        <v>group-menu-intramural-sports</v>
+        <v>group-menu-prof-herzman</v>
       </c>
       <c r="B228" t="str">
         <v>MENU</v>
       </c>
       <c r="C228" t="str">
-        <v>Intramural Sports                    [Menu ID: group-menu-intramural-sports]</v>
+        <v>Prof Herzman                    [Menu ID: group-menu-prof-herzman]</v>
       </c>
       <c r="D228" t="str">
-        <v>group-menu-intramural-sports                    [Term ID: 1644]</v>
+        <v>group-menu-prof-herzman                    [Term ID: 1622]</v>
       </c>
       <c r="E228" t="str">
         <v>OK</v>
@@ -4277,67 +4277,67 @@
     </row>
     <row r="229">
       <c r="A229" t="str">
-        <v>group-menu-intramural-sports</v>
+        <v>group-menu-proofspace</v>
       </c>
       <c r="B229" t="str">
-        <v>ITEM_HREF</v>
+        <v>MENU</v>
       </c>
       <c r="C229" t="str">
-        <v>https://go.geneseo.edu/ileagues</v>
+        <v>ProofSpace                    [Menu ID: group-menu-proofspace]</v>
       </c>
       <c r="D229" t="str">
-        <v>https://quikpayasp.com/geneseo/quikpay/spa/externalauthenticationindex.do#/send-code?dm=commerce_manager_payer</v>
+        <v>group-menu-proofspace                    [Term ID: 1552]</v>
       </c>
       <c r="E229" t="str">
-        <v>❗ HREF Mismatch</v>
+        <v>OK</v>
       </c>
     </row>
     <row r="230">
       <c r="A230" t="str">
-        <v>group-menu-intramural-sports</v>
+        <v>group-menu-property-control-serv</v>
       </c>
       <c r="B230" t="str">
-        <v>ITEM_HREF</v>
+        <v>MENU</v>
       </c>
       <c r="C230" t="str">
-        <v>http://www.nirsa.org</v>
+        <v>Property Control Services                    [Menu ID: group-menu-property-control-serv]</v>
       </c>
       <c r="D230" t="str">
         <v/>
       </c>
       <c r="E230" t="str">
-        <v>❗ HREF Mismatch</v>
+        <v>Missing in WP</v>
       </c>
     </row>
     <row r="231">
       <c r="A231" t="str">
-        <v>group-menu-intramural-sports</v>
+        <v>group-menu-psychology-club</v>
       </c>
       <c r="B231" t="str">
-        <v>ITEM_HREF</v>
+        <v>MENU</v>
       </c>
       <c r="C231" t="str">
-        <v>/sites/default/files/2023-01/TEAM%20ENTRY%20FORM.-intramurals1.doc</v>
+        <v>Psychology Club                    [Menu ID: group-menu-psychology-club]</v>
       </c>
       <c r="D231" t="str">
-        <v>/wp-content/uploads/2025/11/TEAM-ENTRY-FORM.-intramurals1.doc</v>
+        <v>group-menu-psychology-club                    [Term ID: 1626]</v>
       </c>
       <c r="E231" t="str">
-        <v>❗ HREF Mismatch</v>
+        <v>OK</v>
       </c>
     </row>
     <row r="232">
       <c r="A232" t="str">
-        <v>group-menu-isss</v>
+        <v>group-menu-psychology-department</v>
       </c>
       <c r="B232" t="str">
         <v>MENU</v>
       </c>
       <c r="C232" t="str">
-        <v>International Student &amp; Scholar Services                    [Menu ID: group-menu-isss]</v>
+        <v>Department of Psychology                     [Menu ID: group-menu-psychology-department]</v>
       </c>
       <c r="D232" t="str">
-        <v>group-menu-isss                    [Term ID: 1548]</v>
+        <v>group-menu-psychology-department                    [Term ID: 1539]</v>
       </c>
       <c r="E232" t="str">
         <v>OK</v>
@@ -4345,67 +4345,67 @@
     </row>
     <row r="233">
       <c r="A233" t="str">
-        <v>group-menu-jennifer-apple</v>
+        <v>group-menu-purchasing</v>
       </c>
       <c r="B233" t="str">
         <v>MENU</v>
       </c>
       <c r="C233" t="str">
-        <v>Jennifer Apple                    [Menu ID: group-menu-jennifer-apple]</v>
+        <v>Purchasing                    [Menu ID: group-menu-purchasing]</v>
       </c>
       <c r="D233" t="str">
-        <v/>
+        <v>group-menu-purchasing                    [Term ID: 1562]</v>
       </c>
       <c r="E233" t="str">
-        <v>Missing in WP</v>
+        <v>OK</v>
       </c>
     </row>
     <row r="234">
       <c r="A234" t="str">
-        <v>group-menu-joe-dolce</v>
+        <v>group-menu-ratio-christi</v>
       </c>
       <c r="B234" t="str">
         <v>MENU</v>
       </c>
       <c r="C234" t="str">
-        <v>Joe Dolce                    [Menu ID: group-menu-joe-dolce]</v>
+        <v>Ratio Christi                    [Menu ID: group-menu-ratio-christi]</v>
       </c>
       <c r="D234" t="str">
-        <v>group-menu-joe-dolce                    [Term ID: 1702]</v>
+        <v/>
       </c>
       <c r="E234" t="str">
-        <v>OK</v>
+        <v>Missing in WP</v>
       </c>
     </row>
     <row r="235">
       <c r="A235" t="str">
-        <v>group-menu-kappa-sigma</v>
+        <v>group-menu-red-cross-club</v>
       </c>
       <c r="B235" t="str">
         <v>MENU</v>
       </c>
       <c r="C235" t="str">
-        <v>Kappa Sigma                    [Menu ID: group-menu-kappa-sigma]</v>
+        <v>Red Cross Club                    [Menu ID: group-menu-red-cross-club]</v>
       </c>
       <c r="D235" t="str">
-        <v/>
+        <v>group-menu-red-cross-club                    [Term ID: 1639]</v>
       </c>
       <c r="E235" t="str">
-        <v>Missing in WP</v>
+        <v>OK</v>
       </c>
     </row>
     <row r="236">
       <c r="A236" t="str">
-        <v>group-menu-knighline</v>
+        <v>group-menu-red-folder</v>
       </c>
       <c r="B236" t="str">
         <v>MENU</v>
       </c>
       <c r="C236" t="str">
-        <v>Geneseo Knightline Dance Team                    [Menu ID: group-menu-knighline]</v>
+        <v>Red Folder                    [Menu ID: group-menu-red-folder]</v>
       </c>
       <c r="D236" t="str">
-        <v>group-menu-knighline                    [Term ID: 1615]</v>
+        <v>group-menu-red-folder                    [Term ID: 1726]</v>
       </c>
       <c r="E236" t="str">
         <v>OK</v>
@@ -4413,16 +4413,16 @@
     </row>
     <row r="237">
       <c r="A237" t="str">
-        <v>group-menu-kurt-fletcher</v>
+        <v>group-menu-registrar</v>
       </c>
       <c r="B237" t="str">
         <v>MENU</v>
       </c>
       <c r="C237" t="str">
-        <v>Kurt Fletcher                    [Menu ID: group-menu-kurt-fletcher]</v>
+        <v>Registrar                    [Menu ID: group-menu-registrar]</v>
       </c>
       <c r="D237" t="str">
-        <v>group-menu-kurt-fletcher                    [Term ID: 1678]</v>
+        <v>group-menu-registrar                    [Term ID: 1606]</v>
       </c>
       <c r="E237" t="str">
         <v>OK</v>
@@ -4430,13 +4430,13 @@
     </row>
     <row r="238">
       <c r="A238" t="str">
-        <v>group-menu-kurt-fletcher</v>
+        <v>group-menu-reinhardt-research-</v>
       </c>
       <c r="B238" t="str">
-        <v>ITEM_TITLE</v>
+        <v>MENU</v>
       </c>
       <c r="C238" t="str">
-        <v>Vita</v>
+        <v>Reinhardt Research                     [Menu ID: group-menu-reinhardt-research-]</v>
       </c>
       <c r="D238" t="str">
         <v/>
@@ -4447,33 +4447,33 @@
     </row>
     <row r="239">
       <c r="A239" t="str">
-        <v>group-menu-kurt-fletcher</v>
+        <v>group-menu-reunion</v>
       </c>
       <c r="B239" t="str">
-        <v>ITEM_HREF</v>
+        <v>MENU</v>
       </c>
       <c r="C239" t="str">
-        <v>/sites/default/files/sites/fletcher/RESUME.pdf</v>
+        <v>Reunion                    [Menu ID: group-menu-reunion]</v>
       </c>
       <c r="D239" t="str">
-        <v/>
+        <v>group-menu-reunion                    [Term ID: 1662]</v>
       </c>
       <c r="E239" t="str">
-        <v>Missing in WP</v>
+        <v>OK</v>
       </c>
     </row>
     <row r="240">
       <c r="A240" t="str">
-        <v>group-menu-languages-literatures</v>
+        <v>group-menu-roemer-arboretum</v>
       </c>
       <c r="B240" t="str">
         <v>MENU</v>
       </c>
       <c r="C240" t="str">
-        <v>Global Languages and Cultures                    [Menu ID: group-menu-languages-literatures]</v>
+        <v>Roemer Arboretum                    [Menu ID: group-menu-roemer-arboretum]</v>
       </c>
       <c r="D240" t="str">
-        <v>group-menu-languages-literatures                    [Term ID: 1579]</v>
+        <v>group-menu-roemer-arboretum                    [Term ID: 1732]</v>
       </c>
       <c r="E240" t="str">
         <v>OK</v>
@@ -4481,50 +4481,50 @@
     </row>
     <row r="241">
       <c r="A241" t="str">
-        <v>group-menu-languages-literatures</v>
+        <v>group-menu-rose-mcewen</v>
       </c>
       <c r="B241" t="str">
-        <v>CHILD_HREF</v>
+        <v>MENU</v>
       </c>
       <c r="C241" t="str">
-        <v>/languages_literatures/writing_requirement</v>
+        <v>Rose McEwen                    [Menu ID: group-menu-rose-mcewen]</v>
       </c>
       <c r="D241" t="str">
-        <v>/entity:node/107430</v>
+        <v>group-menu-rose-mcewen                    [Term ID: 1591]</v>
       </c>
       <c r="E241" t="str">
-        <v>❗ HREF Mismatch</v>
+        <v>OK</v>
       </c>
     </row>
     <row r="242">
       <c r="A242" t="str">
-        <v>group-menu-languages-literatures</v>
+        <v>group-menu-rugby</v>
       </c>
       <c r="B242" t="str">
-        <v>ITEM_HREF</v>
+        <v>MENU</v>
       </c>
       <c r="C242" t="str">
-        <v>/global-languages-cultures/faculty-resources</v>
+        <v>Men's Rugby                    [Menu ID: group-menu-rugby]</v>
       </c>
       <c r="D242" t="str">
-        <v>/entity:node/151148</v>
+        <v/>
       </c>
       <c r="E242" t="str">
-        <v>❗ HREF Mismatch</v>
+        <v>Missing in WP</v>
       </c>
     </row>
     <row r="243">
       <c r="A243" t="str">
-        <v>group-menu-latin-american-studie</v>
+        <v>group-menu-rysag</v>
       </c>
       <c r="B243" t="str">
         <v>MENU</v>
       </c>
       <c r="C243" t="str">
-        <v>Latin American &amp; Caribbean Studies                    [Menu ID: group-menu-latin-american-studie]</v>
+        <v>RYSAG                    [Menu ID: group-menu-rysag]</v>
       </c>
       <c r="D243" t="str">
-        <v>group-menu-latin-american-studie                    [Term ID: 1543]</v>
+        <v>group-menu-rysag                    [Term ID: 1635]</v>
       </c>
       <c r="E243" t="str">
         <v>OK</v>
@@ -4532,50 +4532,50 @@
     </row>
     <row r="244">
       <c r="A244" t="str">
-        <v>group-menu-latin-american-studie</v>
+        <v>group-menu-safe-party</v>
       </c>
       <c r="B244" t="str">
-        <v>CHILD_TITLE</v>
+        <v>MENU</v>
       </c>
       <c r="C244" t="str">
-        <v>Latin American Studies at SUNY Geneseo: Facebook</v>
+        <v>Safe Party                    [Menu ID: group-menu-safe-party]</v>
       </c>
       <c r="D244" t="str">
-        <v/>
+        <v>group-menu-safe-party                    [Term ID: 1594]</v>
       </c>
       <c r="E244" t="str">
-        <v>Missing in WP</v>
+        <v>OK</v>
       </c>
     </row>
     <row r="245">
       <c r="A245" t="str">
-        <v>group-menu-latin-american-studie</v>
+        <v>group-menu-sam-bean</v>
       </c>
       <c r="B245" t="str">
-        <v>CHILD_HREF</v>
+        <v>MENU</v>
       </c>
       <c r="C245" t="str">
-        <v>https://www.facebook.com/latinamericanstudiesgeneseo?ref=hl</v>
+        <v>Sam Bean                    [Menu ID: group-menu-sam-bean]</v>
       </c>
       <c r="D245" t="str">
-        <v/>
+        <v>group-menu-sam-bean                    [Term ID: 1612]</v>
       </c>
       <c r="E245" t="str">
-        <v>Missing in WP</v>
+        <v>OK</v>
       </c>
     </row>
     <row r="246">
       <c r="A246" t="str">
-        <v>group-menu-lgbtq</v>
+        <v>group-menu-savi-iyer</v>
       </c>
       <c r="B246" t="str">
         <v>MENU</v>
       </c>
       <c r="C246" t="str">
-        <v>Office of LGBTQ+ Life                    [Menu ID: group-menu-lgbtq]</v>
+        <v>Savi Iyer                    [Menu ID: group-menu-savi-iyer]</v>
       </c>
       <c r="D246" t="str">
-        <v>group-menu-lgbtq                    [Term ID: 1735]</v>
+        <v>group-menu-savi-iyer                    [Term ID: 1680]</v>
       </c>
       <c r="E246" t="str">
         <v>OK</v>
@@ -4583,16 +4583,16 @@
     </row>
     <row r="247">
       <c r="A247" t="str">
-        <v>group-menu-linda-ware-ph-d-</v>
+        <v>group-menu-sbdc</v>
       </c>
       <c r="B247" t="str">
         <v>MENU</v>
       </c>
       <c r="C247" t="str">
-        <v>Linda Ware Ph.D.                    [Menu ID: group-menu-linda-ware-ph-d-]</v>
+        <v>SBDC                    [Menu ID: group-menu-sbdc]</v>
       </c>
       <c r="D247" t="str">
-        <v>group-menu-linda-ware-ph-d-                    [Term ID: 1621]</v>
+        <v>group-menu-sbdc                    [Term ID: 1658]</v>
       </c>
       <c r="E247" t="str">
         <v>OK</v>
@@ -4600,33 +4600,33 @@
     </row>
     <row r="248">
       <c r="A248" t="str">
-        <v>group-menu-linda-ware-ph-d-</v>
+        <v>group-menu-scene</v>
       </c>
       <c r="B248" t="str">
-        <v>ITEM_HREF</v>
+        <v>MENU</v>
       </c>
       <c r="C248" t="str">
-        <v>http://lindaware.blogspot.com</v>
+        <v>Scene                    [Menu ID: group-menu-scene]</v>
       </c>
       <c r="D248" t="str">
-        <v/>
+        <v>group-menu-scene                    [Term ID: 1725]</v>
       </c>
       <c r="E248" t="str">
-        <v>❗ HREF Mismatch</v>
+        <v>OK</v>
       </c>
     </row>
     <row r="249">
       <c r="A249" t="str">
-        <v>group-menu-linguistics-minor</v>
+        <v>group-menu-school-of-business</v>
       </c>
       <c r="B249" t="str">
         <v>MENU</v>
       </c>
       <c r="C249" t="str">
-        <v>Linguistics Minor                    [Menu ID: group-menu-linguistics-minor]</v>
+        <v>School of Business                    [Menu ID: group-menu-school-of-business]</v>
       </c>
       <c r="D249" t="str">
-        <v>group-menu-linguistics-minor                    [Term ID: 1719]</v>
+        <v>group-menu-school-of-business                    [Term ID: 1694]</v>
       </c>
       <c r="E249" t="str">
         <v>OK</v>
@@ -4634,47 +4634,47 @@
     </row>
     <row r="250">
       <c r="A250" t="str">
-        <v>group-menu-linguistics-minor</v>
+        <v>group-menu-school-of-education</v>
       </c>
       <c r="B250" t="str">
-        <v>ITEM_TITLE</v>
+        <v>MENU</v>
       </c>
       <c r="C250" t="str">
-        <v>Linguistics Minor</v>
+        <v>School of Education                    [Menu ID: group-menu-school-of-education]</v>
       </c>
       <c r="D250" t="str">
-        <v/>
+        <v>group-menu-school-of-education                    [Term ID: 1560]</v>
       </c>
       <c r="E250" t="str">
-        <v>Missing in WP</v>
+        <v>OK</v>
       </c>
     </row>
     <row r="251">
       <c r="A251" t="str">
-        <v>group-menu-linguistics-minor</v>
+        <v>group-menu-scott-giorgis</v>
       </c>
       <c r="B251" t="str">
-        <v>ITEM_HREF</v>
+        <v>MENU</v>
       </c>
       <c r="C251" t="str">
-        <v/>
+        <v>Scott Giorgis                    [Menu ID: group-menu-scott-giorgis]</v>
       </c>
       <c r="D251" t="str">
-        <v/>
+        <v>group-menu-scott-giorgis                    [Term ID: 1682]</v>
       </c>
       <c r="E251" t="str">
-        <v>Missing in WP</v>
+        <v>OK</v>
       </c>
     </row>
     <row r="252">
       <c r="A252" t="str">
-        <v>group-menu-livingston-cares</v>
+        <v>group-menu-sean-nixon</v>
       </c>
       <c r="B252" t="str">
         <v>MENU</v>
       </c>
       <c r="C252" t="str">
-        <v>Livingston Cares                    [Menu ID: group-menu-livingston-cares]</v>
+        <v>Sean Nixon                    [Menu ID: group-menu-sean-nixon]</v>
       </c>
       <c r="D252" t="str">
         <v/>
@@ -4685,67 +4685,67 @@
     </row>
     <row r="253">
       <c r="A253" t="str">
-        <v>group-menu-mail-services</v>
+        <v>group-menu-seaway-section-2016</v>
       </c>
       <c r="B253" t="str">
         <v>MENU</v>
       </c>
       <c r="C253" t="str">
-        <v>Mail Services                    [Menu ID: group-menu-mail-services]</v>
+        <v>Seaway Section 2016                    [Menu ID: group-menu-seaway-section-2016]</v>
       </c>
       <c r="D253" t="str">
-        <v>group-menu-mail-services                    [Term ID: 1657]</v>
+        <v/>
       </c>
       <c r="E253" t="str">
-        <v>OK</v>
+        <v>Missing in WP</v>
       </c>
     </row>
     <row r="254">
       <c r="A254" t="str">
-        <v>group-menu-make-your-mark</v>
+        <v>group-menu-sefa</v>
       </c>
       <c r="B254" t="str">
         <v>MENU</v>
       </c>
       <c r="C254" t="str">
-        <v>Make Your Mark                    [Menu ID: group-menu-make-your-mark]</v>
+        <v>SEFA                    [Menu ID: group-menu-sefa]</v>
       </c>
       <c r="D254" t="str">
-        <v/>
+        <v>group-menu-sefa                    [Term ID: 1648]</v>
       </c>
       <c r="E254" t="str">
-        <v>Missing in WP</v>
+        <v>OK</v>
       </c>
     </row>
     <row r="255">
       <c r="A255" t="str">
-        <v>group-menu-maria-h-lima</v>
+        <v>group-menu-shakti</v>
       </c>
       <c r="B255" t="str">
         <v>MENU</v>
       </c>
       <c r="C255" t="str">
-        <v>Maria H. Lima                    [Menu ID: group-menu-maria-h-lima]</v>
+        <v>Shakti                    [Menu ID: group-menu-shakti]</v>
       </c>
       <c r="D255" t="str">
-        <v/>
+        <v>group-menu-shakti                    [Term ID: 1640]</v>
       </c>
       <c r="E255" t="str">
-        <v>Missing in WP</v>
+        <v>OK</v>
       </c>
     </row>
     <row r="256">
       <c r="A256" t="str">
-        <v>group-menu-master-teacher</v>
+        <v>group-menu-sibling-peer-research</v>
       </c>
       <c r="B256" t="str">
         <v>MENU</v>
       </c>
       <c r="C256" t="str">
-        <v>Master Teacher                    [Menu ID: group-menu-master-teacher]</v>
+        <v>Sibling-Peer Research Group                    [Menu ID: group-menu-sibling-peer-research]</v>
       </c>
       <c r="D256" t="str">
-        <v>group-menu-master-teacher                    [Term ID: 1663]</v>
+        <v>group-menu-sibling-peer-research                    [Term ID: 1614]</v>
       </c>
       <c r="E256" t="str">
         <v>OK</v>
@@ -4753,16 +4753,16 @@
     </row>
     <row r="257">
       <c r="A257" t="str">
-        <v>group-menu-mathematics</v>
+        <v>group-menu-soaringstars</v>
       </c>
       <c r="B257" t="str">
         <v>MENU</v>
       </c>
       <c r="C257" t="str">
-        <v>Mathematics                    [Menu ID: group-menu-mathematics]</v>
+        <v>SoaringStars                    [Menu ID: group-menu-soaringstars]</v>
       </c>
       <c r="D257" t="str">
-        <v>group-menu-mathematics                    [Term ID: 1553]</v>
+        <v>group-menu-soaringstars                    [Term ID: 1563]</v>
       </c>
       <c r="E257" t="str">
         <v>OK</v>
@@ -4770,67 +4770,67 @@
     </row>
     <row r="258">
       <c r="A258" t="str">
-        <v>group-menu-michael-teres</v>
+        <v>group-menu-society-for-human-res</v>
       </c>
       <c r="B258" t="str">
         <v>MENU</v>
       </c>
       <c r="C258" t="str">
-        <v>Michael Teres                    [Menu ID: group-menu-michael-teres]</v>
+        <v>Society for Human Resource Man                    [Menu ID: group-menu-society-for-human-res]</v>
       </c>
       <c r="D258" t="str">
-        <v/>
+        <v>group-menu-society-for-human-res                    [Term ID: 1597]</v>
       </c>
       <c r="E258" t="str">
-        <v>Missing in WP</v>
+        <v>OK</v>
       </c>
     </row>
     <row r="259">
       <c r="A259" t="str">
-        <v>group-menu-migration-and-electio</v>
+        <v>group-menu-sociology</v>
       </c>
       <c r="B259" t="str">
         <v>MENU</v>
       </c>
       <c r="C259" t="str">
-        <v>Migration and Elections Databa                    [Menu ID: group-menu-migration-and-electio]</v>
+        <v>Sociology                    [Menu ID: group-menu-sociology]</v>
       </c>
       <c r="D259" t="str">
-        <v/>
+        <v>group-menu-sociology                    [Term ID: 1555]</v>
       </c>
       <c r="E259" t="str">
-        <v>Missing in WP</v>
+        <v>OK</v>
       </c>
     </row>
     <row r="260">
       <c r="A260" t="str">
-        <v>group-menu-miles</v>
+        <v>group-menu-sociomedical-sciences</v>
       </c>
       <c r="B260" t="str">
         <v>MENU</v>
       </c>
       <c r="C260" t="str">
-        <v>MILES                    [Menu ID: group-menu-miles]</v>
+        <v>Sociomedical Sciences                    [Menu ID: group-menu-sociomedical-sciences]</v>
       </c>
       <c r="D260" t="str">
-        <v/>
+        <v>group-menu-sociomedical-sciences                    [Term ID: 1534]</v>
       </c>
       <c r="E260" t="str">
-        <v>Missing in WP</v>
+        <v>OK</v>
       </c>
     </row>
     <row r="261">
       <c r="A261" t="str">
-        <v>group-menu-milne-library</v>
+        <v>group-menu-sofi</v>
       </c>
       <c r="B261" t="str">
         <v>MENU</v>
       </c>
       <c r="C261" t="str">
-        <v>Fraser Hall Library                    [Menu ID: group-menu-milne-library]</v>
+        <v>Student Course Experience (SCE)                    [Menu ID: group-menu-sofi]</v>
       </c>
       <c r="D261" t="str">
-        <v>group-menu-milne-library                    [Term ID: 1703]</v>
+        <v>group-menu-sofi                    [Term ID: 1649]</v>
       </c>
       <c r="E261" t="str">
         <v>OK</v>
@@ -4838,16 +4838,16 @@
     </row>
     <row r="262">
       <c r="A262" t="str">
-        <v>group-menu-ming-mei-chang</v>
+        <v>group-menu-sponsored-research</v>
       </c>
       <c r="B262" t="str">
         <v>MENU</v>
       </c>
       <c r="C262" t="str">
-        <v>Ming-Mei Chang                    [Menu ID: group-menu-ming-mei-chang]</v>
+        <v>Sponsored Research                    [Menu ID: group-menu-sponsored-research]</v>
       </c>
       <c r="D262" t="str">
-        <v>group-menu-ming-mei-chang                    [Term ID: 1677]</v>
+        <v>group-menu-sponsored-research                    [Term ID: 1638]</v>
       </c>
       <c r="E262" t="str">
         <v>OK</v>
@@ -4855,64 +4855,64 @@
     </row>
     <row r="263">
       <c r="A263" t="str">
-        <v>group-menu-ming-mei-chang</v>
+        <v>group-menu-stitches-geneseo</v>
       </c>
       <c r="B263" t="str">
-        <v>ITEM_HREF</v>
+        <v>MENU</v>
       </c>
       <c r="C263" t="str">
-        <v>/sites/default/files/sites/chang/Western%20blot%20analysis.pdf</v>
+        <v>Stitches Geneseo                    [Menu ID: group-menu-stitches-geneseo]</v>
       </c>
       <c r="D263" t="str">
-        <v>/wp-content/uploads/2025/11/Western-blot-analysis.pdf</v>
+        <v/>
       </c>
       <c r="E263" t="str">
-        <v>❗ HREF Mismatch</v>
+        <v>Missing in WP</v>
       </c>
     </row>
     <row r="264">
       <c r="A264" t="str">
-        <v>group-menu-ming-mei-chang</v>
+        <v>group-menu-strategic-planning-gr</v>
       </c>
       <c r="B264" t="str">
-        <v>ITEM_HREF</v>
+        <v>MENU</v>
       </c>
       <c r="C264" t="str">
-        <v>/biology</v>
+        <v>Strategic Planning Group                    [Menu ID: group-menu-strategic-planning-gr]</v>
       </c>
       <c r="D264" t="str">
-        <v>/internal:/node/7097</v>
+        <v>group-menu-strategic-planning-gr                    [Term ID: 1700]</v>
       </c>
       <c r="E264" t="str">
-        <v>❗ HREF Mismatch</v>
+        <v>OK</v>
       </c>
     </row>
     <row r="265">
       <c r="A265" t="str">
-        <v>group-menu-minority-association-</v>
+        <v>group-menu-student-accounts</v>
       </c>
       <c r="B265" t="str">
         <v>MENU</v>
       </c>
       <c r="C265" t="str">
-        <v>Minority Association for PreHealth                    [Menu ID: group-menu-minority-association-]</v>
+        <v>Student Accounts                    [Menu ID: group-menu-student-accounts]</v>
       </c>
       <c r="D265" t="str">
-        <v/>
+        <v>group-menu-student-accounts                    [Term ID: 1650]</v>
       </c>
       <c r="E265" t="str">
-        <v>Missing in WP</v>
+        <v>OK</v>
       </c>
     </row>
     <row r="266">
       <c r="A266" t="str">
-        <v>group-menu-mlk</v>
+        <v>group-menu-student-advocate-resp</v>
       </c>
       <c r="B266" t="str">
         <v>MENU</v>
       </c>
       <c r="C266" t="str">
-        <v>mlk                    [Menu ID: group-menu-mlk]</v>
+        <v>Student Advocate Response Team                    [Menu ID: group-menu-student-advocate-resp]</v>
       </c>
       <c r="D266" t="str">
         <v/>
@@ -4923,33 +4923,33 @@
     </row>
     <row r="267">
       <c r="A267" t="str">
-        <v>group-menu-msche-accreditation</v>
+        <v>group-menu-student-and-campus-li</v>
       </c>
       <c r="B267" t="str">
         <v>MENU</v>
       </c>
       <c r="C267" t="str">
-        <v>MSCHE Accreditation                    [Menu ID: group-menu-msche-accreditation]</v>
+        <v>Student and Campus Life Administrative Team                    [Menu ID: group-menu-student-and-campus-li]</v>
       </c>
       <c r="D267" t="str">
-        <v>group-menu-msche-accreditation                    [Term ID: 1731]</v>
+        <v/>
       </c>
       <c r="E267" t="str">
-        <v>OK</v>
+        <v>Missing in WP</v>
       </c>
     </row>
     <row r="268">
       <c r="A268" t="str">
-        <v>group-menu-multicultural-program</v>
+        <v>group-menu-student-association</v>
       </c>
       <c r="B268" t="str">
         <v>MENU</v>
       </c>
       <c r="C268" t="str">
-        <v>Multicultural Affairs                    [Menu ID: group-menu-multicultural-program]</v>
+        <v>Student Association                    [Menu ID: group-menu-student-association]</v>
       </c>
       <c r="D268" t="str">
-        <v>group-menu-multicultural-program                    [Term ID: 1550]</v>
+        <v>group-menu-student-association                    [Term ID: 1544]</v>
       </c>
       <c r="E268" t="str">
         <v>OK</v>
@@ -4957,50 +4957,50 @@
     </row>
     <row r="269">
       <c r="A269" t="str">
-        <v>group-menu-multicultural-program</v>
+        <v>group-menu-student-conduct-commu</v>
       </c>
       <c r="B269" t="str">
-        <v>ITEM_HREF</v>
+        <v>MENU</v>
       </c>
       <c r="C269" t="str">
-        <v>/lgbtq</v>
+        <v>Student Conduct &amp; Community Standards                    [Menu ID: group-menu-student-conduct-commu]</v>
       </c>
       <c r="D269" t="str">
-        <v>/lgbtq/lgbtq-life-0</v>
+        <v>group-menu-student-conduct-commu                    [Term ID: 1536]</v>
       </c>
       <c r="E269" t="str">
-        <v>❗ HREF Mismatch</v>
+        <v>OK</v>
       </c>
     </row>
     <row r="270">
       <c r="A270" t="str">
-        <v>group-menu-multicultural-program</v>
+        <v>group-menu-student-employment</v>
       </c>
       <c r="B270" t="str">
-        <v>ITEM_HREF</v>
+        <v>MENU</v>
       </c>
       <c r="C270" t="str">
-        <v>/ir/fact_book</v>
+        <v>Student Employment                    [Menu ID: group-menu-student-employment]</v>
       </c>
       <c r="D270" t="str">
-        <v>/internal:/ir/fact_book</v>
+        <v>group-menu-student-employment                    [Term ID: 1729]</v>
       </c>
       <c r="E270" t="str">
-        <v>❗ HREF Mismatch</v>
+        <v>OK</v>
       </c>
     </row>
     <row r="271">
       <c r="A271" t="str">
-        <v>group-menu-mycourses</v>
+        <v>group-menu-student-gateway</v>
       </c>
       <c r="B271" t="str">
         <v>MENU</v>
       </c>
       <c r="C271" t="str">
-        <v>myCourses                    [Menu ID: group-menu-mycourses]</v>
+        <v>Student Gateway                    [Menu ID: group-menu-student-gateway]</v>
       </c>
       <c r="D271" t="str">
-        <v>group-menu-mycourses                    [Term ID: 1611]</v>
+        <v>group-menu-student-gateway                    [Term ID: 1704]</v>
       </c>
       <c r="E271" t="str">
         <v>OK</v>
@@ -5008,101 +5008,101 @@
     </row>
     <row r="272">
       <c r="A272" t="str">
-        <v>group-menu-mycourses</v>
+        <v>group-menu-student-handbook</v>
       </c>
       <c r="B272" t="str">
-        <v>ITEM_HREF</v>
+        <v>MENU</v>
       </c>
       <c r="C272" t="str">
-        <v>https://mycourses.geneseo.edu</v>
+        <v>Student Handbook                    [Menu ID: group-menu-student-handbook]</v>
       </c>
       <c r="D272" t="str">
-        <v/>
+        <v>group-menu-student-handbook                    [Term ID: 1660]</v>
       </c>
       <c r="E272" t="str">
-        <v>❗ HREF Mismatch</v>
+        <v>OK</v>
       </c>
     </row>
     <row r="273">
       <c r="A273" t="str">
-        <v>group-menu-native-american-studi</v>
+        <v>group-menu-student-handbook</v>
       </c>
       <c r="B273" t="str">
-        <v>MENU</v>
+        <v>ITEM_TITLE</v>
       </c>
       <c r="C273" t="str">
-        <v>Native American Studies                    [Menu ID: group-menu-native-american-studi]</v>
+        <v>What Faculty Should Know about FERPA</v>
       </c>
       <c r="D273" t="str">
-        <v>group-menu-native-american-studi                    [Term ID: 1692]</v>
+        <v/>
       </c>
       <c r="E273" t="str">
-        <v>OK</v>
+        <v>Missing in WP</v>
       </c>
     </row>
     <row r="274">
       <c r="A274" t="str">
-        <v>group-menu-ncate</v>
+        <v>group-menu-student-handbook</v>
       </c>
       <c r="B274" t="str">
-        <v>MENU</v>
+        <v>ITEM_HREF</v>
       </c>
       <c r="C274" t="str">
-        <v>CAEP Accreditation                    [Menu ID: group-menu-ncate]</v>
+        <v>/sites/default/files/sites/community/FERPA_facultystaff_2014.pdf</v>
       </c>
       <c r="D274" t="str">
-        <v>group-menu-ncate                    [Term ID: 1673]</v>
+        <v/>
       </c>
       <c r="E274" t="str">
-        <v>OK</v>
+        <v>Missing in WP</v>
       </c>
     </row>
     <row r="275">
       <c r="A275" t="str">
-        <v>group-menu-ncate</v>
+        <v>group-menu-student-handbook</v>
       </c>
       <c r="B275" t="str">
-        <v>ITEM_HREF</v>
+        <v>ITEM_TITLE</v>
       </c>
       <c r="C275" t="str">
-        <v>/news_events/school-education-receives-ncate-reaccreditation</v>
+        <v>Good Samaritan Policy</v>
       </c>
       <c r="D275" t="str">
-        <v>/internal:/news_events/school-education-receives-ncate-reaccreditation</v>
+        <v/>
       </c>
       <c r="E275" t="str">
-        <v>❗ HREF Mismatch</v>
+        <v>Missing in WP</v>
       </c>
     </row>
     <row r="276">
       <c r="A276" t="str">
-        <v>group-menu-ncate</v>
+        <v>group-menu-student-handbook</v>
       </c>
       <c r="B276" t="str">
         <v>ITEM_HREF</v>
       </c>
       <c r="C276" t="str">
-        <v>/ncate/accreditation-process</v>
+        <v>/sites/default/files/sites/handbook/Good%20Samaritan%20Policy%20Final.pdf</v>
       </c>
       <c r="D276" t="str">
-        <v>/education/accreditation-process</v>
+        <v/>
       </c>
       <c r="E276" t="str">
-        <v>❗ HREF Mismatch</v>
+        <v>Missing in WP</v>
       </c>
     </row>
     <row r="277">
       <c r="A277" t="str">
-        <v>group-menu-neh-seminar</v>
+        <v>group-menu-student-life</v>
       </c>
       <c r="B277" t="str">
         <v>MENU</v>
       </c>
       <c r="C277" t="str">
-        <v>NEH Seminar                    [Menu ID: group-menu-neh-seminar]</v>
+        <v>Student Life                    [Menu ID: group-menu-student-life]</v>
       </c>
       <c r="D277" t="str">
-        <v>group-menu-neh-seminar                    [Term ID: 1620]</v>
+        <v>group-menu-student-life                    [Term ID: 1530]</v>
       </c>
       <c r="E277" t="str">
         <v>OK</v>
@@ -5110,33 +5110,33 @@
     </row>
     <row r="278">
       <c r="A278" t="str">
-        <v>group-menu-neh-seminar</v>
+        <v>group-menu-study-abroad</v>
       </c>
       <c r="B278" t="str">
-        <v>ITEM_HREF</v>
+        <v>MENU</v>
       </c>
       <c r="C278" t="str">
-        <v>/sites/default/files/sites/neh/NEH%202015%20Daily%20Schedule.pdf</v>
+        <v>Study Abroad                    [Menu ID: group-menu-study-abroad]</v>
       </c>
       <c r="D278" t="str">
-        <v>/wp-content/uploads/2025/11/2015-School-Teacher-Application-Information-and-Instructions-Copy.pdf</v>
+        <v>group-menu-study-abroad                    [Term ID: 1567]</v>
       </c>
       <c r="E278" t="str">
-        <v>❗ HREF Mismatch</v>
+        <v>OK</v>
       </c>
     </row>
     <row r="279">
       <c r="A279" t="str">
-        <v>group-menu-neuroscience</v>
+        <v>group-menu-summer-sessions</v>
       </c>
       <c r="B279" t="str">
         <v>MENU</v>
       </c>
       <c r="C279" t="str">
-        <v>Neuroscience                    [Menu ID: group-menu-neuroscience]</v>
+        <v>Summer Sessions                    [Menu ID: group-menu-summer-sessions]</v>
       </c>
       <c r="D279" t="str">
-        <v>group-menu-neuroscience                    [Term ID: 1687]</v>
+        <v>group-menu-summer-sessions                    [Term ID: 1721]</v>
       </c>
       <c r="E279" t="str">
         <v>OK</v>
@@ -5144,13 +5144,13 @@
     </row>
     <row r="280">
       <c r="A280" t="str">
-        <v>group-menu-new-student-programs</v>
+        <v>group-menu-suny-geneseo-cheerlea</v>
       </c>
       <c r="B280" t="str">
         <v>MENU</v>
       </c>
       <c r="C280" t="str">
-        <v>More Information                     [Menu ID: group-menu-new-student-programs]</v>
+        <v>Geneseo Cheerleading                    [Menu ID: group-menu-suny-geneseo-cheerlea]</v>
       </c>
       <c r="D280" t="str">
         <v/>
@@ -5161,16 +5161,16 @@
     </row>
     <row r="281">
       <c r="A281" t="str">
-        <v>group-menu-noyce-scholarship-pro</v>
+        <v>group-menu-support-geneseo</v>
       </c>
       <c r="B281" t="str">
         <v>MENU</v>
       </c>
       <c r="C281" t="str">
-        <v>Noyce Scholarship Program                    [Menu ID: group-menu-noyce-scholarship-pro]</v>
+        <v>Support Geneseo                    [Menu ID: group-menu-support-geneseo]</v>
       </c>
       <c r="D281" t="str">
-        <v>group-menu-noyce-scholarship-pro                    [Term ID: 1645]</v>
+        <v>group-menu-support-geneseo                    [Term ID: 1542]</v>
       </c>
       <c r="E281" t="str">
         <v>OK</v>
@@ -5178,16 +5178,16 @@
     </row>
     <row r="282">
       <c r="A282" t="str">
-        <v>group-menu-nuclear-physics</v>
+        <v>group-menu-sustainability</v>
       </c>
       <c r="B282" t="str">
         <v>MENU</v>
       </c>
       <c r="C282" t="str">
-        <v>Nuclear Physics                    [Menu ID: group-menu-nuclear-physics]</v>
+        <v>Sustainability                    [Menu ID: group-menu-sustainability]</v>
       </c>
       <c r="D282" t="str">
-        <v>group-menu-nuclear-physics                    [Term ID: 1664]</v>
+        <v>group-menu-sustainability                    [Term ID: 1570]</v>
       </c>
       <c r="E282" t="str">
         <v>OK</v>
@@ -5195,16 +5195,16 @@
     </row>
     <row r="283">
       <c r="A283" t="str">
-        <v>group-menu-ny-alert</v>
+        <v>group-menu-teaching-and-learning</v>
       </c>
       <c r="B283" t="str">
         <v>MENU</v>
       </c>
       <c r="C283" t="str">
-        <v>NY Alert                    [Menu ID: group-menu-ny-alert]</v>
+        <v>Teaching and Learning Center                    [Menu ID: group-menu-teaching-and-learning]</v>
       </c>
       <c r="D283" t="str">
-        <v>group-menu-ny-alert                    [Term ID: 1710]</v>
+        <v>group-menu-teaching-and-learning                    [Term ID: 1633]</v>
       </c>
       <c r="E283" t="str">
         <v>OK</v>
@@ -5212,13 +5212,13 @@
     </row>
     <row r="284">
       <c r="A284" t="str">
-        <v>group-menu-nyalert</v>
+        <v>group-menu-tedx-suny-geneseo</v>
       </c>
       <c r="B284" t="str">
         <v>MENU</v>
       </c>
       <c r="C284" t="str">
-        <v>nyalert                    [Menu ID: group-menu-nyalert]</v>
+        <v>TEDx SUNY Geneseo                    [Menu ID: group-menu-tedx-suny-geneseo]</v>
       </c>
       <c r="D284" t="str">
         <v/>
@@ -5229,16 +5229,16 @@
     </row>
     <row r="285">
       <c r="A285" t="str">
-        <v>group-menu-nysacac</v>
+        <v>group-menu-testing-center</v>
       </c>
       <c r="B285" t="str">
         <v>MENU</v>
       </c>
       <c r="C285" t="str">
-        <v>NYSACAC                    [Menu ID: group-menu-nysacac]</v>
+        <v>Testing Center                    [Menu ID: group-menu-testing-center]</v>
       </c>
       <c r="D285" t="str">
-        <v>group-menu-nysacac                    [Term ID: 1727]</v>
+        <v>group-menu-testing-center                    [Term ID: 1668]</v>
       </c>
       <c r="E285" t="str">
         <v>OK</v>
@@ -5246,33 +5246,33 @@
     </row>
     <row r="286">
       <c r="A286" t="str">
-        <v>group-menu-nysacac</v>
+        <v>group-menu-the-l-i-v-e-s-program</v>
       </c>
       <c r="B286" t="str">
-        <v>ITEM_HREF</v>
+        <v>MENU</v>
       </c>
       <c r="C286" t="str">
-        <v>https://nysacac.memberclicks.net/index.php?option=com_mc&amp;view=mc&amp;Itemid=96</v>
+        <v>The LIVES Program                    [Menu ID: group-menu-the-l-i-v-e-s-program]</v>
       </c>
       <c r="D286" t="str">
-        <v/>
+        <v>group-menu-the-l-i-v-e-s-program                    [Term ID: 1608]</v>
       </c>
       <c r="E286" t="str">
-        <v>❗ HREF Mismatch</v>
+        <v>OK</v>
       </c>
     </row>
     <row r="287">
       <c r="A287" t="str">
-        <v>group-menu-off-campus-living</v>
+        <v>group-menu-the-national-honor-so</v>
       </c>
       <c r="B287" t="str">
         <v>MENU</v>
       </c>
       <c r="C287" t="str">
-        <v>Off-Campus Living                    [Menu ID: group-menu-off-campus-living]</v>
+        <v>The National Honor Society in Psychology                    [Menu ID: group-menu-the-national-honor-so]</v>
       </c>
       <c r="D287" t="str">
-        <v>group-menu-off-campus-living                    [Term ID: 1646]</v>
+        <v>group-menu-the-national-honor-so                    [Term ID: 1599]</v>
       </c>
       <c r="E287" t="str">
         <v>OK</v>
@@ -5280,33 +5280,33 @@
     </row>
     <row r="288">
       <c r="A288" t="str">
-        <v>group-menu-office-of-the-dean</v>
+        <v>group-menu-theatre-dance</v>
       </c>
       <c r="B288" t="str">
         <v>MENU</v>
       </c>
       <c r="C288" t="str">
-        <v>Office of the Advising Director                    [Menu ID: group-menu-office-of-the-dean]</v>
+        <v>Theatre &amp; Dance                    [Menu ID: group-menu-theatre-dance]</v>
       </c>
       <c r="D288" t="str">
-        <v>group-menu-office-of-the-dean                    [Term ID: 1723]</v>
+        <v/>
       </c>
       <c r="E288" t="str">
-        <v>OK</v>
+        <v>Missing in WP</v>
       </c>
     </row>
     <row r="289">
       <c r="A289" t="str">
-        <v>group-menu-office-of-the-preside</v>
+        <v>group-menu-thomas-greenfield</v>
       </c>
       <c r="B289" t="str">
         <v>MENU</v>
       </c>
       <c r="C289" t="str">
-        <v>Office of the President                    [Menu ID: group-menu-office-of-the-preside]</v>
+        <v>Thomas Greenfield                    [Menu ID: group-menu-thomas-greenfield]</v>
       </c>
       <c r="D289" t="str">
-        <v>group-menu-office-of-the-preside                    [Term ID: 1529]</v>
+        <v>group-menu-thomas-greenfield                    [Term ID: 1685]</v>
       </c>
       <c r="E289" t="str">
         <v>OK</v>
@@ -5314,64 +5314,64 @@
     </row>
     <row r="290">
       <c r="A290" t="str">
-        <v>group-menu-office-of-the-preside</v>
+        <v>group-menu-thomas-greenfield</v>
       </c>
       <c r="B290" t="str">
-        <v>ITEM_HREF</v>
+        <v>ITEM_TITLE</v>
       </c>
       <c r="C290" t="str">
-        <v>/president/suny-geneseo-advancing-our-instutional-mission-aim-awards</v>
+        <v>Musician's Resume</v>
       </c>
       <c r="D290" t="str">
-        <v>/president/suny-geneseo-advancing-our-institutional-mission-aim-awards</v>
+        <v/>
       </c>
       <c r="E290" t="str">
-        <v>❗ HREF Mismatch</v>
+        <v>Missing in WP</v>
       </c>
     </row>
     <row r="291">
       <c r="A291" t="str">
-        <v>group-menu-office-of-the-provost</v>
+        <v>group-menu-thomas-greenfield</v>
       </c>
       <c r="B291" t="str">
-        <v>MENU</v>
+        <v>ITEM_HREF</v>
       </c>
       <c r="C291" t="str">
-        <v>Office of the Provost                    [Menu ID: group-menu-office-of-the-provost]</v>
+        <v>/tag/music</v>
       </c>
       <c r="D291" t="str">
-        <v>group-menu-office-of-the-provost                    [Term ID: 1676]</v>
+        <v/>
       </c>
       <c r="E291" t="str">
-        <v>OK</v>
+        <v>Missing in WP</v>
       </c>
     </row>
     <row r="292">
       <c r="A292" t="str">
-        <v>group-menu-office-of-the-provost</v>
+        <v>group-menu-title-ix</v>
       </c>
       <c r="B292" t="str">
-        <v>ITEM_HREF</v>
+        <v>MENU</v>
       </c>
       <c r="C292" t="str">
-        <v>/provost/PRODiG-plus</v>
+        <v>Title IX &amp; Equity Compliance                    [Menu ID: group-menu-title-ix]</v>
       </c>
       <c r="D292" t="str">
-        <v>/provost/prodig-plus</v>
+        <v>group-menu-title-ix                    [Term ID: 1603]</v>
       </c>
       <c r="E292" t="str">
-        <v>❗ HREF Mismatch</v>
+        <v>OK</v>
       </c>
     </row>
     <row r="293">
       <c r="A293" t="str">
-        <v>group-menu-offices</v>
+        <v>group-menu-title-ix</v>
       </c>
       <c r="B293" t="str">
-        <v>MENU</v>
+        <v>CHILD_TITLE</v>
       </c>
       <c r="C293" t="str">
-        <v>Offices                    [Menu ID: group-menu-offices]</v>
+        <v>Love Shouldn't Hurt Campaign</v>
       </c>
       <c r="D293" t="str">
         <v/>
@@ -5382,64 +5382,64 @@
     </row>
     <row r="294">
       <c r="A294" t="str">
-        <v>group-menu-oip</v>
+        <v>group-menu-title-ix</v>
       </c>
       <c r="B294" t="str">
-        <v>MENU</v>
+        <v>CHILD_HREF</v>
       </c>
       <c r="C294" t="str">
-        <v>Center for Global Engagement                    [Menu ID: group-menu-oip]</v>
+        <v>/titleix/love-shouldnt-hurt-campaign</v>
       </c>
       <c r="D294" t="str">
-        <v>group-menu-oip                    [Term ID: 1665]</v>
+        <v/>
       </c>
       <c r="E294" t="str">
-        <v>OK</v>
+        <v>Missing in WP</v>
       </c>
     </row>
     <row r="295">
       <c r="A295" t="str">
-        <v>group-menu-oip</v>
+        <v>group-menu-title-ix</v>
       </c>
       <c r="B295" t="str">
-        <v>ITEM_HREF</v>
+        <v>ITEM_TITLE</v>
       </c>
       <c r="C295" t="str">
-        <v>http://geneseo.edu/study_abroad</v>
+        <v>Pregnant and Parenting Students' Accommodations</v>
       </c>
       <c r="D295" t="str">
-        <v>/study_abroad</v>
+        <v/>
       </c>
       <c r="E295" t="str">
-        <v>❗ HREF Mismatch</v>
+        <v>Missing in WP</v>
       </c>
     </row>
     <row r="296">
       <c r="A296" t="str">
-        <v>group-menu-oip</v>
+        <v>group-menu-title-ix</v>
       </c>
       <c r="B296" t="str">
         <v>ITEM_HREF</v>
       </c>
       <c r="C296" t="str">
-        <v>/iss</v>
+        <v>/titleix/pregnant-and-parenting-students-accommodations</v>
       </c>
       <c r="D296" t="str">
-        <v>/internal:/iss</v>
+        <v/>
       </c>
       <c r="E296" t="str">
-        <v>❗ HREF Mismatch</v>
+        <v>Missing in WP</v>
       </c>
     </row>
     <row r="297">
       <c r="A297" t="str">
-        <v>group-menu-orlando-furioso</v>
+        <v>group-menu-travel</v>
       </c>
       <c r="B297" t="str">
         <v>MENU</v>
       </c>
       <c r="C297" t="str">
-        <v>Orlando furioso                    [Menu ID: group-menu-orlando-furioso]</v>
+        <v>Travel                    [Menu ID: group-menu-travel]</v>
       </c>
       <c r="D297" t="str">
         <v/>
@@ -5450,16 +5450,16 @@
     </row>
     <row r="298">
       <c r="A298" t="str">
-        <v>group-menu-parents</v>
+        <v>group-menu-tri-beta</v>
       </c>
       <c r="B298" t="str">
         <v>MENU</v>
       </c>
       <c r="C298" t="str">
-        <v>Parent and Family Resources                    [Menu ID: group-menu-parents]</v>
+        <v>Tri-Beta                    [Menu ID: group-menu-tri-beta]</v>
       </c>
       <c r="D298" t="str">
-        <v>group-menu-parents                    [Term ID: 1701]</v>
+        <v>group-menu-tri-beta                    [Term ID: 1625]</v>
       </c>
       <c r="E298" t="str">
         <v>OK</v>
@@ -5467,16 +5467,16 @@
     </row>
     <row r="299">
       <c r="A299" t="str">
-        <v>group-menu-parking-transportatio</v>
+        <v>group-menu-undergraduate-alumni-</v>
       </c>
       <c r="B299" t="str">
         <v>MENU</v>
       </c>
       <c r="C299" t="str">
-        <v>Parking &amp; Transportation                    [Menu ID: group-menu-parking-transportatio]</v>
+        <v>Undergraduate Alumni Association                    [Menu ID: group-menu-undergraduate-alumni-]</v>
       </c>
       <c r="D299" t="str">
-        <v>group-menu-parking-transportatio                    [Term ID: 1667]</v>
+        <v>group-menu-undergraduate-alumni-                    [Term ID: 1637]</v>
       </c>
       <c r="E299" t="str">
         <v>OK</v>
@@ -5484,16 +5484,16 @@
     </row>
     <row r="300">
       <c r="A300" t="str">
-        <v>group-menu-pathways</v>
+        <v>group-menu-undergraduate-researc</v>
       </c>
       <c r="B300" t="str">
         <v>MENU</v>
       </c>
       <c r="C300" t="str">
-        <v>Pathways                    [Menu ID: group-menu-pathways]</v>
+        <v>Undergraduate Research                    [Menu ID: group-menu-undergraduate-researc]</v>
       </c>
       <c r="D300" t="str">
-        <v>group-menu-pathways                    [Term ID: 1647]</v>
+        <v>group-menu-undergraduate-researc                    [Term ID: 1559]</v>
       </c>
       <c r="E300" t="str">
         <v>OK</v>
@@ -5501,33 +5501,33 @@
     </row>
     <row r="301">
       <c r="A301" t="str">
-        <v>group-menu-peace-action-geneseo</v>
+        <v>group-menu-ventureworks</v>
       </c>
       <c r="B301" t="str">
         <v>MENU</v>
       </c>
       <c r="C301" t="str">
-        <v>Peace Action Geneseo                    [Menu ID: group-menu-peace-action-geneseo]</v>
+        <v>VentureWorks                    [Menu ID: group-menu-ventureworks]</v>
       </c>
       <c r="D301" t="str">
-        <v/>
+        <v>group-menu-ventureworks                    [Term ID: 1540]</v>
       </c>
       <c r="E301" t="str">
-        <v>Missing in WP</v>
+        <v>OK</v>
       </c>
     </row>
     <row r="302">
       <c r="A302" t="str">
-        <v>group-menu-peace-poetry</v>
+        <v>group-menu-veterans</v>
       </c>
       <c r="B302" t="str">
         <v>MENU</v>
       </c>
       <c r="C302" t="str">
-        <v>Peace Poetry                    [Menu ID: group-menu-peace-poetry]</v>
+        <v>Veterans                    [Menu ID: group-menu-veterans]</v>
       </c>
       <c r="D302" t="str">
-        <v>group-menu-peace-poetry                    [Term ID: 1641]</v>
+        <v>group-menu-veterans                    [Term ID: 1616]</v>
       </c>
       <c r="E302" t="str">
         <v>OK</v>
@@ -5535,64 +5535,64 @@
     </row>
     <row r="303">
       <c r="A303" t="str">
-        <v>group-menu-pep-band</v>
+        <v>group-menu-volunteer-center</v>
       </c>
       <c r="B303" t="str">
         <v>MENU</v>
       </c>
       <c r="C303" t="str">
-        <v>Pep Band                    [Menu ID: group-menu-pep-band]</v>
+        <v>Student Volunteerism and Community Engagement                     [Menu ID: group-menu-volunteer-center]</v>
       </c>
       <c r="D303" t="str">
-        <v/>
+        <v>group-menu-volunteer-center                    [Term ID: 1592]</v>
       </c>
       <c r="E303" t="str">
-        <v>Missing in WP</v>
+        <v>OK</v>
       </c>
     </row>
     <row r="304">
       <c r="A304" t="str">
-        <v>group-menu-phi-beta-kappa</v>
+        <v>group-menu-volunteer-center</v>
       </c>
       <c r="B304" t="str">
-        <v>MENU</v>
+        <v>ITEM_TITLE</v>
       </c>
       <c r="C304" t="str">
-        <v>Phi Beta Kappa                    [Menu ID: group-menu-phi-beta-kappa]</v>
+        <v>Knights' First Day of Service</v>
       </c>
       <c r="D304" t="str">
-        <v>group-menu-phi-beta-kappa                    [Term ID: 1618]</v>
+        <v/>
       </c>
       <c r="E304" t="str">
-        <v>OK</v>
+        <v>Missing in WP</v>
       </c>
     </row>
     <row r="305">
       <c r="A305" t="str">
-        <v>group-menu-phi-beta-kappa</v>
+        <v>group-menu-volunteer-center</v>
       </c>
       <c r="B305" t="str">
         <v>ITEM_HREF</v>
       </c>
       <c r="C305" t="str">
-        <v>http://pbk.org</v>
+        <v>/volunteer_center/knights-first-day-service</v>
       </c>
       <c r="D305" t="str">
         <v/>
       </c>
       <c r="E305" t="str">
-        <v>❗ HREF Mismatch</v>
+        <v>Missing in WP</v>
       </c>
     </row>
     <row r="306">
       <c r="A306" t="str">
-        <v>group-menu-phi-beta-lambda</v>
+        <v>group-menu-volunteer-center</v>
       </c>
       <c r="B306" t="str">
-        <v>MENU</v>
+        <v>ITEM_TITLE</v>
       </c>
       <c r="C306" t="str">
-        <v>Phi Beta Lambda                    [Menu ID: group-menu-phi-beta-lambda]</v>
+        <v>Knights' Harvest Pantry</v>
       </c>
       <c r="D306" t="str">
         <v/>
@@ -5603,13 +5603,13 @@
     </row>
     <row r="307">
       <c r="A307" t="str">
-        <v>group-menu-phi-eta-sigma</v>
+        <v>group-menu-volunteer-center</v>
       </c>
       <c r="B307" t="str">
-        <v>MENU</v>
+        <v>ITEM_HREF</v>
       </c>
       <c r="C307" t="str">
-        <v>Phi Eta Sigma                    [Menu ID: group-menu-phi-eta-sigma]</v>
+        <v>/volunteer_center/knights-harvest-pantry</v>
       </c>
       <c r="D307" t="str">
         <v/>
@@ -5620,16 +5620,16 @@
     </row>
     <row r="308">
       <c r="A308" t="str">
-        <v>group-menu-philosophy</v>
+        <v>group-menu-vote</v>
       </c>
       <c r="B308" t="str">
         <v>MENU</v>
       </c>
       <c r="C308" t="str">
-        <v>Philosophy                    [Menu ID: group-menu-philosophy]</v>
+        <v>Vote                    [Menu ID: group-menu-vote]</v>
       </c>
       <c r="D308" t="str">
-        <v>group-menu-philosophy                    [Term ID: 1541]</v>
+        <v>group-menu-vote                    [Term ID: 1672]</v>
       </c>
       <c r="E308" t="str">
         <v>OK</v>
@@ -5637,33 +5637,33 @@
     </row>
     <row r="309">
       <c r="A309" t="str">
-        <v>group-menu-philosophy</v>
+        <v>group-menu-wadsworth-auditorium</v>
       </c>
       <c r="B309" t="str">
-        <v>ITEM_HREF</v>
+        <v>MENU</v>
       </c>
       <c r="C309" t="str">
-        <v>https://securelb.imodules.com/s/1648/rd/interior.aspx?sid=1648&amp;gid=2&amp;pgid=507&amp;cid=1179&amp;dids=84</v>
+        <v>Wadsworth Auditorium                    [Menu ID: group-menu-wadsworth-auditorium]</v>
       </c>
       <c r="D309" t="str">
-        <v>https://securelb.imodules.com/s/1648/lg24/form.aspx?sid=1648&amp;gid=2&amp;pgid=507&amp;cid=1179&amp;dids=84</v>
+        <v>group-menu-wadsworth-auditorium                    [Term ID: 1651]</v>
       </c>
       <c r="E309" t="str">
-        <v>❗ HREF Mismatch</v>
+        <v>OK</v>
       </c>
     </row>
     <row r="310">
       <c r="A310" t="str">
-        <v>group-menu-physics-astronomy</v>
+        <v>group-menu-weeks-of-welcome</v>
       </c>
       <c r="B310" t="str">
         <v>MENU</v>
       </c>
       <c r="C310" t="str">
-        <v>Physics &amp; Astronomy                    [Menu ID: group-menu-physics-astronomy]</v>
+        <v>New Student Orientation                    [Menu ID: group-menu-weeks-of-welcome]</v>
       </c>
       <c r="D310" t="str">
-        <v>group-menu-physics-astronomy                    [Term ID: 1557]</v>
+        <v>group-menu-weeks-of-welcome                    [Term ID: 1605]</v>
       </c>
       <c r="E310" t="str">
         <v>OK</v>
@@ -5671,135 +5671,135 @@
     </row>
     <row r="311">
       <c r="A311" t="str">
-        <v>group-menu-physics-astronomy</v>
+        <v>group-menu-weeks-of-welcome</v>
       </c>
       <c r="B311" t="str">
-        <v>ITEM_HREF</v>
+        <v>MENU</v>
       </c>
       <c r="C311" t="str">
-        <v>/physics/PLC</v>
+        <v>Weeks of Welcome                    [Menu ID: group-menu-weeks-of-welcome-0]</v>
       </c>
       <c r="D311" t="str">
-        <v>/physics/plc</v>
+        <v>group-menu-weeks-of-welcome                    [Term ID: 1605]</v>
       </c>
       <c r="E311" t="str">
-        <v>❗ HREF Mismatch</v>
+        <v>OK</v>
       </c>
     </row>
     <row r="312">
       <c r="A312" t="str">
-        <v>group-menu-physics-astronomy</v>
+        <v>group-menu-winter-guard</v>
       </c>
       <c r="B312" t="str">
-        <v>ITEM_HREF</v>
+        <v>MENU</v>
       </c>
       <c r="C312" t="str">
-        <v>/physics/department-physics-astronomy-news</v>
+        <v>Winter Guard                    [Menu ID: group-menu-winter-guard]</v>
       </c>
       <c r="D312" t="str">
-        <v>/entity:node/150571</v>
+        <v/>
       </c>
       <c r="E312" t="str">
-        <v>❗ HREF Mismatch</v>
+        <v>Missing in WP</v>
       </c>
     </row>
     <row r="313">
       <c r="A313" t="str">
-        <v>group-menu-phystec-geneseo</v>
+        <v>group-menu-women-s-action-coalit</v>
       </c>
       <c r="B313" t="str">
         <v>MENU</v>
       </c>
       <c r="C313" t="str">
-        <v>PhysTEC Geneseo                    [Menu ID: group-menu-phystec-geneseo]</v>
+        <v>Women's Action Coalition                    [Menu ID: group-menu-women-s-action-coalit]</v>
       </c>
       <c r="D313" t="str">
-        <v>group-menu-phystec-geneseo                    [Term ID: 1602]</v>
+        <v/>
       </c>
       <c r="E313" t="str">
-        <v>OK</v>
+        <v>Missing in WP</v>
       </c>
     </row>
     <row r="314">
       <c r="A314" t="str">
-        <v>group-menu-police</v>
+        <v>group-menu-women-s-ice-hockey</v>
       </c>
       <c r="B314" t="str">
         <v>MENU</v>
       </c>
       <c r="C314" t="str">
-        <v>Police                    [Menu ID: group-menu-police]</v>
+        <v>Women's Ice Hockey                    [Menu ID: group-menu-women-s-ice-hockey]</v>
       </c>
       <c r="D314" t="str">
-        <v>group-menu-police                    [Term ID: 1666]</v>
+        <v/>
       </c>
       <c r="E314" t="str">
-        <v>OK</v>
+        <v>Missing in WP</v>
       </c>
     </row>
     <row r="315">
       <c r="A315" t="str">
-        <v>group-menu-police</v>
+        <v>group-menu-women-s-leadership-in</v>
       </c>
       <c r="B315" t="str">
-        <v>ITEM_HREF</v>
+        <v>MENU</v>
       </c>
       <c r="C315" t="str">
-        <v>/sites/default/files/documents/ASR%20%282024%29.pdf</v>
+        <v>Women's Leadership Institute                    [Menu ID: group-menu-women-s-leadership-in]</v>
       </c>
       <c r="D315" t="str">
-        <v>/wp-content/uploads/2025/11/ASR-2024.pdf</v>
+        <v>group-menu-women-s-leadership-in                    [Term ID: 1613]</v>
       </c>
       <c r="E315" t="str">
-        <v>❗ HREF Mismatch</v>
+        <v>OK</v>
       </c>
     </row>
     <row r="316">
       <c r="A316" t="str">
-        <v>group-menu-police</v>
+        <v>group-menu-women-s-rugby</v>
       </c>
       <c r="B316" t="str">
-        <v>ITEM_HREF</v>
+        <v>MENU</v>
       </c>
       <c r="C316" t="str">
-        <v>/police/request-records-or-reports</v>
+        <v>Women's Rugby                    [Menu ID: group-menu-women-s-rugby]</v>
       </c>
       <c r="D316" t="str">
-        <v>/police/university-police-forms-and-report-requests</v>
+        <v>group-menu-women-s-rugby                    [Term ID: 1624]</v>
       </c>
       <c r="E316" t="str">
-        <v>❗ HREF Mismatch</v>
+        <v>OK</v>
       </c>
     </row>
     <row r="317">
       <c r="A317" t="str">
-        <v>group-menu-police</v>
+        <v>group-menu-women-s-studies</v>
       </c>
       <c r="B317" t="str">
-        <v>ITEM_HREF</v>
+        <v>MENU</v>
       </c>
       <c r="C317" t="str">
-        <v>/geneseo.edu/police/staff</v>
+        <v>Women and Gender Studies                    [Menu ID: group-menu-women-s-studies]</v>
       </c>
       <c r="D317" t="str">
-        <v>/geneseoedu/police/staff</v>
+        <v>group-menu-women-s-studies                    [Term ID: 1582]</v>
       </c>
       <c r="E317" t="str">
-        <v>❗ HREF Mismatch</v>
+        <v>OK</v>
       </c>
     </row>
     <row r="318">
       <c r="A318" t="str">
-        <v>group-menu-political-science</v>
+        <v>group-menu-workout-center</v>
       </c>
       <c r="B318" t="str">
         <v>MENU</v>
       </c>
       <c r="C318" t="str">
-        <v>Political Science                    [Menu ID: group-menu-political-science]</v>
+        <v>Workout Center                    [Menu ID: group-menu-workout-center]</v>
       </c>
       <c r="D318" t="str">
-        <v>group-menu-political-science                    [Term ID: 1533]</v>
+        <v>group-menu-workout-center                    [Term ID: 1652]</v>
       </c>
       <c r="E318" t="str">
         <v>OK</v>
@@ -5807,305 +5807,305 @@
     </row>
     <row r="319">
       <c r="A319" t="str">
-        <v>group-menu-poll-everywhere</v>
+        <v>group-menu-xerox-center</v>
       </c>
       <c r="B319" t="str">
         <v>MENU</v>
       </c>
       <c r="C319" t="str">
-        <v>Poll Everywhere                    [Menu ID: group-menu-poll-everywhere]</v>
+        <v>Xerox Center                    [Menu ID: group-menu-xerox-center]</v>
       </c>
       <c r="D319" t="str">
-        <v>group-menu-poll-everywhere                    [Term ID: 1617]</v>
+        <v/>
       </c>
       <c r="E319" t="str">
-        <v>OK</v>
+        <v>Missing in WP</v>
       </c>
     </row>
     <row r="320">
       <c r="A320" t="str">
-        <v>group-menu-poll-everywhere</v>
+        <v>group-menu-yoga-club</v>
       </c>
       <c r="B320" t="str">
-        <v>ITEM_HREF</v>
+        <v>MENU</v>
       </c>
       <c r="C320" t="str">
-        <v>http://www.polleverywhere.com</v>
+        <v>Yoga Club                    [Menu ID: group-menu-yoga-club]</v>
       </c>
       <c r="D320" t="str">
-        <v/>
+        <v>group-menu-yoga-club                    [Term ID: 1636]</v>
       </c>
       <c r="E320" t="str">
-        <v>❗ HREF Mismatch</v>
+        <v>OK</v>
       </c>
     </row>
     <row r="321">
       <c r="A321" t="str">
-        <v>group-menu-poll-everywhere</v>
+        <v>group-menu-yoga-club</v>
       </c>
       <c r="B321" t="str">
-        <v>ITEM_HREF</v>
+        <v>ITEM_TITLE</v>
       </c>
       <c r="C321" t="str">
-        <v>http://www.polleverywhere.com/faq</v>
+        <v>Hall of Fame - Past Officers</v>
       </c>
       <c r="D321" t="str">
-        <v>/faq</v>
+        <v/>
       </c>
       <c r="E321" t="str">
-        <v>❗ HREF Mismatch</v>
+        <v>Missing in WP</v>
       </c>
     </row>
     <row r="322">
       <c r="A322" t="str">
-        <v>group-menu-power-of-physical-sci</v>
+        <v>group-menu-yoga-club</v>
       </c>
       <c r="B322" t="str">
-        <v>MENU</v>
+        <v>ITEM_HREF</v>
       </c>
       <c r="C322" t="str">
-        <v>Power of Physical Science                    [Menu ID: group-menu-power-of-physical-sci]</v>
+        <v>/yoga/hall-fame-past-officers</v>
       </c>
       <c r="D322" t="str">
-        <v>group-menu-power-of-physical-sci                    [Term ID: 1535]</v>
+        <v/>
       </c>
       <c r="E322" t="str">
-        <v>OK</v>
+        <v>Missing in WP</v>
       </c>
     </row>
     <row r="323">
       <c r="A323" t="str">
-        <v>group-menu-power-of-physical-sci</v>
+        <v>group-menu-yoga-club</v>
       </c>
       <c r="B323" t="str">
-        <v>ITEM_HREF</v>
+        <v>ITEM_TITLE</v>
       </c>
       <c r="C323" t="str">
-        <v>/pops/lesson-3</v>
+        <v>Instructor's Bio</v>
       </c>
       <c r="D323" t="str">
-        <v>/?page_id=42725</v>
+        <v/>
       </c>
       <c r="E323" t="str">
-        <v>❗ HREF Mismatch</v>
+        <v>Missing in WP</v>
       </c>
     </row>
     <row r="324">
       <c r="A324" t="str">
-        <v>group-menu-power-of-physical-sci</v>
+        <v>group-menu-yoga-club</v>
       </c>
       <c r="B324" t="str">
         <v>ITEM_HREF</v>
       </c>
       <c r="C324" t="str">
-        <v>/pops/power-physical-science</v>
+        <v>/yoga/instructors-bio</v>
       </c>
       <c r="D324" t="str">
-        <v>/?page_id=42723</v>
+        <v/>
       </c>
       <c r="E324" t="str">
-        <v>❗ HREF Mismatch</v>
+        <v>Missing in WP</v>
       </c>
     </row>
     <row r="325">
       <c r="A325" t="str">
-        <v>group-menu-power-of-physical-sci</v>
+        <v>group-menu-yoga-club</v>
       </c>
       <c r="B325" t="str">
-        <v>CHILD_HREF</v>
+        <v>ITEM_TITLE</v>
       </c>
       <c r="C325" t="str">
-        <v>/pops/lesson-2</v>
+        <v>Sefirot - Tree of Life</v>
       </c>
       <c r="D325" t="str">
-        <v>/?page_id=42724</v>
+        <v/>
       </c>
       <c r="E325" t="str">
-        <v>❗ HREF Mismatch</v>
+        <v>Missing in WP</v>
       </c>
     </row>
     <row r="326">
       <c r="A326" t="str">
-        <v>group-menu-power-of-physical-sci</v>
+        <v>group-menu-yoga-club</v>
       </c>
       <c r="B326" t="str">
-        <v>CHILD_HREF</v>
+        <v>ITEM_HREF</v>
       </c>
       <c r="C326" t="str">
-        <v>/pops/lesson-5</v>
+        <v>/yoga/sefirot-tree-life</v>
       </c>
       <c r="D326" t="str">
-        <v>/?page_id=42727</v>
+        <v/>
       </c>
       <c r="E326" t="str">
-        <v>❗ HREF Mismatch</v>
+        <v>Missing in WP</v>
       </c>
     </row>
     <row r="327">
       <c r="A327" t="str">
-        <v>group-menu-power-of-physical-sci</v>
+        <v>human-cognition-and-memory-lab</v>
       </c>
       <c r="B327" t="str">
-        <v>CHILD_HREF</v>
+        <v>MENU</v>
       </c>
       <c r="C327" t="str">
-        <v>/pops/lesson-6</v>
+        <v>Human Cognition and Memory Lab                    [Menu ID: human-cognition-and-memory-lab]</v>
       </c>
       <c r="D327" t="str">
-        <v>/?page_id=42728</v>
+        <v/>
       </c>
       <c r="E327" t="str">
-        <v>❗ HREF Mismatch</v>
+        <v>Missing in WP</v>
       </c>
     </row>
     <row r="328">
       <c r="A328" t="str">
-        <v>group-menu-power-of-physical-sci</v>
+        <v>human-development</v>
       </c>
       <c r="B328" t="str">
-        <v>CHILD_HREF</v>
+        <v>MENU</v>
       </c>
       <c r="C328" t="str">
-        <v>/pops/state-standards</v>
+        <v>Human Development                    [Menu ID: human-development]</v>
       </c>
       <c r="D328" t="str">
-        <v>/?page_id=42720</v>
+        <v/>
       </c>
       <c r="E328" t="str">
-        <v>❗ HREF Mismatch</v>
+        <v>Missing in WP</v>
       </c>
     </row>
     <row r="329">
       <c r="A329" t="str">
-        <v>group-menu-power-of-physical-sci</v>
+        <v>human-development-minor</v>
       </c>
       <c r="B329" t="str">
-        <v>ITEM_HREF</v>
+        <v>MENU</v>
       </c>
       <c r="C329" t="str">
-        <v>/pops/lesson-4</v>
+        <v>Human Development                    [Menu ID: human-development-minor]</v>
       </c>
       <c r="D329" t="str">
-        <v>/?page_id=42726</v>
+        <v>human-development-minor                    [Term ID: 1740]</v>
       </c>
       <c r="E329" t="str">
-        <v>❗ HREF Mismatch</v>
+        <v>OK</v>
       </c>
     </row>
     <row r="330">
       <c r="A330" t="str">
-        <v>group-menu-power-of-physical-sci</v>
+        <v>intersession</v>
       </c>
       <c r="B330" t="str">
-        <v>ITEM_HREF</v>
+        <v>MENU</v>
       </c>
       <c r="C330" t="str">
-        <v>/pops/drop-vs-launch</v>
+        <v>Intersession                    [Menu ID: intersession]</v>
       </c>
       <c r="D330" t="str">
-        <v>/?page_id=42721</v>
+        <v/>
       </c>
       <c r="E330" t="str">
-        <v>❗ HREF Mismatch</v>
+        <v>Missing in WP</v>
       </c>
     </row>
     <row r="331">
       <c r="A331" t="str">
-        <v>group-menu-power-of-physical-sci</v>
+        <v>join-us</v>
       </c>
       <c r="B331" t="str">
-        <v>ITEM_HREF</v>
+        <v>MENU</v>
       </c>
       <c r="C331" t="str">
-        <v>/pops/generator</v>
+        <v>Join Us                    [Menu ID: join-us]</v>
       </c>
       <c r="D331" t="str">
-        <v>/?page_id=42731</v>
+        <v>join-us                    [Term ID: 1736]</v>
       </c>
       <c r="E331" t="str">
-        <v>❗ HREF Mismatch</v>
+        <v>OK</v>
       </c>
     </row>
     <row r="332">
       <c r="A332" t="str">
-        <v>group-menu-power-of-physical-sci</v>
+        <v>mcnair</v>
       </c>
       <c r="B332" t="str">
-        <v>ITEM_HREF</v>
+        <v>MENU</v>
       </c>
       <c r="C332" t="str">
-        <v>/pops/partner-school-districts</v>
+        <v>McNair                    [Menu ID: mcnair]</v>
       </c>
       <c r="D332" t="str">
-        <v>/?page_id=42729</v>
+        <v>mcnair                    [Term ID: 1528]</v>
       </c>
       <c r="E332" t="str">
-        <v>❗ HREF Mismatch</v>
+        <v>OK</v>
       </c>
     </row>
     <row r="333">
       <c r="A333" t="str">
-        <v>group-menu-power-of-physical-sci</v>
+        <v>meet-the-global-cluster-profiles</v>
       </c>
       <c r="B333" t="str">
-        <v>ITEM_HREF</v>
+        <v>MENU</v>
       </c>
       <c r="C333" t="str">
-        <v>/pops/references</v>
+        <v>Meet the Global Cluster: Profiles of faculty                    [Menu ID: meet-the-global-cluster-profiles]</v>
       </c>
       <c r="D333" t="str">
-        <v>/?page_id=42730</v>
+        <v/>
       </c>
       <c r="E333" t="str">
-        <v>❗ HREF Mismatch</v>
+        <v>Missing in WP</v>
       </c>
     </row>
     <row r="334">
       <c r="A334" t="str">
-        <v>group-menu-pre-law</v>
+        <v>middle-states-self-study</v>
       </c>
       <c r="B334" t="str">
         <v>MENU</v>
       </c>
       <c r="C334" t="str">
-        <v>Pre-Law                    [Menu ID: group-menu-pre-law]</v>
+        <v>Middle States Self-Study                    [Menu ID: middle-states-self-study]</v>
       </c>
       <c r="D334" t="str">
-        <v>group-menu-pre-law                    [Term ID: 1689]</v>
+        <v/>
       </c>
       <c r="E334" t="str">
-        <v>OK</v>
+        <v>Missing in WP</v>
       </c>
     </row>
     <row r="335">
       <c r="A335" t="str">
-        <v>group-menu-pre-law</v>
+        <v>muons-over-letchworth</v>
       </c>
       <c r="B335" t="str">
-        <v>ITEM_HREF</v>
+        <v>MENU</v>
       </c>
       <c r="C335" t="str">
-        <v>/prelaw/EventsAtGeneseo</v>
+        <v>Muons Over Letchworth                    [Menu ID: muons-over-letchworth]</v>
       </c>
       <c r="D335" t="str">
-        <v>/prelaw/eventsatgeneseo</v>
+        <v>muons-over-letchworth                    [Term ID: 1746]</v>
       </c>
       <c r="E335" t="str">
-        <v>❗ HREF Mismatch</v>
+        <v>OK</v>
       </c>
     </row>
     <row r="336">
       <c r="A336" t="str">
-        <v>group-menu-premed</v>
+        <v>newman</v>
       </c>
       <c r="B336" t="str">
         <v>MENU</v>
       </c>
       <c r="C336" t="str">
-        <v>Pre-Med/Pre-Health                    [Menu ID: group-menu-premed]</v>
+        <v>Newman                    [Menu ID: newman]</v>
       </c>
       <c r="D336" t="str">
-        <v>group-menu-premed                    [Term ID: 1690]</v>
+        <v>newman                    [Term ID: 1738]</v>
       </c>
       <c r="E336" t="str">
         <v>OK</v>
@@ -6113,16 +6113,16 @@
     </row>
     <row r="337">
       <c r="A337" t="str">
-        <v>group-menu-prism-math-club</v>
+        <v>newman-catholic-campus-mini</v>
       </c>
       <c r="B337" t="str">
         <v>MENU</v>
       </c>
       <c r="C337" t="str">
-        <v>PRISM Math Club                    [Menu ID: group-menu-prism-math-club]</v>
+        <v>Newman Catholic Campus Ministry                    [Menu ID: newman-catholic-campus-mini]</v>
       </c>
       <c r="D337" t="str">
-        <v>group-menu-prism-math-club                    [Term ID: 1627]</v>
+        <v>newman-catholic-campus-mini                    [Term ID: 1634]</v>
       </c>
       <c r="E337" t="str">
         <v>OK</v>
@@ -6130,16 +6130,16 @@
     </row>
     <row r="338">
       <c r="A338" t="str">
-        <v>group-menu-prof-gu</v>
+        <v>office-of-accessibility</v>
       </c>
       <c r="B338" t="str">
         <v>MENU</v>
       </c>
       <c r="C338" t="str">
-        <v>Prof Gu                    [Menu ID: group-menu-prof-gu]</v>
+        <v>Office of Accessibility                    [Menu ID: office-of-accessibility]</v>
       </c>
       <c r="D338" t="str">
-        <v>group-menu-prof-gu                    [Term ID: 1595]</v>
+        <v>office-of-accessibility                    [Term ID: 1575]</v>
       </c>
       <c r="E338" t="str">
         <v>OK</v>
@@ -6147,115 +6147,115 @@
     </row>
     <row r="339">
       <c r="A339" t="str">
-        <v>group-menu-prof-gu</v>
+        <v>office-of-accessibility</v>
       </c>
       <c r="B339" t="str">
-        <v>ITEM_HREF</v>
+        <v>CHILD_TITLE</v>
       </c>
       <c r="C339" t="str">
-        <v>/sites/default/files/sites/business/Gu_Resume.pdf</v>
+        <v>Housing Accommodation FAQ's</v>
       </c>
       <c r="D339" t="str">
-        <v>/wp-content/uploads/2025/11/Gu_Resume.pdf</v>
+        <v/>
       </c>
       <c r="E339" t="str">
-        <v>❗ HREF Mismatch</v>
+        <v>Missing in WP</v>
       </c>
     </row>
     <row r="340">
       <c r="A340" t="str">
-        <v>group-menu-prof-herzman</v>
+        <v>office-of-accessibility</v>
       </c>
       <c r="B340" t="str">
-        <v>MENU</v>
+        <v>CHILD_HREF</v>
       </c>
       <c r="C340" t="str">
-        <v>Prof Herzman                    [Menu ID: group-menu-prof-herzman]</v>
+        <v>/accessibility-office/housing-accommodation-faqs</v>
       </c>
       <c r="D340" t="str">
-        <v>group-menu-prof-herzman                    [Term ID: 1622]</v>
+        <v/>
       </c>
       <c r="E340" t="str">
-        <v>OK</v>
+        <v>Missing in WP</v>
       </c>
     </row>
     <row r="341">
       <c r="A341" t="str">
-        <v>group-menu-prof-herzman</v>
+        <v>office-of-disability</v>
       </c>
       <c r="B341" t="str">
-        <v>ITEM_HREF</v>
+        <v>MENU</v>
       </c>
       <c r="C341" t="str">
-        <v>http://english.geneseo.edu</v>
+        <v>Disability Services                    [Menu ID: office-of-disability]</v>
       </c>
       <c r="D341" t="str">
         <v/>
       </c>
       <c r="E341" t="str">
-        <v>❗ HREF Mismatch</v>
+        <v>Missing in WP</v>
       </c>
     </row>
     <row r="342">
       <c r="A342" t="str">
-        <v>group-menu-prof-herzman</v>
+        <v>office-of-disability-servic</v>
       </c>
       <c r="B342" t="str">
-        <v>ITEM_HREF</v>
+        <v>MENU</v>
       </c>
       <c r="C342" t="str">
-        <v>http://writingguide.geneseo.edu</v>
+        <v>Disability Services                    [Menu ID: office-of-disability-servic]</v>
       </c>
       <c r="D342" t="str">
         <v/>
       </c>
       <c r="E342" t="str">
-        <v>❗ HREF Mismatch</v>
+        <v>Missing in WP</v>
       </c>
     </row>
     <row r="343">
       <c r="A343" t="str">
-        <v>group-menu-prof-herzman</v>
+        <v>policy</v>
       </c>
       <c r="B343" t="str">
-        <v>ITEM_HREF</v>
+        <v>MENU</v>
       </c>
       <c r="C343" t="str">
-        <v>http://vos.ucsb.edu</v>
+        <v>Policy                    [Menu ID: policy]</v>
       </c>
       <c r="D343" t="str">
-        <v/>
+        <v>policy                    [Term ID: 1745]</v>
       </c>
       <c r="E343" t="str">
-        <v>❗ HREF Mismatch</v>
+        <v>OK</v>
       </c>
     </row>
     <row r="344">
       <c r="A344" t="str">
-        <v>group-menu-proofspace</v>
+        <v>policy</v>
       </c>
       <c r="B344" t="str">
-        <v>MENU</v>
+        <v>ITEM_TITLE</v>
       </c>
       <c r="C344" t="str">
-        <v>ProofSpace                    [Menu ID: group-menu-proofspace]</v>
+        <v>Department Policies and Procedures</v>
       </c>
       <c r="D344" t="str">
-        <v>group-menu-proofspace                    [Term ID: 1552]</v>
+        <v/>
       </c>
       <c r="E344" t="str">
-        <v>OK</v>
+        <v>Missing in WP</v>
       </c>
     </row>
     <row r="345">
       <c r="A345" t="str">
-        <v>group-menu-property-control-serv</v>
+        <v>policy</v>
       </c>
       <c r="B345" t="str">
-        <v>MENU</v>
+        <v>ITEM_HREF</v>
       </c>
       <c r="C345" t="str">
-        <v>Property Control Services                    [Menu ID: group-menu-property-control-serv]</v>
+        <v>/president/departmental-policies-procedures</v>
       </c>
       <c r="D345" t="str">
         <v/>
@@ -6266,16 +6266,16 @@
     </row>
     <row r="346">
       <c r="A346" t="str">
-        <v>group-menu-psychology-club</v>
+        <v>pride-alliance</v>
       </c>
       <c r="B346" t="str">
         <v>MENU</v>
       </c>
       <c r="C346" t="str">
-        <v>Psychology Club                    [Menu ID: group-menu-psychology-club]</v>
+        <v>Pride Alliance                    [Menu ID: pride-alliance]</v>
       </c>
       <c r="D346" t="str">
-        <v>group-menu-psychology-club                    [Term ID: 1626]</v>
+        <v>pride-alliance                    [Term ID: 1739]</v>
       </c>
       <c r="E346" t="str">
         <v>OK</v>
@@ -6283,16 +6283,16 @@
     </row>
     <row r="347">
       <c r="A347" t="str">
-        <v>group-menu-psychology-department</v>
+        <v>quick-links</v>
       </c>
       <c r="B347" t="str">
         <v>MENU</v>
       </c>
       <c r="C347" t="str">
-        <v>Department of Psychology                     [Menu ID: group-menu-psychology-department]</v>
+        <v>Quick Links                    [Menu ID: quick-links]</v>
       </c>
       <c r="D347" t="str">
-        <v>group-menu-psychology-department                    [Term ID: 1539]</v>
+        <v>quick-links                    [Term ID: 1737]</v>
       </c>
       <c r="E347" t="str">
         <v>OK</v>
@@ -6300,64 +6300,64 @@
     </row>
     <row r="348">
       <c r="A348" t="str">
-        <v>group-menu-purchasing</v>
+        <v>rave</v>
       </c>
       <c r="B348" t="str">
         <v>MENU</v>
       </c>
       <c r="C348" t="str">
-        <v>Purchasing                    [Menu ID: group-menu-purchasing]</v>
+        <v>RAVE                    [Menu ID: rave]</v>
       </c>
       <c r="D348" t="str">
-        <v>group-menu-purchasing                    [Term ID: 1562]</v>
+        <v/>
       </c>
       <c r="E348" t="str">
-        <v>OK</v>
+        <v>Missing in WP</v>
       </c>
     </row>
     <row r="349">
       <c r="A349" t="str">
-        <v>group-menu-purchasing</v>
+        <v>rlk</v>
       </c>
       <c r="B349" t="str">
-        <v>ITEM_HREF</v>
+        <v>MENU</v>
       </c>
       <c r="C349" t="str">
-        <v>http://duplicating.geneseo.edu</v>
+        <v>Royal Lady Knights                    [Menu ID: rlk]</v>
       </c>
       <c r="D349" t="str">
         <v/>
       </c>
       <c r="E349" t="str">
-        <v>❗ HREF Mismatch</v>
+        <v>Missing in WP</v>
       </c>
     </row>
     <row r="350">
       <c r="A350" t="str">
-        <v>group-menu-purchasing</v>
+        <v>safezone</v>
       </c>
       <c r="B350" t="str">
-        <v>CHILD_HREF</v>
+        <v>MENU</v>
       </c>
       <c r="C350" t="str">
-        <v>http://duplicating.geneseo.edu</v>
+        <v>Safe Zone                    [Menu ID: safezone]</v>
       </c>
       <c r="D350" t="str">
-        <v/>
+        <v>safezone                    [Term ID: 1632]</v>
       </c>
       <c r="E350" t="str">
-        <v>❗ HREF Mismatch</v>
+        <v>OK</v>
       </c>
     </row>
     <row r="351">
       <c r="A351" t="str">
-        <v>group-menu-ratio-christi</v>
+        <v>salvador-tarun-jr-</v>
       </c>
       <c r="B351" t="str">
         <v>MENU</v>
       </c>
       <c r="C351" t="str">
-        <v>Ratio Christi                    [Menu ID: group-menu-ratio-christi]</v>
+        <v>Salvador Tarun Jr.                    [Menu ID: salvador-tarun-jr-]</v>
       </c>
       <c r="D351" t="str">
         <v/>
@@ -6368,16 +6368,16 @@
     </row>
     <row r="352">
       <c r="A352" t="str">
-        <v>group-menu-red-cross-club</v>
+        <v>secondary</v>
       </c>
       <c r="B352" t="str">
         <v>MENU</v>
       </c>
       <c r="C352" t="str">
-        <v>Red Cross Club                    [Menu ID: group-menu-red-cross-club]</v>
+        <v>Secondary Navigation                    [Menu ID: secondary]</v>
       </c>
       <c r="D352" t="str">
-        <v>group-menu-red-cross-club                    [Term ID: 1639]</v>
+        <v>secondary                    [Term ID: 1610]</v>
       </c>
       <c r="E352" t="str">
         <v>OK</v>
@@ -6385,16 +6385,16 @@
     </row>
     <row r="353">
       <c r="A353" t="str">
-        <v>group-menu-red-folder</v>
+        <v>south-village-counseling</v>
       </c>
       <c r="B353" t="str">
         <v>MENU</v>
       </c>
       <c r="C353" t="str">
-        <v>Red Folder                    [Menu ID: group-menu-red-folder]</v>
+        <v>Mind-Body Home                    [Menu ID: south-village-counseling]</v>
       </c>
       <c r="D353" t="str">
-        <v>group-menu-red-folder                    [Term ID: 1726]</v>
+        <v>south-village-counseling                    [Term ID: 1743]</v>
       </c>
       <c r="E353" t="str">
         <v>OK</v>
@@ -6402,16 +6402,16 @@
     </row>
     <row r="354">
       <c r="A354" t="str">
-        <v>group-menu-registrar</v>
+        <v>student-athlete-resource-ce</v>
       </c>
       <c r="B354" t="str">
         <v>MENU</v>
       </c>
       <c r="C354" t="str">
-        <v>Registrar                    [Menu ID: group-menu-registrar]</v>
+        <v>Student Athlete Resource Center                    [Menu ID: student-athlete-resource-ce]</v>
       </c>
       <c r="D354" t="str">
-        <v>group-menu-registrar                    [Term ID: 1606]</v>
+        <v>student-athlete-resource-ce                    [Term ID: 1758]</v>
       </c>
       <c r="E354" t="str">
         <v>OK</v>
@@ -6419,2727 +6419,92 @@
     </row>
     <row r="355">
       <c r="A355" t="str">
-        <v>group-menu-registrar</v>
+        <v>student-coalition-for-mirga</v>
       </c>
       <c r="B355" t="str">
-        <v>ITEM_HREF</v>
+        <v>MENU</v>
       </c>
       <c r="C355" t="str">
-        <v>/registrar/SOC</v>
+        <v>Student Coalition for Mirgant Workers                    [Menu ID: student-coalition-for-mirga]</v>
       </c>
       <c r="D355" t="str">
-        <v>/registrar/soc</v>
+        <v/>
       </c>
       <c r="E355" t="str">
-        <v>❗ HREF Mismatch</v>
+        <v>Missing in WP</v>
       </c>
     </row>
     <row r="356">
       <c r="A356" t="str">
-        <v>group-menu-registrar</v>
+        <v>voices-for-planned-parentho</v>
       </c>
       <c r="B356" t="str">
-        <v>ITEM_HREF</v>
+        <v>MENU</v>
       </c>
       <c r="C356" t="str">
-        <v>/registrar/RegistrationDates</v>
+        <v>Voices for Planned Parenthood                    [Menu ID: voices-for-planned-parentho]</v>
       </c>
       <c r="D356" t="str">
-        <v>/registrar/registrationdates</v>
+        <v/>
       </c>
       <c r="E356" t="str">
-        <v>❗ HREF Mismatch</v>
+        <v>Missing in WP</v>
       </c>
     </row>
     <row r="357">
       <c r="A357" t="str">
-        <v>group-menu-registrar</v>
+        <v>web-accessibility</v>
       </c>
       <c r="B357" t="str">
-        <v>CHILD_HREF</v>
+        <v>MENU</v>
       </c>
       <c r="C357" t="str">
-        <v>/dean_office/transfer_college_credit</v>
+        <v>Web Accessibility                    [Menu ID: web-accessibility]</v>
       </c>
       <c r="D357" t="str">
-        <v>/advising/transfer-college-credit</v>
+        <v>web-accessibility                    [Term ID: 1748]</v>
       </c>
       <c r="E357" t="str">
-        <v>❗ HREF Mismatch</v>
+        <v>OK</v>
       </c>
     </row>
     <row r="358">
       <c r="A358" t="str">
-        <v>group-menu-reinhardt-research-</v>
+        <v>wgsu</v>
       </c>
       <c r="B358" t="str">
         <v>MENU</v>
       </c>
       <c r="C358" t="str">
-        <v>Reinhardt Research                     [Menu ID: group-menu-reinhardt-research-]</v>
+        <v>WGSU-FM                    [Menu ID: wgsu]</v>
       </c>
       <c r="D358" t="str">
-        <v/>
+        <v>wgsu                    [Term ID: 1585]</v>
       </c>
       <c r="E358" t="str">
-        <v>Missing in WP</v>
+        <v>OK</v>
       </c>
     </row>
     <row r="359">
       <c r="A359" t="str">
-        <v>group-menu-reunion</v>
+        <v>who-are-we-</v>
       </c>
       <c r="B359" t="str">
         <v>MENU</v>
       </c>
       <c r="C359" t="str">
-        <v>Reunion                    [Menu ID: group-menu-reunion]</v>
+        <v>Who Are We?                    [Menu ID: who-are-we-]</v>
       </c>
       <c r="D359" t="str">
-        <v>group-menu-reunion                    [Term ID: 1662]</v>
+        <v/>
       </c>
       <c r="E359" t="str">
-        <v>OK</v>
-      </c>
-    </row>
-    <row r="360">
-      <c r="A360" t="str">
-        <v>group-menu-reunion</v>
-      </c>
-      <c r="B360" t="str">
-        <v>ITEM_TITLE</v>
-      </c>
-      <c r="C360" t="str">
-        <v>Menus</v>
-      </c>
-      <c r="D360" t="str">
-        <v/>
-      </c>
-      <c r="E360" t="str">
-        <v>Missing in WP</v>
-      </c>
-    </row>
-    <row r="361">
-      <c r="A361" t="str">
-        <v>group-menu-reunion</v>
-      </c>
-      <c r="B361" t="str">
-        <v>ITEM_HREF</v>
-      </c>
-      <c r="C361" t="str">
-        <v>/reunion/reunion-menus2019</v>
-      </c>
-      <c r="D361" t="str">
-        <v/>
-      </c>
-      <c r="E361" t="str">
-        <v>Missing in WP</v>
-      </c>
-    </row>
-    <row r="362">
-      <c r="A362" t="str">
-        <v>group-menu-roemer-arboretum</v>
-      </c>
-      <c r="B362" t="str">
-        <v>MENU</v>
-      </c>
-      <c r="C362" t="str">
-        <v>Roemer Arboretum                    [Menu ID: group-menu-roemer-arboretum]</v>
-      </c>
-      <c r="D362" t="str">
-        <v>group-menu-roemer-arboretum                    [Term ID: 1732]</v>
-      </c>
-      <c r="E362" t="str">
-        <v>OK</v>
-      </c>
-    </row>
-    <row r="363">
-      <c r="A363" t="str">
-        <v>group-menu-rose-mcewen</v>
-      </c>
-      <c r="B363" t="str">
-        <v>MENU</v>
-      </c>
-      <c r="C363" t="str">
-        <v>Rose McEwen                    [Menu ID: group-menu-rose-mcewen]</v>
-      </c>
-      <c r="D363" t="str">
-        <v>group-menu-rose-mcewen                    [Term ID: 1591]</v>
-      </c>
-      <c r="E363" t="str">
-        <v>OK</v>
-      </c>
-    </row>
-    <row r="364">
-      <c r="A364" t="str">
-        <v>group-menu-rugby</v>
-      </c>
-      <c r="B364" t="str">
-        <v>MENU</v>
-      </c>
-      <c r="C364" t="str">
-        <v>Men's Rugby                    [Menu ID: group-menu-rugby]</v>
-      </c>
-      <c r="D364" t="str">
-        <v/>
-      </c>
-      <c r="E364" t="str">
-        <v>Missing in WP</v>
-      </c>
-    </row>
-    <row r="365">
-      <c r="A365" t="str">
-        <v>group-menu-rysag</v>
-      </c>
-      <c r="B365" t="str">
-        <v>MENU</v>
-      </c>
-      <c r="C365" t="str">
-        <v>RYSAG                    [Menu ID: group-menu-rysag]</v>
-      </c>
-      <c r="D365" t="str">
-        <v>group-menu-rysag                    [Term ID: 1635]</v>
-      </c>
-      <c r="E365" t="str">
-        <v>OK</v>
-      </c>
-    </row>
-    <row r="366">
-      <c r="A366" t="str">
-        <v>group-menu-rysag</v>
-      </c>
-      <c r="B366" t="str">
-        <v>ITEM_HREF</v>
-      </c>
-      <c r="C366" t="str">
-        <v>http://rysagparents.blogspot.com</v>
-      </c>
-      <c r="D366" t="str">
-        <v/>
-      </c>
-      <c r="E366" t="str">
-        <v>❗ HREF Mismatch</v>
-      </c>
-    </row>
-    <row r="367">
-      <c r="A367" t="str">
-        <v>group-menu-safe-party</v>
-      </c>
-      <c r="B367" t="str">
-        <v>MENU</v>
-      </c>
-      <c r="C367" t="str">
-        <v>Safe Party                    [Menu ID: group-menu-safe-party]</v>
-      </c>
-      <c r="D367" t="str">
-        <v>group-menu-safe-party                    [Term ID: 1594]</v>
-      </c>
-      <c r="E367" t="str">
-        <v>OK</v>
-      </c>
-    </row>
-    <row r="368">
-      <c r="A368" t="str">
-        <v>group-menu-sam-bean</v>
-      </c>
-      <c r="B368" t="str">
-        <v>MENU</v>
-      </c>
-      <c r="C368" t="str">
-        <v>Sam Bean                    [Menu ID: group-menu-sam-bean]</v>
-      </c>
-      <c r="D368" t="str">
-        <v>group-menu-sam-bean                    [Term ID: 1612]</v>
-      </c>
-      <c r="E368" t="str">
-        <v>OK</v>
-      </c>
-    </row>
-    <row r="369">
-      <c r="A369" t="str">
-        <v>group-menu-savi-iyer</v>
-      </c>
-      <c r="B369" t="str">
-        <v>MENU</v>
-      </c>
-      <c r="C369" t="str">
-        <v>Savi Iyer                    [Menu ID: group-menu-savi-iyer]</v>
-      </c>
-      <c r="D369" t="str">
-        <v>group-menu-savi-iyer                    [Term ID: 1680]</v>
-      </c>
-      <c r="E369" t="str">
-        <v>OK</v>
-      </c>
-    </row>
-    <row r="370">
-      <c r="A370" t="str">
-        <v>group-menu-sbdc</v>
-      </c>
-      <c r="B370" t="str">
-        <v>MENU</v>
-      </c>
-      <c r="C370" t="str">
-        <v>SBDC                    [Menu ID: group-menu-sbdc]</v>
-      </c>
-      <c r="D370" t="str">
-        <v>group-menu-sbdc                    [Term ID: 1658]</v>
-      </c>
-      <c r="E370" t="str">
-        <v>OK</v>
-      </c>
-    </row>
-    <row r="371">
-      <c r="A371" t="str">
-        <v>group-menu-scene</v>
-      </c>
-      <c r="B371" t="str">
-        <v>MENU</v>
-      </c>
-      <c r="C371" t="str">
-        <v>Scene                    [Menu ID: group-menu-scene]</v>
-      </c>
-      <c r="D371" t="str">
-        <v>group-menu-scene                    [Term ID: 1725]</v>
-      </c>
-      <c r="E371" t="str">
-        <v>OK</v>
-      </c>
-    </row>
-    <row r="372">
-      <c r="A372" t="str">
-        <v>group-menu-school-of-business</v>
-      </c>
-      <c r="B372" t="str">
-        <v>MENU</v>
-      </c>
-      <c r="C372" t="str">
-        <v>School of Business                    [Menu ID: group-menu-school-of-business]</v>
-      </c>
-      <c r="D372" t="str">
-        <v>group-menu-school-of-business                    [Term ID: 1694]</v>
-      </c>
-      <c r="E372" t="str">
-        <v>OK</v>
-      </c>
-    </row>
-    <row r="373">
-      <c r="A373" t="str">
-        <v>group-menu-school-of-business</v>
-      </c>
-      <c r="B373" t="str">
-        <v>ITEM_HREF</v>
-      </c>
-      <c r="C373" t="str">
-        <v>/business/prospective-students</v>
-      </c>
-      <c r="D373" t="str">
-        <v>/business/prospective-business-students</v>
-      </c>
-      <c r="E373" t="str">
-        <v>❗ HREF Mismatch</v>
-      </c>
-    </row>
-    <row r="374">
-      <c r="A374" t="str">
-        <v>group-menu-school-of-business</v>
-      </c>
-      <c r="B374" t="str">
-        <v>ITEM_HREF</v>
-      </c>
-      <c r="C374" t="str">
-        <v>/business/student%20outcomes</v>
-      </c>
-      <c r="D374" t="str">
-        <v>/business/student-outcomes</v>
-      </c>
-      <c r="E374" t="str">
-        <v>❗ HREF Mismatch</v>
-      </c>
-    </row>
-    <row r="375">
-      <c r="A375" t="str">
-        <v>group-menu-school-of-business</v>
-      </c>
-      <c r="B375" t="str">
-        <v>ITEM_HREF</v>
-      </c>
-      <c r="C375" t="str">
-        <v>/business/alumni</v>
-      </c>
-      <c r="D375" t="str">
-        <v>/business/business-advisory-council</v>
-      </c>
-      <c r="E375" t="str">
-        <v>❗ HREF Mismatch</v>
-      </c>
-    </row>
-    <row r="376">
-      <c r="A376" t="str">
-        <v>group-menu-school-of-business</v>
-      </c>
-      <c r="B376" t="str">
-        <v>ITEM_HREF</v>
-      </c>
-      <c r="C376" t="str">
-        <v>/school-business-faqs</v>
-      </c>
-      <c r="D376" t="str">
-        <v>/business/school-business-frequently-asked-questions</v>
-      </c>
-      <c r="E376" t="str">
-        <v>❗ HREF Mismatch</v>
-      </c>
-    </row>
-    <row r="377">
-      <c r="A377" t="str">
-        <v>group-menu-school-of-education</v>
-      </c>
-      <c r="B377" t="str">
-        <v>MENU</v>
-      </c>
-      <c r="C377" t="str">
-        <v>School of Education                    [Menu ID: group-menu-school-of-education]</v>
-      </c>
-      <c r="D377" t="str">
-        <v>group-menu-school-of-education                    [Term ID: 1560]</v>
-      </c>
-      <c r="E377" t="str">
-        <v>OK</v>
-      </c>
-    </row>
-    <row r="378">
-      <c r="A378" t="str">
-        <v>group-menu-scott-giorgis</v>
-      </c>
-      <c r="B378" t="str">
-        <v>MENU</v>
-      </c>
-      <c r="C378" t="str">
-        <v>Scott Giorgis                    [Menu ID: group-menu-scott-giorgis]</v>
-      </c>
-      <c r="D378" t="str">
-        <v>group-menu-scott-giorgis                    [Term ID: 1682]</v>
-      </c>
-      <c r="E378" t="str">
-        <v>OK</v>
-      </c>
-    </row>
-    <row r="379">
-      <c r="A379" t="str">
-        <v>group-menu-sean-nixon</v>
-      </c>
-      <c r="B379" t="str">
-        <v>MENU</v>
-      </c>
-      <c r="C379" t="str">
-        <v>Sean Nixon                    [Menu ID: group-menu-sean-nixon]</v>
-      </c>
-      <c r="D379" t="str">
-        <v/>
-      </c>
-      <c r="E379" t="str">
-        <v>Missing in WP</v>
-      </c>
-    </row>
-    <row r="380">
-      <c r="A380" t="str">
-        <v>group-menu-seaway-section-2016</v>
-      </c>
-      <c r="B380" t="str">
-        <v>MENU</v>
-      </c>
-      <c r="C380" t="str">
-        <v>Seaway Section 2016                    [Menu ID: group-menu-seaway-section-2016]</v>
-      </c>
-      <c r="D380" t="str">
-        <v/>
-      </c>
-      <c r="E380" t="str">
-        <v>Missing in WP</v>
-      </c>
-    </row>
-    <row r="381">
-      <c r="A381" t="str">
-        <v>group-menu-sefa</v>
-      </c>
-      <c r="B381" t="str">
-        <v>MENU</v>
-      </c>
-      <c r="C381" t="str">
-        <v>SEFA                    [Menu ID: group-menu-sefa]</v>
-      </c>
-      <c r="D381" t="str">
-        <v>group-menu-sefa                    [Term ID: 1648]</v>
-      </c>
-      <c r="E381" t="str">
-        <v>OK</v>
-      </c>
-    </row>
-    <row r="382">
-      <c r="A382" t="str">
-        <v>group-menu-shakti</v>
-      </c>
-      <c r="B382" t="str">
-        <v>MENU</v>
-      </c>
-      <c r="C382" t="str">
-        <v>Shakti                    [Menu ID: group-menu-shakti]</v>
-      </c>
-      <c r="D382" t="str">
-        <v>group-menu-shakti                    [Term ID: 1640]</v>
-      </c>
-      <c r="E382" t="str">
-        <v>OK</v>
-      </c>
-    </row>
-    <row r="383">
-      <c r="A383" t="str">
-        <v>group-menu-sibling-peer-research</v>
-      </c>
-      <c r="B383" t="str">
-        <v>MENU</v>
-      </c>
-      <c r="C383" t="str">
-        <v>Sibling-Peer Research Group                    [Menu ID: group-menu-sibling-peer-research]</v>
-      </c>
-      <c r="D383" t="str">
-        <v>group-menu-sibling-peer-research                    [Term ID: 1614]</v>
-      </c>
-      <c r="E383" t="str">
-        <v>OK</v>
-      </c>
-    </row>
-    <row r="384">
-      <c r="A384" t="str">
-        <v>group-menu-soaringstars</v>
-      </c>
-      <c r="B384" t="str">
-        <v>MENU</v>
-      </c>
-      <c r="C384" t="str">
-        <v>SoaringStars                    [Menu ID: group-menu-soaringstars]</v>
-      </c>
-      <c r="D384" t="str">
-        <v>group-menu-soaringstars                    [Term ID: 1563]</v>
-      </c>
-      <c r="E384" t="str">
-        <v>OK</v>
-      </c>
-    </row>
-    <row r="385">
-      <c r="A385" t="str">
-        <v>group-menu-soaringstars</v>
-      </c>
-      <c r="B385" t="str">
-        <v>ITEM_HREF</v>
-      </c>
-      <c r="C385" t="str">
-        <v>/soaringstars/co-directors</v>
-      </c>
-      <c r="D385" t="str">
-        <v>/?page_id=44590</v>
-      </c>
-      <c r="E385" t="str">
-        <v>❗ HREF Mismatch</v>
-      </c>
-    </row>
-    <row r="386">
-      <c r="A386" t="str">
-        <v>group-menu-society-for-human-res</v>
-      </c>
-      <c r="B386" t="str">
-        <v>MENU</v>
-      </c>
-      <c r="C386" t="str">
-        <v>Society for Human Resource Man                    [Menu ID: group-menu-society-for-human-res]</v>
-      </c>
-      <c r="D386" t="str">
-        <v>group-menu-society-for-human-res                    [Term ID: 1597]</v>
-      </c>
-      <c r="E386" t="str">
-        <v>OK</v>
-      </c>
-    </row>
-    <row r="387">
-      <c r="A387" t="str">
-        <v>group-menu-sociology</v>
-      </c>
-      <c r="B387" t="str">
-        <v>MENU</v>
-      </c>
-      <c r="C387" t="str">
-        <v>Sociology                    [Menu ID: group-menu-sociology]</v>
-      </c>
-      <c r="D387" t="str">
-        <v>group-menu-sociology                    [Term ID: 1555]</v>
-      </c>
-      <c r="E387" t="str">
-        <v>OK</v>
-      </c>
-    </row>
-    <row r="388">
-      <c r="A388" t="str">
-        <v>group-menu-sociomedical-sciences</v>
-      </c>
-      <c r="B388" t="str">
-        <v>MENU</v>
-      </c>
-      <c r="C388" t="str">
-        <v>Sociomedical Sciences                    [Menu ID: group-menu-sociomedical-sciences]</v>
-      </c>
-      <c r="D388" t="str">
-        <v>group-menu-sociomedical-sciences                    [Term ID: 1534]</v>
-      </c>
-      <c r="E388" t="str">
-        <v>OK</v>
-      </c>
-    </row>
-    <row r="389">
-      <c r="A389" t="str">
-        <v>group-menu-sociomedical-sciences</v>
-      </c>
-      <c r="B389" t="str">
-        <v>ITEM_HREF</v>
-      </c>
-      <c r="C389" t="str">
-        <v>/sociomedical_sciences/job-opportunities</v>
-      </c>
-      <c r="D389" t="str">
-        <v>/sociomedical_sciences/sociomedical-sciences-job-opportunities</v>
-      </c>
-      <c r="E389" t="str">
-        <v>❗ HREF Mismatch</v>
-      </c>
-    </row>
-    <row r="390">
-      <c r="A390" t="str">
-        <v>group-menu-sofi</v>
-      </c>
-      <c r="B390" t="str">
-        <v>MENU</v>
-      </c>
-      <c r="C390" t="str">
-        <v>Student Course Experience (SCE)                    [Menu ID: group-menu-sofi]</v>
-      </c>
-      <c r="D390" t="str">
-        <v>group-menu-sofi                    [Term ID: 1649]</v>
-      </c>
-      <c r="E390" t="str">
-        <v>OK</v>
-      </c>
-    </row>
-    <row r="391">
-      <c r="A391" t="str">
-        <v>group-menu-sofi</v>
-      </c>
-      <c r="B391" t="str">
-        <v>ITEM_HREF</v>
-      </c>
-      <c r="C391" t="str">
-        <v>/sce</v>
-      </c>
-      <c r="D391" t="str">
-        <v>/entity:node/3144</v>
-      </c>
-      <c r="E391" t="str">
-        <v>❗ HREF Mismatch</v>
-      </c>
-    </row>
-    <row r="392">
-      <c r="A392" t="str">
-        <v>group-menu-sponsored-research</v>
-      </c>
-      <c r="B392" t="str">
-        <v>MENU</v>
-      </c>
-      <c r="C392" t="str">
-        <v>Sponsored Research                    [Menu ID: group-menu-sponsored-research]</v>
-      </c>
-      <c r="D392" t="str">
-        <v>group-menu-sponsored-research                    [Term ID: 1638]</v>
-      </c>
-      <c r="E392" t="str">
-        <v>OK</v>
-      </c>
-    </row>
-    <row r="393">
-      <c r="A393" t="str">
-        <v>group-menu-stitches-geneseo</v>
-      </c>
-      <c r="B393" t="str">
-        <v>MENU</v>
-      </c>
-      <c r="C393" t="str">
-        <v>Stitches Geneseo                    [Menu ID: group-menu-stitches-geneseo]</v>
-      </c>
-      <c r="D393" t="str">
-        <v/>
-      </c>
-      <c r="E393" t="str">
-        <v>Missing in WP</v>
-      </c>
-    </row>
-    <row r="394">
-      <c r="A394" t="str">
-        <v>group-menu-strategic-planning-gr</v>
-      </c>
-      <c r="B394" t="str">
-        <v>MENU</v>
-      </c>
-      <c r="C394" t="str">
-        <v>Strategic Planning Group                    [Menu ID: group-menu-strategic-planning-gr]</v>
-      </c>
-      <c r="D394" t="str">
-        <v>group-menu-strategic-planning-gr                    [Term ID: 1700]</v>
-      </c>
-      <c r="E394" t="str">
-        <v>OK</v>
-      </c>
-    </row>
-    <row r="395">
-      <c r="A395" t="str">
-        <v>group-menu-student-accounts</v>
-      </c>
-      <c r="B395" t="str">
-        <v>MENU</v>
-      </c>
-      <c r="C395" t="str">
-        <v>Student Accounts                    [Menu ID: group-menu-student-accounts]</v>
-      </c>
-      <c r="D395" t="str">
-        <v>group-menu-student-accounts                    [Term ID: 1650]</v>
-      </c>
-      <c r="E395" t="str">
-        <v>OK</v>
-      </c>
-    </row>
-    <row r="396">
-      <c r="A396" t="str">
-        <v>group-menu-student-advocate-resp</v>
-      </c>
-      <c r="B396" t="str">
-        <v>MENU</v>
-      </c>
-      <c r="C396" t="str">
-        <v>Student Advocate Response Team                    [Menu ID: group-menu-student-advocate-resp]</v>
-      </c>
-      <c r="D396" t="str">
-        <v/>
-      </c>
-      <c r="E396" t="str">
-        <v>Missing in WP</v>
-      </c>
-    </row>
-    <row r="397">
-      <c r="A397" t="str">
-        <v>group-menu-student-and-campus-li</v>
-      </c>
-      <c r="B397" t="str">
-        <v>MENU</v>
-      </c>
-      <c r="C397" t="str">
-        <v>Student and Campus Life Administrative Team                    [Menu ID: group-menu-student-and-campus-li]</v>
-      </c>
-      <c r="D397" t="str">
-        <v/>
-      </c>
-      <c r="E397" t="str">
-        <v>Missing in WP</v>
-      </c>
-    </row>
-    <row r="398">
-      <c r="A398" t="str">
-        <v>group-menu-student-association</v>
-      </c>
-      <c r="B398" t="str">
-        <v>MENU</v>
-      </c>
-      <c r="C398" t="str">
-        <v>Student Association                    [Menu ID: group-menu-student-association]</v>
-      </c>
-      <c r="D398" t="str">
-        <v>group-menu-student-association                    [Term ID: 1544]</v>
-      </c>
-      <c r="E398" t="str">
-        <v>OK</v>
-      </c>
-    </row>
-    <row r="399">
-      <c r="A399" t="str">
-        <v>group-menu-student-conduct-commu</v>
-      </c>
-      <c r="B399" t="str">
-        <v>MENU</v>
-      </c>
-      <c r="C399" t="str">
-        <v>Student Conduct &amp; Community Standards                    [Menu ID: group-menu-student-conduct-commu]</v>
-      </c>
-      <c r="D399" t="str">
-        <v>group-menu-student-conduct-commu                    [Term ID: 1536]</v>
-      </c>
-      <c r="E399" t="str">
-        <v>OK</v>
-      </c>
-    </row>
-    <row r="400">
-      <c r="A400" t="str">
-        <v>group-menu-student-employment</v>
-      </c>
-      <c r="B400" t="str">
-        <v>MENU</v>
-      </c>
-      <c r="C400" t="str">
-        <v>Student Employment                    [Menu ID: group-menu-student-employment]</v>
-      </c>
-      <c r="D400" t="str">
-        <v>group-menu-student-employment                    [Term ID: 1729]</v>
-      </c>
-      <c r="E400" t="str">
-        <v>OK</v>
-      </c>
-    </row>
-    <row r="401">
-      <c r="A401" t="str">
-        <v>group-menu-student-employment</v>
-      </c>
-      <c r="B401" t="str">
-        <v>ITEM_HREF</v>
-      </c>
-      <c r="C401" t="str">
-        <v>/student_employment/student-faq</v>
-      </c>
-      <c r="D401" t="str">
-        <v>/?page_id=44837</v>
-      </c>
-      <c r="E401" t="str">
-        <v>❗ HREF Mismatch</v>
-      </c>
-    </row>
-    <row r="402">
-      <c r="A402" t="str">
-        <v>group-menu-student-gateway</v>
-      </c>
-      <c r="B402" t="str">
-        <v>MENU</v>
-      </c>
-      <c r="C402" t="str">
-        <v>Student Gateway                    [Menu ID: group-menu-student-gateway]</v>
-      </c>
-      <c r="D402" t="str">
-        <v>group-menu-student-gateway                    [Term ID: 1704]</v>
-      </c>
-      <c r="E402" t="str">
-        <v>OK</v>
-      </c>
-    </row>
-    <row r="403">
-      <c r="A403" t="str">
-        <v>group-menu-student-gateway</v>
-      </c>
-      <c r="B403" t="str">
-        <v>ITEM_HREF</v>
-      </c>
-      <c r="C403" t="str">
-        <v>https://my.geneseo.edu</v>
-      </c>
-      <c r="D403" t="str">
-        <v/>
-      </c>
-      <c r="E403" t="str">
-        <v>❗ HREF Mismatch</v>
-      </c>
-    </row>
-    <row r="404">
-      <c r="A404" t="str">
-        <v>group-menu-student-gateway</v>
-      </c>
-      <c r="B404" t="str">
-        <v>ITEM_HREF</v>
-      </c>
-      <c r="C404" t="str">
-        <v>/student_life/student-organization-directory</v>
-      </c>
-      <c r="D404" t="str">
-        <v>https://webapps.geneseo.edu/student-organizations</v>
-      </c>
-      <c r="E404" t="str">
-        <v>❗ HREF Mismatch</v>
-      </c>
-    </row>
-    <row r="405">
-      <c r="A405" t="str">
-        <v>group-menu-student-handbook</v>
-      </c>
-      <c r="B405" t="str">
-        <v>MENU</v>
-      </c>
-      <c r="C405" t="str">
-        <v>Student Handbook                    [Menu ID: group-menu-student-handbook]</v>
-      </c>
-      <c r="D405" t="str">
-        <v>group-menu-student-handbook                    [Term ID: 1660]</v>
-      </c>
-      <c r="E405" t="str">
-        <v>OK</v>
-      </c>
-    </row>
-    <row r="406">
-      <c r="A406" t="str">
-        <v>group-menu-student-handbook</v>
-      </c>
-      <c r="B406" t="str">
-        <v>ITEM_HREF</v>
-      </c>
-      <c r="C406" t="str">
-        <v>http://c4c.geneseo.edu</v>
-      </c>
-      <c r="D406" t="str">
-        <v/>
-      </c>
-      <c r="E406" t="str">
-        <v>❗ HREF Mismatch</v>
-      </c>
-    </row>
-    <row r="407">
-      <c r="A407" t="str">
-        <v>group-menu-student-handbook</v>
-      </c>
-      <c r="B407" t="str">
-        <v>ITEM_HREF</v>
-      </c>
-      <c r="C407" t="str">
-        <v>/handbook/student-code-conduct</v>
-      </c>
-      <c r="D407" t="str">
-        <v>/internal:/handbook/student-code-conduct</v>
-      </c>
-      <c r="E407" t="str">
-        <v>❗ HREF Mismatch</v>
-      </c>
-    </row>
-    <row r="408">
-      <c r="A408" t="str">
-        <v>group-menu-student-handbook</v>
-      </c>
-      <c r="B408" t="str">
-        <v>ITEM_TITLE</v>
-      </c>
-      <c r="C408" t="str">
-        <v>What Faculty Should Know about FERPA</v>
-      </c>
-      <c r="D408" t="str">
-        <v/>
-      </c>
-      <c r="E408" t="str">
-        <v>Missing in WP</v>
-      </c>
-    </row>
-    <row r="409">
-      <c r="A409" t="str">
-        <v>group-menu-student-handbook</v>
-      </c>
-      <c r="B409" t="str">
-        <v>ITEM_HREF</v>
-      </c>
-      <c r="C409" t="str">
-        <v>/sites/default/files/sites/community/FERPA_facultystaff_2014.pdf</v>
-      </c>
-      <c r="D409" t="str">
-        <v/>
-      </c>
-      <c r="E409" t="str">
-        <v>Missing in WP</v>
-      </c>
-    </row>
-    <row r="410">
-      <c r="A410" t="str">
-        <v>group-menu-student-handbook</v>
-      </c>
-      <c r="B410" t="str">
-        <v>ITEM_TITLE</v>
-      </c>
-      <c r="C410" t="str">
-        <v>Good Samaritan Policy</v>
-      </c>
-      <c r="D410" t="str">
-        <v/>
-      </c>
-      <c r="E410" t="str">
-        <v>Missing in WP</v>
-      </c>
-    </row>
-    <row r="411">
-      <c r="A411" t="str">
-        <v>group-menu-student-handbook</v>
-      </c>
-      <c r="B411" t="str">
-        <v>ITEM_HREF</v>
-      </c>
-      <c r="C411" t="str">
-        <v>/sites/default/files/sites/handbook/Good%20Samaritan%20Policy%20Final.pdf</v>
-      </c>
-      <c r="D411" t="str">
-        <v/>
-      </c>
-      <c r="E411" t="str">
-        <v>Missing in WP</v>
-      </c>
-    </row>
-    <row r="412">
-      <c r="A412" t="str">
-        <v>group-menu-student-life</v>
-      </c>
-      <c r="B412" t="str">
-        <v>MENU</v>
-      </c>
-      <c r="C412" t="str">
-        <v>Student Life                    [Menu ID: group-menu-student-life]</v>
-      </c>
-      <c r="D412" t="str">
-        <v>group-menu-student-life                    [Term ID: 1530]</v>
-      </c>
-      <c r="E412" t="str">
-        <v>OK</v>
-      </c>
-    </row>
-    <row r="413">
-      <c r="A413" t="str">
-        <v>group-menu-student-life</v>
-      </c>
-      <c r="B413" t="str">
-        <v>ITEM_HREF</v>
-      </c>
-      <c r="C413" t="str">
-        <v>/student_life/student-basic-needs</v>
-      </c>
-      <c r="D413" t="str">
-        <v>/student_life/resources-student-basic-needs</v>
-      </c>
-      <c r="E413" t="str">
-        <v>❗ HREF Mismatch</v>
-      </c>
-    </row>
-    <row r="414">
-      <c r="A414" t="str">
-        <v>group-menu-student-life</v>
-      </c>
-      <c r="B414" t="str">
-        <v>ITEM_HREF</v>
-      </c>
-      <c r="C414" t="str">
-        <v>/orientation-and-wow</v>
-      </c>
-      <c r="D414" t="str">
-        <v>/orientation</v>
-      </c>
-      <c r="E414" t="str">
-        <v>❗ HREF Mismatch</v>
-      </c>
-    </row>
-    <row r="415">
-      <c r="A415" t="str">
-        <v>group-menu-study-abroad</v>
-      </c>
-      <c r="B415" t="str">
-        <v>MENU</v>
-      </c>
-      <c r="C415" t="str">
-        <v>Study Abroad                    [Menu ID: group-menu-study-abroad]</v>
-      </c>
-      <c r="D415" t="str">
-        <v>group-menu-study-abroad                    [Term ID: 1567]</v>
-      </c>
-      <c r="E415" t="str">
-        <v>OK</v>
-      </c>
-    </row>
-    <row r="416">
-      <c r="A416" t="str">
-        <v>group-menu-study-abroad</v>
-      </c>
-      <c r="B416" t="str">
-        <v>ITEM_HREF</v>
-      </c>
-      <c r="C416" t="str">
-        <v>/study_abroad/contact-us</v>
-      </c>
-      <c r="D416" t="str">
-        <v>/study_abroad/contact-study-abroad</v>
-      </c>
-      <c r="E416" t="str">
-        <v>❗ HREF Mismatch</v>
-      </c>
-    </row>
-    <row r="417">
-      <c r="A417" t="str">
-        <v>group-menu-summer-sessions</v>
-      </c>
-      <c r="B417" t="str">
-        <v>MENU</v>
-      </c>
-      <c r="C417" t="str">
-        <v>Summer Sessions                    [Menu ID: group-menu-summer-sessions]</v>
-      </c>
-      <c r="D417" t="str">
-        <v>group-menu-summer-sessions                    [Term ID: 1721]</v>
-      </c>
-      <c r="E417" t="str">
-        <v>OK</v>
-      </c>
-    </row>
-    <row r="418">
-      <c r="A418" t="str">
-        <v>group-menu-suny-geneseo-cheerlea</v>
-      </c>
-      <c r="B418" t="str">
-        <v>MENU</v>
-      </c>
-      <c r="C418" t="str">
-        <v>Geneseo Cheerleading                    [Menu ID: group-menu-suny-geneseo-cheerlea]</v>
-      </c>
-      <c r="D418" t="str">
-        <v/>
-      </c>
-      <c r="E418" t="str">
-        <v>Missing in WP</v>
-      </c>
-    </row>
-    <row r="419">
-      <c r="A419" t="str">
-        <v>group-menu-support-geneseo</v>
-      </c>
-      <c r="B419" t="str">
-        <v>MENU</v>
-      </c>
-      <c r="C419" t="str">
-        <v>Support Geneseo                    [Menu ID: group-menu-support-geneseo]</v>
-      </c>
-      <c r="D419" t="str">
-        <v>group-menu-support-geneseo                    [Term ID: 1542]</v>
-      </c>
-      <c r="E419" t="str">
-        <v>OK</v>
-      </c>
-    </row>
-    <row r="420">
-      <c r="A420" t="str">
-        <v>group-menu-support-geneseo</v>
-      </c>
-      <c r="B420" t="str">
-        <v>CHILD_TITLE</v>
-      </c>
-      <c r="C420" t="str">
-        <v>Milne Library Naming Opportunities</v>
-      </c>
-      <c r="D420" t="str">
-        <v/>
-      </c>
-      <c r="E420" t="str">
-        <v>Missing in WP</v>
-      </c>
-    </row>
-    <row r="421">
-      <c r="A421" t="str">
-        <v>group-menu-support-geneseo</v>
-      </c>
-      <c r="B421" t="str">
-        <v>CHILD_HREF</v>
-      </c>
-      <c r="C421" t="str">
-        <v>/support/milnenaming</v>
-      </c>
-      <c r="D421" t="str">
-        <v/>
-      </c>
-      <c r="E421" t="str">
-        <v>Missing in WP</v>
-      </c>
-    </row>
-    <row r="422">
-      <c r="A422" t="str">
-        <v>group-menu-sustainability</v>
-      </c>
-      <c r="B422" t="str">
-        <v>MENU</v>
-      </c>
-      <c r="C422" t="str">
-        <v>Sustainability                    [Menu ID: group-menu-sustainability]</v>
-      </c>
-      <c r="D422" t="str">
-        <v>group-menu-sustainability                    [Term ID: 1570]</v>
-      </c>
-      <c r="E422" t="str">
-        <v>OK</v>
-      </c>
-    </row>
-    <row r="423">
-      <c r="A423" t="str">
-        <v>group-menu-teaching-and-learning</v>
-      </c>
-      <c r="B423" t="str">
-        <v>MENU</v>
-      </c>
-      <c r="C423" t="str">
-        <v>Teaching and Learning Center                    [Menu ID: group-menu-teaching-and-learning]</v>
-      </c>
-      <c r="D423" t="str">
-        <v>group-menu-teaching-and-learning                    [Term ID: 1633]</v>
-      </c>
-      <c r="E423" t="str">
-        <v>OK</v>
-      </c>
-    </row>
-    <row r="424">
-      <c r="A424" t="str">
-        <v>group-menu-tedx-suny-geneseo</v>
-      </c>
-      <c r="B424" t="str">
-        <v>MENU</v>
-      </c>
-      <c r="C424" t="str">
-        <v>TEDx SUNY Geneseo                    [Menu ID: group-menu-tedx-suny-geneseo]</v>
-      </c>
-      <c r="D424" t="str">
-        <v/>
-      </c>
-      <c r="E424" t="str">
-        <v>Missing in WP</v>
-      </c>
-    </row>
-    <row r="425">
-      <c r="A425" t="str">
-        <v>group-menu-testing-center</v>
-      </c>
-      <c r="B425" t="str">
-        <v>MENU</v>
-      </c>
-      <c r="C425" t="str">
-        <v>Testing Center                    [Menu ID: group-menu-testing-center]</v>
-      </c>
-      <c r="D425" t="str">
-        <v>group-menu-testing-center                    [Term ID: 1668]</v>
-      </c>
-      <c r="E425" t="str">
-        <v>OK</v>
-      </c>
-    </row>
-    <row r="426">
-      <c r="A426" t="str">
-        <v>group-menu-the-l-i-v-e-s-program</v>
-      </c>
-      <c r="B426" t="str">
-        <v>MENU</v>
-      </c>
-      <c r="C426" t="str">
-        <v>The LIVES Program                    [Menu ID: group-menu-the-l-i-v-e-s-program]</v>
-      </c>
-      <c r="D426" t="str">
-        <v>group-menu-the-l-i-v-e-s-program                    [Term ID: 1608]</v>
-      </c>
-      <c r="E426" t="str">
-        <v>OK</v>
-      </c>
-    </row>
-    <row r="427">
-      <c r="A427" t="str">
-        <v>group-menu-the-national-honor-so</v>
-      </c>
-      <c r="B427" t="str">
-        <v>MENU</v>
-      </c>
-      <c r="C427" t="str">
-        <v>The National Honor Society in Psychology                    [Menu ID: group-menu-the-national-honor-so]</v>
-      </c>
-      <c r="D427" t="str">
-        <v>group-menu-the-national-honor-so                    [Term ID: 1599]</v>
-      </c>
-      <c r="E427" t="str">
-        <v>OK</v>
-      </c>
-    </row>
-    <row r="428">
-      <c r="A428" t="str">
-        <v>group-menu-theatre-dance</v>
-      </c>
-      <c r="B428" t="str">
-        <v>MENU</v>
-      </c>
-      <c r="C428" t="str">
-        <v>Theatre &amp; Dance                    [Menu ID: group-menu-theatre-dance]</v>
-      </c>
-      <c r="D428" t="str">
-        <v/>
-      </c>
-      <c r="E428" t="str">
-        <v>Missing in WP</v>
-      </c>
-    </row>
-    <row r="429">
-      <c r="A429" t="str">
-        <v>group-menu-thomas-greenfield</v>
-      </c>
-      <c r="B429" t="str">
-        <v>MENU</v>
-      </c>
-      <c r="C429" t="str">
-        <v>Thomas Greenfield                    [Menu ID: group-menu-thomas-greenfield]</v>
-      </c>
-      <c r="D429" t="str">
-        <v>group-menu-thomas-greenfield                    [Term ID: 1685]</v>
-      </c>
-      <c r="E429" t="str">
-        <v>OK</v>
-      </c>
-    </row>
-    <row r="430">
-      <c r="A430" t="str">
-        <v>group-menu-thomas-greenfield</v>
-      </c>
-      <c r="B430" t="str">
-        <v>ITEM_HREF</v>
-      </c>
-      <c r="C430" t="str">
-        <v>/sites/default/files/sites/tag/Academic%20Resume%20August%202011.doc</v>
-      </c>
-      <c r="D430" t="str">
-        <v>/wp-content/uploads/2025/11/Academic-Resume-August-2011.doc</v>
-      </c>
-      <c r="E430" t="str">
-        <v>❗ HREF Mismatch</v>
-      </c>
-    </row>
-    <row r="431">
-      <c r="A431" t="str">
-        <v>group-menu-thomas-greenfield</v>
-      </c>
-      <c r="B431" t="str">
-        <v>ITEM_TITLE</v>
-      </c>
-      <c r="C431" t="str">
-        <v>Musician's Resume</v>
-      </c>
-      <c r="D431" t="str">
-        <v/>
-      </c>
-      <c r="E431" t="str">
-        <v>Missing in WP</v>
-      </c>
-    </row>
-    <row r="432">
-      <c r="A432" t="str">
-        <v>group-menu-thomas-greenfield</v>
-      </c>
-      <c r="B432" t="str">
-        <v>ITEM_HREF</v>
-      </c>
-      <c r="C432" t="str">
-        <v>/tag/music</v>
-      </c>
-      <c r="D432" t="str">
-        <v/>
-      </c>
-      <c r="E432" t="str">
-        <v>Missing in WP</v>
-      </c>
-    </row>
-    <row r="433">
-      <c r="A433" t="str">
-        <v>group-menu-thomas-greenfield</v>
-      </c>
-      <c r="B433" t="str">
-        <v>ITEM_HREF</v>
-      </c>
-      <c r="C433" t="str">
-        <v>/tag/photos</v>
-      </c>
-      <c r="D433" t="str">
-        <v>/?page_id=43746</v>
-      </c>
-      <c r="E433" t="str">
-        <v>❗ HREF Mismatch</v>
-      </c>
-    </row>
-    <row r="434">
-      <c r="A434" t="str">
-        <v>group-menu-thomas-greenfield</v>
-      </c>
-      <c r="B434" t="str">
-        <v>ITEM_HREF</v>
-      </c>
-      <c r="C434" t="str">
-        <v>/tag/oxford</v>
-      </c>
-      <c r="D434" t="str">
-        <v>/?page_id=43748</v>
-      </c>
-      <c r="E434" t="str">
-        <v>❗ HREF Mismatch</v>
-      </c>
-    </row>
-    <row r="435">
-      <c r="A435" t="str">
-        <v>group-menu-thomas-greenfield</v>
-      </c>
-      <c r="B435" t="str">
-        <v>ITEM_HREF</v>
-      </c>
-      <c r="C435" t="str">
-        <v>/tag/humanities-athens-2011</v>
-      </c>
-      <c r="D435" t="str">
-        <v>/?page_id=43750</v>
-      </c>
-      <c r="E435" t="str">
-        <v>❗ HREF Mismatch</v>
-      </c>
-    </row>
-    <row r="436">
-      <c r="A436" t="str">
-        <v>group-menu-thomas-greenfield</v>
-      </c>
-      <c r="B436" t="str">
-        <v>ITEM_HREF</v>
-      </c>
-      <c r="C436" t="str">
-        <v>/tag/ireland</v>
-      </c>
-      <c r="D436" t="str">
-        <v>/?page_id=43745</v>
-      </c>
-      <c r="E436" t="str">
-        <v>❗ HREF Mismatch</v>
-      </c>
-    </row>
-    <row r="437">
-      <c r="A437" t="str">
-        <v>group-menu-thomas-greenfield</v>
-      </c>
-      <c r="B437" t="str">
-        <v>ITEM_HREF</v>
-      </c>
-      <c r="C437" t="str">
-        <v>http://writingguide.geneseo.edu</v>
-      </c>
-      <c r="D437" t="str">
-        <v/>
-      </c>
-      <c r="E437" t="str">
-        <v>❗ HREF Mismatch</v>
-      </c>
-    </row>
-    <row r="438">
-      <c r="A438" t="str">
-        <v>group-menu-thomas-greenfield</v>
-      </c>
-      <c r="B438" t="str">
-        <v>ITEM_HREF</v>
-      </c>
-      <c r="C438" t="str">
-        <v>http://library.geneseo.edu</v>
-      </c>
-      <c r="D438" t="str">
-        <v/>
-      </c>
-      <c r="E438" t="str">
-        <v>❗ HREF Mismatch</v>
-      </c>
-    </row>
-    <row r="439">
-      <c r="A439" t="str">
-        <v>group-menu-thomas-greenfield</v>
-      </c>
-      <c r="B439" t="str">
-        <v>ITEM_HREF</v>
-      </c>
-      <c r="C439" t="str">
-        <v>https://bulletin.geneseo.edu</v>
-      </c>
-      <c r="D439" t="str">
-        <v/>
-      </c>
-      <c r="E439" t="str">
-        <v>❗ HREF Mismatch</v>
-      </c>
-    </row>
-    <row r="440">
-      <c r="A440" t="str">
-        <v>group-menu-thomas-greenfield</v>
-      </c>
-      <c r="B440" t="str">
-        <v>ITEM_HREF</v>
-      </c>
-      <c r="C440" t="str">
-        <v>http://www.mla.org</v>
-      </c>
-      <c r="D440" t="str">
-        <v/>
-      </c>
-      <c r="E440" t="str">
-        <v>❗ HREF Mismatch</v>
-      </c>
-    </row>
-    <row r="441">
-      <c r="A441" t="str">
-        <v>group-menu-thomas-greenfield</v>
-      </c>
-      <c r="B441" t="str">
-        <v>ITEM_HREF</v>
-      </c>
-      <c r="C441" t="str">
-        <v>http://proxy.geneseo.edu:2055/search</v>
-      </c>
-      <c r="D441" t="str">
-        <v>/search</v>
-      </c>
-      <c r="E441" t="str">
-        <v>❗ HREF Mismatch</v>
-      </c>
-    </row>
-    <row r="442">
-      <c r="A442" t="str">
-        <v>group-menu-title-ix</v>
-      </c>
-      <c r="B442" t="str">
-        <v>MENU</v>
-      </c>
-      <c r="C442" t="str">
-        <v>Title IX &amp; Equity Compliance                    [Menu ID: group-menu-title-ix]</v>
-      </c>
-      <c r="D442" t="str">
-        <v>group-menu-title-ix                    [Term ID: 1603]</v>
-      </c>
-      <c r="E442" t="str">
-        <v>OK</v>
-      </c>
-    </row>
-    <row r="443">
-      <c r="A443" t="str">
-        <v>group-menu-title-ix</v>
-      </c>
-      <c r="B443" t="str">
-        <v>ITEM_HREF</v>
-      </c>
-      <c r="C443" t="str">
-        <v>https://cm.maxient.com/reportingform.php?SUNYGeneseo=&amp;layout_id=2</v>
-      </c>
-      <c r="D443" t="str">
-        <v>https://cm.maxient.com/reportingform.php?SUNYGeneseo&amp;layout_id=2#</v>
-      </c>
-      <c r="E443" t="str">
-        <v>❗ HREF Mismatch</v>
-      </c>
-    </row>
-    <row r="444">
-      <c r="A444" t="str">
-        <v>group-menu-title-ix</v>
-      </c>
-      <c r="B444" t="str">
-        <v>ITEM_TITLE</v>
-      </c>
-      <c r="C444" t="str">
-        <v>SUNY Geneseo Sexual Violence Response Policy</v>
-      </c>
-      <c r="D444" t="str">
-        <v/>
-      </c>
-      <c r="E444" t="str">
-        <v>Missing in WP</v>
-      </c>
-    </row>
-    <row r="445">
-      <c r="A445" t="str">
-        <v>group-menu-title-ix</v>
-      </c>
-      <c r="B445" t="str">
-        <v>ITEM_HREF</v>
-      </c>
-      <c r="C445" t="str">
-        <v>/titleix/sexual-violence-response-policy</v>
-      </c>
-      <c r="D445" t="str">
-        <v/>
-      </c>
-      <c r="E445" t="str">
-        <v>Missing in WP</v>
-      </c>
-    </row>
-    <row r="446">
-      <c r="A446" t="str">
-        <v>group-menu-travel</v>
-      </c>
-      <c r="B446" t="str">
-        <v>MENU</v>
-      </c>
-      <c r="C446" t="str">
-        <v>Travel                    [Menu ID: group-menu-travel]</v>
-      </c>
-      <c r="D446" t="str">
-        <v/>
-      </c>
-      <c r="E446" t="str">
-        <v>Missing in WP</v>
-      </c>
-    </row>
-    <row r="447">
-      <c r="A447" t="str">
-        <v>group-menu-tri-beta</v>
-      </c>
-      <c r="B447" t="str">
-        <v>MENU</v>
-      </c>
-      <c r="C447" t="str">
-        <v>Tri-Beta                    [Menu ID: group-menu-tri-beta]</v>
-      </c>
-      <c r="D447" t="str">
-        <v>group-menu-tri-beta                    [Term ID: 1625]</v>
-      </c>
-      <c r="E447" t="str">
-        <v>OK</v>
-      </c>
-    </row>
-    <row r="448">
-      <c r="A448" t="str">
-        <v>group-menu-undergraduate-alumni-</v>
-      </c>
-      <c r="B448" t="str">
-        <v>MENU</v>
-      </c>
-      <c r="C448" t="str">
-        <v>Undergraduate Alumni Association                    [Menu ID: group-menu-undergraduate-alumni-]</v>
-      </c>
-      <c r="D448" t="str">
-        <v>group-menu-undergraduate-alumni-                    [Term ID: 1637]</v>
-      </c>
-      <c r="E448" t="str">
-        <v>OK</v>
-      </c>
-    </row>
-    <row r="449">
-      <c r="A449" t="str">
-        <v>group-menu-undergraduate-alumni-</v>
-      </c>
-      <c r="B449" t="str">
-        <v>ITEM_HREF</v>
-      </c>
-      <c r="C449" t="str">
-        <v>/uaa/e-yearbook-photo-submission-links</v>
-      </c>
-      <c r="D449" t="str">
-        <v>/uaa/e-yearbook</v>
-      </c>
-      <c r="E449" t="str">
-        <v>❗ HREF Mismatch</v>
-      </c>
-    </row>
-    <row r="450">
-      <c r="A450" t="str">
-        <v>group-menu-undergraduate-researc</v>
-      </c>
-      <c r="B450" t="str">
-        <v>MENU</v>
-      </c>
-      <c r="C450" t="str">
-        <v>Undergraduate Research                    [Menu ID: group-menu-undergraduate-researc]</v>
-      </c>
-      <c r="D450" t="str">
-        <v>group-menu-undergraduate-researc                    [Term ID: 1559]</v>
-      </c>
-      <c r="E450" t="str">
-        <v>OK</v>
-      </c>
-    </row>
-    <row r="451">
-      <c r="A451" t="str">
-        <v>group-menu-undergraduate-researc</v>
-      </c>
-      <c r="B451" t="str">
-        <v>ITEM_HREF</v>
-      </c>
-      <c r="C451" t="str">
-        <v>http://www.cur.org</v>
-      </c>
-      <c r="D451" t="str">
-        <v/>
-      </c>
-      <c r="E451" t="str">
-        <v>❗ HREF Mismatch</v>
-      </c>
-    </row>
-    <row r="452">
-      <c r="A452" t="str">
-        <v>group-menu-ventureworks</v>
-      </c>
-      <c r="B452" t="str">
-        <v>MENU</v>
-      </c>
-      <c r="C452" t="str">
-        <v>VentureWorks                    [Menu ID: group-menu-ventureworks]</v>
-      </c>
-      <c r="D452" t="str">
-        <v>group-menu-ventureworks                    [Term ID: 1540]</v>
-      </c>
-      <c r="E452" t="str">
-        <v>OK</v>
-      </c>
-    </row>
-    <row r="453">
-      <c r="A453" t="str">
-        <v>group-menu-veterans</v>
-      </c>
-      <c r="B453" t="str">
-        <v>MENU</v>
-      </c>
-      <c r="C453" t="str">
-        <v>Veterans                    [Menu ID: group-menu-veterans]</v>
-      </c>
-      <c r="D453" t="str">
-        <v>group-menu-veterans                    [Term ID: 1616]</v>
-      </c>
-      <c r="E453" t="str">
-        <v>OK</v>
-      </c>
-    </row>
-    <row r="454">
-      <c r="A454" t="str">
-        <v>group-menu-volunteer-center</v>
-      </c>
-      <c r="B454" t="str">
-        <v>MENU</v>
-      </c>
-      <c r="C454" t="str">
-        <v>Student Volunteerism and Community Engagement                     [Menu ID: group-menu-volunteer-center]</v>
-      </c>
-      <c r="D454" t="str">
-        <v>group-menu-volunteer-center                    [Term ID: 1592]</v>
-      </c>
-      <c r="E454" t="str">
-        <v>OK</v>
-      </c>
-    </row>
-    <row r="455">
-      <c r="A455" t="str">
-        <v>group-menu-vote</v>
-      </c>
-      <c r="B455" t="str">
-        <v>MENU</v>
-      </c>
-      <c r="C455" t="str">
-        <v>Vote                    [Menu ID: group-menu-vote]</v>
-      </c>
-      <c r="D455" t="str">
-        <v>group-menu-vote                    [Term ID: 1672]</v>
-      </c>
-      <c r="E455" t="str">
-        <v>OK</v>
-      </c>
-    </row>
-    <row r="456">
-      <c r="A456" t="str">
-        <v>group-menu-vote</v>
-      </c>
-      <c r="B456" t="str">
-        <v>ITEM_HREF</v>
-      </c>
-      <c r="C456" t="str">
-        <v>/NSLVE</v>
-      </c>
-      <c r="D456" t="str">
-        <v>/nslve</v>
-      </c>
-      <c r="E456" t="str">
-        <v>❗ HREF Mismatch</v>
-      </c>
-    </row>
-    <row r="457">
-      <c r="A457" t="str">
-        <v>group-menu-wadsworth-auditorium</v>
-      </c>
-      <c r="B457" t="str">
-        <v>MENU</v>
-      </c>
-      <c r="C457" t="str">
-        <v>Wadsworth Auditorium                    [Menu ID: group-menu-wadsworth-auditorium]</v>
-      </c>
-      <c r="D457" t="str">
-        <v>group-menu-wadsworth-auditorium                    [Term ID: 1651]</v>
-      </c>
-      <c r="E457" t="str">
-        <v>OK</v>
-      </c>
-    </row>
-    <row r="458">
-      <c r="A458" t="str">
-        <v>group-menu-wadsworth-auditorium</v>
-      </c>
-      <c r="B458" t="str">
-        <v>ITEM_HREF</v>
-      </c>
-      <c r="C458" t="str">
-        <v>http://admissions.geneseo.edu/?p=directions</v>
-      </c>
-      <c r="D458" t="str">
-        <v/>
-      </c>
-      <c r="E458" t="str">
-        <v>❗ HREF Mismatch</v>
-      </c>
-    </row>
-    <row r="459">
-      <c r="A459" t="str">
-        <v>group-menu-weeks-of-welcome</v>
-      </c>
-      <c r="B459" t="str">
-        <v>MENU</v>
-      </c>
-      <c r="C459" t="str">
-        <v>New Student Orientation                    [Menu ID: group-menu-weeks-of-welcome]</v>
-      </c>
-      <c r="D459" t="str">
-        <v>group-menu-weeks-of-welcome                    [Term ID: 1605]</v>
-      </c>
-      <c r="E459" t="str">
-        <v>OK</v>
-      </c>
-    </row>
-    <row r="460">
-      <c r="A460" t="str">
-        <v>group-menu-weeks-of-welcome</v>
-      </c>
-      <c r="B460" t="str">
-        <v>ITEM_HREF</v>
-      </c>
-      <c r="C460" t="str">
-        <v>/orientation/new-student-checklist-fall-2022</v>
-      </c>
-      <c r="D460" t="str">
-        <v>/orientation/new-student-checklist</v>
-      </c>
-      <c r="E460" t="str">
-        <v>❗ HREF Mismatch</v>
-      </c>
-    </row>
-    <row r="461">
-      <c r="A461" t="str">
-        <v>group-menu-weeks-of-welcome</v>
-      </c>
-      <c r="B461" t="str">
-        <v>MENU</v>
-      </c>
-      <c r="C461" t="str">
-        <v>Weeks of Welcome                    [Menu ID: group-menu-weeks-of-welcome-0]</v>
-      </c>
-      <c r="D461" t="str">
-        <v>group-menu-weeks-of-welcome                    [Term ID: 1605]</v>
-      </c>
-      <c r="E461" t="str">
-        <v>OK</v>
-      </c>
-    </row>
-    <row r="462">
-      <c r="A462" t="str">
-        <v>group-menu-winter-guard</v>
-      </c>
-      <c r="B462" t="str">
-        <v>MENU</v>
-      </c>
-      <c r="C462" t="str">
-        <v>Winter Guard                    [Menu ID: group-menu-winter-guard]</v>
-      </c>
-      <c r="D462" t="str">
-        <v/>
-      </c>
-      <c r="E462" t="str">
-        <v>Missing in WP</v>
-      </c>
-    </row>
-    <row r="463">
-      <c r="A463" t="str">
-        <v>group-menu-women-s-action-coalit</v>
-      </c>
-      <c r="B463" t="str">
-        <v>MENU</v>
-      </c>
-      <c r="C463" t="str">
-        <v>Women's Action Coalition                    [Menu ID: group-menu-women-s-action-coalit]</v>
-      </c>
-      <c r="D463" t="str">
-        <v/>
-      </c>
-      <c r="E463" t="str">
-        <v>Missing in WP</v>
-      </c>
-    </row>
-    <row r="464">
-      <c r="A464" t="str">
-        <v>group-menu-women-s-ice-hockey</v>
-      </c>
-      <c r="B464" t="str">
-        <v>MENU</v>
-      </c>
-      <c r="C464" t="str">
-        <v>Women's Ice Hockey                    [Menu ID: group-menu-women-s-ice-hockey]</v>
-      </c>
-      <c r="D464" t="str">
-        <v/>
-      </c>
-      <c r="E464" t="str">
-        <v>Missing in WP</v>
-      </c>
-    </row>
-    <row r="465">
-      <c r="A465" t="str">
-        <v>group-menu-women-s-leadership-in</v>
-      </c>
-      <c r="B465" t="str">
-        <v>MENU</v>
-      </c>
-      <c r="C465" t="str">
-        <v>Women's Leadership Institute                    [Menu ID: group-menu-women-s-leadership-in]</v>
-      </c>
-      <c r="D465" t="str">
-        <v>group-menu-women-s-leadership-in                    [Term ID: 1613]</v>
-      </c>
-      <c r="E465" t="str">
-        <v>OK</v>
-      </c>
-    </row>
-    <row r="466">
-      <c r="A466" t="str">
-        <v>group-menu-women-s-leadership-in</v>
-      </c>
-      <c r="B466" t="str">
-        <v>ITEM_HREF</v>
-      </c>
-      <c r="C466" t="str">
-        <v>http://gold.geneseo.edu</v>
-      </c>
-      <c r="D466" t="str">
-        <v/>
-      </c>
-      <c r="E466" t="str">
-        <v>❗ HREF Mismatch</v>
-      </c>
-    </row>
-    <row r="467">
-      <c r="A467" t="str">
-        <v>group-menu-women-s-leadership-in</v>
-      </c>
-      <c r="B467" t="str">
-        <v>ITEM_HREF</v>
-      </c>
-      <c r="C467" t="str">
-        <v>http://geneseo.edu/aop</v>
-      </c>
-      <c r="D467" t="str">
-        <v>/aop</v>
-      </c>
-      <c r="E467" t="str">
-        <v>❗ HREF Mismatch</v>
-      </c>
-    </row>
-    <row r="468">
-      <c r="A468" t="str">
-        <v>group-menu-women-s-rugby</v>
-      </c>
-      <c r="B468" t="str">
-        <v>MENU</v>
-      </c>
-      <c r="C468" t="str">
-        <v>Women's Rugby                    [Menu ID: group-menu-women-s-rugby]</v>
-      </c>
-      <c r="D468" t="str">
-        <v>group-menu-women-s-rugby                    [Term ID: 1624]</v>
-      </c>
-      <c r="E468" t="str">
-        <v>OK</v>
-      </c>
-    </row>
-    <row r="469">
-      <c r="A469" t="str">
-        <v>group-menu-women-s-rugby</v>
-      </c>
-      <c r="B469" t="str">
-        <v>ITEM_HREF</v>
-      </c>
-      <c r="C469" t="str">
-        <v>/womens_rugby/Learning-and-Links</v>
-      </c>
-      <c r="D469" t="str">
-        <v>/womens_rugby/learning-and-links</v>
-      </c>
-      <c r="E469" t="str">
-        <v>❗ HREF Mismatch</v>
-      </c>
-    </row>
-    <row r="470">
-      <c r="A470" t="str">
-        <v>group-menu-women-s-studies</v>
-      </c>
-      <c r="B470" t="str">
-        <v>MENU</v>
-      </c>
-      <c r="C470" t="str">
-        <v>Women and Gender Studies                    [Menu ID: group-menu-women-s-studies]</v>
-      </c>
-      <c r="D470" t="str">
-        <v>group-menu-women-s-studies                    [Term ID: 1582]</v>
-      </c>
-      <c r="E470" t="str">
-        <v>OK</v>
-      </c>
-    </row>
-    <row r="471">
-      <c r="A471" t="str">
-        <v>group-menu-workout-center</v>
-      </c>
-      <c r="B471" t="str">
-        <v>MENU</v>
-      </c>
-      <c r="C471" t="str">
-        <v>Workout Center                    [Menu ID: group-menu-workout-center]</v>
-      </c>
-      <c r="D471" t="str">
-        <v>group-menu-workout-center                    [Term ID: 1652]</v>
-      </c>
-      <c r="E471" t="str">
-        <v>OK</v>
-      </c>
-    </row>
-    <row r="472">
-      <c r="A472" t="str">
-        <v>group-menu-workout-center</v>
-      </c>
-      <c r="B472" t="str">
-        <v>ITEM_HREF</v>
-      </c>
-      <c r="C472" t="str">
-        <v>http://knights.geneseo.edu</v>
-      </c>
-      <c r="D472" t="str">
-        <v/>
-      </c>
-      <c r="E472" t="str">
-        <v>❗ HREF Mismatch</v>
-      </c>
-    </row>
-    <row r="473">
-      <c r="A473" t="str">
-        <v>group-menu-xerox-center</v>
-      </c>
-      <c r="B473" t="str">
-        <v>MENU</v>
-      </c>
-      <c r="C473" t="str">
-        <v>Xerox Center                    [Menu ID: group-menu-xerox-center]</v>
-      </c>
-      <c r="D473" t="str">
-        <v/>
-      </c>
-      <c r="E473" t="str">
-        <v>Missing in WP</v>
-      </c>
-    </row>
-    <row r="474">
-      <c r="A474" t="str">
-        <v>group-menu-yoga-club</v>
-      </c>
-      <c r="B474" t="str">
-        <v>MENU</v>
-      </c>
-      <c r="C474" t="str">
-        <v>Yoga Club                    [Menu ID: group-menu-yoga-club]</v>
-      </c>
-      <c r="D474" t="str">
-        <v>group-menu-yoga-club                    [Term ID: 1636]</v>
-      </c>
-      <c r="E474" t="str">
-        <v>OK</v>
-      </c>
-    </row>
-    <row r="475">
-      <c r="A475" t="str">
-        <v>group-menu-yoga-club</v>
-      </c>
-      <c r="B475" t="str">
-        <v>ITEM_HREF</v>
-      </c>
-      <c r="C475" t="str">
-        <v>/yoga/medicine-wheel</v>
-      </c>
-      <c r="D475" t="str">
-        <v>/entity:node/70357</v>
-      </c>
-      <c r="E475" t="str">
-        <v>❗ HREF Mismatch</v>
-      </c>
-    </row>
-    <row r="476">
-      <c r="A476" t="str">
-        <v>group-menu-yoga-club</v>
-      </c>
-      <c r="B476" t="str">
-        <v>ITEM_HREF</v>
-      </c>
-      <c r="C476" t="str">
-        <v>/yoga/parables-and-teachings</v>
-      </c>
-      <c r="D476" t="str">
-        <v>/entity:node/70358</v>
-      </c>
-      <c r="E476" t="str">
-        <v>❗ HREF Mismatch</v>
-      </c>
-    </row>
-    <row r="477">
-      <c r="A477" t="str">
-        <v>human-cognition-and-memory-lab</v>
-      </c>
-      <c r="B477" t="str">
-        <v>MENU</v>
-      </c>
-      <c r="C477" t="str">
-        <v>Human Cognition and Memory Lab                    [Menu ID: human-cognition-and-memory-lab]</v>
-      </c>
-      <c r="D477" t="str">
-        <v/>
-      </c>
-      <c r="E477" t="str">
-        <v>Missing in WP</v>
-      </c>
-    </row>
-    <row r="478">
-      <c r="A478" t="str">
-        <v>human-development</v>
-      </c>
-      <c r="B478" t="str">
-        <v>MENU</v>
-      </c>
-      <c r="C478" t="str">
-        <v>Human Development                    [Menu ID: human-development]</v>
-      </c>
-      <c r="D478" t="str">
-        <v/>
-      </c>
-      <c r="E478" t="str">
-        <v>Missing in WP</v>
-      </c>
-    </row>
-    <row r="479">
-      <c r="A479" t="str">
-        <v>human-development-minor</v>
-      </c>
-      <c r="B479" t="str">
-        <v>MENU</v>
-      </c>
-      <c r="C479" t="str">
-        <v>Human Development                    [Menu ID: human-development-minor]</v>
-      </c>
-      <c r="D479" t="str">
-        <v>human-development-minor                    [Term ID: 1740]</v>
-      </c>
-      <c r="E479" t="str">
-        <v>OK</v>
-      </c>
-    </row>
-    <row r="480">
-      <c r="A480" t="str">
-        <v>intersession</v>
-      </c>
-      <c r="B480" t="str">
-        <v>MENU</v>
-      </c>
-      <c r="C480" t="str">
-        <v>Intersession                    [Menu ID: intersession]</v>
-      </c>
-      <c r="D480" t="str">
-        <v/>
-      </c>
-      <c r="E480" t="str">
-        <v>Missing in WP</v>
-      </c>
-    </row>
-    <row r="481">
-      <c r="A481" t="str">
-        <v>join-us</v>
-      </c>
-      <c r="B481" t="str">
-        <v>MENU</v>
-      </c>
-      <c r="C481" t="str">
-        <v>Join Us                    [Menu ID: join-us]</v>
-      </c>
-      <c r="D481" t="str">
-        <v>join-us                    [Term ID: 1736]</v>
-      </c>
-      <c r="E481" t="str">
-        <v>OK</v>
-      </c>
-    </row>
-    <row r="482">
-      <c r="A482" t="str">
-        <v>mcnair</v>
-      </c>
-      <c r="B482" t="str">
-        <v>MENU</v>
-      </c>
-      <c r="C482" t="str">
-        <v>McNair                    [Menu ID: mcnair]</v>
-      </c>
-      <c r="D482" t="str">
-        <v>mcnair                    [Term ID: 1528]</v>
-      </c>
-      <c r="E482" t="str">
-        <v>OK</v>
-      </c>
-    </row>
-    <row r="483">
-      <c r="A483" t="str">
-        <v>mcnair</v>
-      </c>
-      <c r="B483" t="str">
-        <v>CHILD_HREF</v>
-      </c>
-      <c r="C483" t="str">
-        <v>/mcnair/apply/preview/GIRO</v>
-      </c>
-      <c r="D483" t="str">
-        <v>/mcnair/apply/preview/giro</v>
-      </c>
-      <c r="E483" t="str">
-        <v>❗ HREF Mismatch</v>
-      </c>
-    </row>
-    <row r="484">
-      <c r="A484" t="str">
-        <v>mcnair</v>
-      </c>
-      <c r="B484" t="str">
-        <v>CHILD_HREF</v>
-      </c>
-      <c r="C484" t="str">
-        <v>https://docs.google.com/forms/d/1YASQWtSzvAgRJmO6euaZ2URKTJwFqtHbMDdSpCnMgyA/viewform?edit_requested=true</v>
-      </c>
-      <c r="D484" t="str">
-        <v/>
-      </c>
-      <c r="E484" t="str">
-        <v>❗ HREF Mismatch</v>
-      </c>
-    </row>
-    <row r="485">
-      <c r="A485" t="str">
-        <v>mcnair</v>
-      </c>
-      <c r="B485" t="str">
-        <v>CHILD_HREF</v>
-      </c>
-      <c r="C485" t="str">
-        <v>https://docs.google.com/forms/d/e/1FAIpQLSdaXPOoJAlLSvQkGaaoqEO16gu5qh62Nb8Sc0RMonhdzv-99Q/viewform</v>
-      </c>
-      <c r="D485" t="str">
-        <v/>
-      </c>
-      <c r="E485" t="str">
-        <v>❗ HREF Mismatch</v>
-      </c>
-    </row>
-    <row r="486">
-      <c r="A486" t="str">
-        <v>meet-the-global-cluster-profiles</v>
-      </c>
-      <c r="B486" t="str">
-        <v>MENU</v>
-      </c>
-      <c r="C486" t="str">
-        <v>Meet the Global Cluster: Profiles of faculty                    [Menu ID: meet-the-global-cluster-profiles]</v>
-      </c>
-      <c r="D486" t="str">
-        <v/>
-      </c>
-      <c r="E486" t="str">
-        <v>Missing in WP</v>
-      </c>
-    </row>
-    <row r="487">
-      <c r="A487" t="str">
-        <v>middle-states-self-study</v>
-      </c>
-      <c r="B487" t="str">
-        <v>MENU</v>
-      </c>
-      <c r="C487" t="str">
-        <v>Middle States Self-Study                    [Menu ID: middle-states-self-study]</v>
-      </c>
-      <c r="D487" t="str">
-        <v/>
-      </c>
-      <c r="E487" t="str">
-        <v>Missing in WP</v>
-      </c>
-    </row>
-    <row r="488">
-      <c r="A488" t="str">
-        <v>muons-over-letchworth</v>
-      </c>
-      <c r="B488" t="str">
-        <v>MENU</v>
-      </c>
-      <c r="C488" t="str">
-        <v>Muons Over Letchworth                    [Menu ID: muons-over-letchworth]</v>
-      </c>
-      <c r="D488" t="str">
-        <v>muons-over-letchworth                    [Term ID: 1746]</v>
-      </c>
-      <c r="E488" t="str">
-        <v>OK</v>
-      </c>
-    </row>
-    <row r="489">
-      <c r="A489" t="str">
-        <v>newman</v>
-      </c>
-      <c r="B489" t="str">
-        <v>MENU</v>
-      </c>
-      <c r="C489" t="str">
-        <v>Newman                    [Menu ID: newman]</v>
-      </c>
-      <c r="D489" t="str">
-        <v>newman                    [Term ID: 1738]</v>
-      </c>
-      <c r="E489" t="str">
-        <v>OK</v>
-      </c>
-    </row>
-    <row r="490">
-      <c r="A490" t="str">
-        <v>newman-catholic-campus-mini</v>
-      </c>
-      <c r="B490" t="str">
-        <v>MENU</v>
-      </c>
-      <c r="C490" t="str">
-        <v>Newman Catholic Campus Ministry                    [Menu ID: newman-catholic-campus-mini]</v>
-      </c>
-      <c r="D490" t="str">
-        <v>newman-catholic-campus-mini                    [Term ID: 1634]</v>
-      </c>
-      <c r="E490" t="str">
-        <v>OK</v>
-      </c>
-    </row>
-    <row r="491">
-      <c r="A491" t="str">
-        <v>newman-catholic-campus-mini</v>
-      </c>
-      <c r="B491" t="str">
-        <v>ITEM_HREF</v>
-      </c>
-      <c r="C491" t="str">
-        <v>/newman</v>
-      </c>
-      <c r="D491" t="str">
-        <v>/entity:node/73348</v>
-      </c>
-      <c r="E491" t="str">
-        <v>❗ HREF Mismatch</v>
-      </c>
-    </row>
-    <row r="492">
-      <c r="A492" t="str">
-        <v>office-of-accessibility</v>
-      </c>
-      <c r="B492" t="str">
-        <v>MENU</v>
-      </c>
-      <c r="C492" t="str">
-        <v>Office of Accessibility                    [Menu ID: office-of-accessibility]</v>
-      </c>
-      <c r="D492" t="str">
-        <v>office-of-accessibility                    [Term ID: 1575]</v>
-      </c>
-      <c r="E492" t="str">
-        <v>OK</v>
-      </c>
-    </row>
-    <row r="493">
-      <c r="A493" t="str">
-        <v>office-of-accessibility</v>
-      </c>
-      <c r="B493" t="str">
-        <v>ITEM_HREF</v>
-      </c>
-      <c r="C493" t="str">
-        <v>/accessibility-office/student-resources</v>
-      </c>
-      <c r="D493" t="str">
-        <v>/accessibility-office/accessibility-resources-students</v>
-      </c>
-      <c r="E493" t="str">
-        <v>❗ HREF Mismatch</v>
-      </c>
-    </row>
-    <row r="494">
-      <c r="A494" t="str">
-        <v>office-of-accessibility</v>
-      </c>
-      <c r="B494" t="str">
-        <v>ITEM_HREF</v>
-      </c>
-      <c r="C494" t="str">
-        <v>/accessibility-office/faculty-resources</v>
-      </c>
-      <c r="D494" t="str">
-        <v>/accessibility-office/accessibility-resources-faculty</v>
-      </c>
-      <c r="E494" t="str">
-        <v>❗ HREF Mismatch</v>
-      </c>
-    </row>
-    <row r="495">
-      <c r="A495" t="str">
-        <v>office-of-disability</v>
-      </c>
-      <c r="B495" t="str">
-        <v>MENU</v>
-      </c>
-      <c r="C495" t="str">
-        <v>Disability Services                    [Menu ID: office-of-disability]</v>
-      </c>
-      <c r="D495" t="str">
-        <v/>
-      </c>
-      <c r="E495" t="str">
-        <v>Missing in WP</v>
-      </c>
-    </row>
-    <row r="496">
-      <c r="A496" t="str">
-        <v>office-of-disability-servic</v>
-      </c>
-      <c r="B496" t="str">
-        <v>MENU</v>
-      </c>
-      <c r="C496" t="str">
-        <v>Disability Services                    [Menu ID: office-of-disability-servic]</v>
-      </c>
-      <c r="D496" t="str">
-        <v/>
-      </c>
-      <c r="E496" t="str">
-        <v>Missing in WP</v>
-      </c>
-    </row>
-    <row r="497">
-      <c r="A497" t="str">
-        <v>policy</v>
-      </c>
-      <c r="B497" t="str">
-        <v>MENU</v>
-      </c>
-      <c r="C497" t="str">
-        <v>Policy                    [Menu ID: policy]</v>
-      </c>
-      <c r="D497" t="str">
-        <v>policy                    [Term ID: 1745]</v>
-      </c>
-      <c r="E497" t="str">
-        <v>OK</v>
-      </c>
-    </row>
-    <row r="498">
-      <c r="A498" t="str">
-        <v>pride-alliance</v>
-      </c>
-      <c r="B498" t="str">
-        <v>MENU</v>
-      </c>
-      <c r="C498" t="str">
-        <v>Pride Alliance                    [Menu ID: pride-alliance]</v>
-      </c>
-      <c r="D498" t="str">
-        <v>pride-alliance                    [Term ID: 1739]</v>
-      </c>
-      <c r="E498" t="str">
-        <v>OK</v>
-      </c>
-    </row>
-    <row r="499">
-      <c r="A499" t="str">
-        <v>quick-links</v>
-      </c>
-      <c r="B499" t="str">
-        <v>MENU</v>
-      </c>
-      <c r="C499" t="str">
-        <v>Quick Links                    [Menu ID: quick-links]</v>
-      </c>
-      <c r="D499" t="str">
-        <v>quick-links                    [Term ID: 1737]</v>
-      </c>
-      <c r="E499" t="str">
-        <v>OK</v>
-      </c>
-    </row>
-    <row r="500">
-      <c r="A500" t="str">
-        <v>rave</v>
-      </c>
-      <c r="B500" t="str">
-        <v>MENU</v>
-      </c>
-      <c r="C500" t="str">
-        <v>RAVE                    [Menu ID: rave]</v>
-      </c>
-      <c r="D500" t="str">
-        <v/>
-      </c>
-      <c r="E500" t="str">
-        <v>Missing in WP</v>
-      </c>
-    </row>
-    <row r="501">
-      <c r="A501" t="str">
-        <v>rlk</v>
-      </c>
-      <c r="B501" t="str">
-        <v>MENU</v>
-      </c>
-      <c r="C501" t="str">
-        <v>Royal Lady Knights                    [Menu ID: rlk]</v>
-      </c>
-      <c r="D501" t="str">
-        <v/>
-      </c>
-      <c r="E501" t="str">
-        <v>Missing in WP</v>
-      </c>
-    </row>
-    <row r="502">
-      <c r="A502" t="str">
-        <v>safezone</v>
-      </c>
-      <c r="B502" t="str">
-        <v>MENU</v>
-      </c>
-      <c r="C502" t="str">
-        <v>Safe Zone                    [Menu ID: safezone]</v>
-      </c>
-      <c r="D502" t="str">
-        <v>safezone                    [Term ID: 1632]</v>
-      </c>
-      <c r="E502" t="str">
-        <v>OK</v>
-      </c>
-    </row>
-    <row r="503">
-      <c r="A503" t="str">
-        <v>safezone</v>
-      </c>
-      <c r="B503" t="str">
-        <v>ITEM_HREF</v>
-      </c>
-      <c r="C503" t="str">
-        <v>/safezone/open-training-sessions</v>
-      </c>
-      <c r="D503" t="str">
-        <v>/safezone/safe-zone-open-training-sessions-and-request-training</v>
-      </c>
-      <c r="E503" t="str">
-        <v>❗ HREF Mismatch</v>
-      </c>
-    </row>
-    <row r="504">
-      <c r="A504" t="str">
-        <v>safezone</v>
-      </c>
-      <c r="B504" t="str">
-        <v>ITEM_HREF</v>
-      </c>
-      <c r="C504" t="str">
-        <v>/safezone/safe-zone-time</v>
-      </c>
-      <c r="D504" t="str">
-        <v>/safezone/history-safe-zone-suny-geneseo</v>
-      </c>
-      <c r="E504" t="str">
-        <v>❗ HREF Mismatch</v>
-      </c>
-    </row>
-    <row r="505">
-      <c r="A505" t="str">
-        <v>salvador-tarun-jr-</v>
-      </c>
-      <c r="B505" t="str">
-        <v>MENU</v>
-      </c>
-      <c r="C505" t="str">
-        <v>Salvador Tarun Jr.                    [Menu ID: salvador-tarun-jr-]</v>
-      </c>
-      <c r="D505" t="str">
-        <v/>
-      </c>
-      <c r="E505" t="str">
-        <v>Missing in WP</v>
-      </c>
-    </row>
-    <row r="506">
-      <c r="A506" t="str">
-        <v>secondary</v>
-      </c>
-      <c r="B506" t="str">
-        <v>MENU</v>
-      </c>
-      <c r="C506" t="str">
-        <v>Secondary Navigation                    [Menu ID: secondary]</v>
-      </c>
-      <c r="D506" t="str">
-        <v>secondary                    [Term ID: 1610]</v>
-      </c>
-      <c r="E506" t="str">
-        <v>OK</v>
-      </c>
-    </row>
-    <row r="507">
-      <c r="A507" t="str">
-        <v>south-village-counseling</v>
-      </c>
-      <c r="B507" t="str">
-        <v>MENU</v>
-      </c>
-      <c r="C507" t="str">
-        <v>Mind-Body Home                    [Menu ID: south-village-counseling]</v>
-      </c>
-      <c r="D507" t="str">
-        <v>south-village-counseling                    [Term ID: 1743]</v>
-      </c>
-      <c r="E507" t="str">
-        <v>OK</v>
-      </c>
-    </row>
-    <row r="508">
-      <c r="A508" t="str">
-        <v>student-athlete-resource-ce</v>
-      </c>
-      <c r="B508" t="str">
-        <v>MENU</v>
-      </c>
-      <c r="C508" t="str">
-        <v>Student Athlete Resource Center                    [Menu ID: student-athlete-resource-ce]</v>
-      </c>
-      <c r="D508" t="str">
-        <v>student-athlete-resource-ce                    [Term ID: 1758]</v>
-      </c>
-      <c r="E508" t="str">
-        <v>OK</v>
-      </c>
-    </row>
-    <row r="509">
-      <c r="A509" t="str">
-        <v>student-athlete-resource-ce</v>
-      </c>
-      <c r="B509" t="str">
-        <v>ITEM_HREF</v>
-      </c>
-      <c r="C509" t="str">
-        <v>/SAMs</v>
-      </c>
-      <c r="D509" t="str">
-        <v>/sams</v>
-      </c>
-      <c r="E509" t="str">
-        <v>❗ HREF Mismatch</v>
-      </c>
-    </row>
-    <row r="510">
-      <c r="A510" t="str">
-        <v>student-coalition-for-mirga</v>
-      </c>
-      <c r="B510" t="str">
-        <v>MENU</v>
-      </c>
-      <c r="C510" t="str">
-        <v>Student Coalition for Mirgant Workers                    [Menu ID: student-coalition-for-mirga]</v>
-      </c>
-      <c r="D510" t="str">
-        <v/>
-      </c>
-      <c r="E510" t="str">
-        <v>Missing in WP</v>
-      </c>
-    </row>
-    <row r="511">
-      <c r="A511" t="str">
-        <v>voices-for-planned-parentho</v>
-      </c>
-      <c r="B511" t="str">
-        <v>MENU</v>
-      </c>
-      <c r="C511" t="str">
-        <v>Voices for Planned Parenthood                    [Menu ID: voices-for-planned-parentho]</v>
-      </c>
-      <c r="D511" t="str">
-        <v/>
-      </c>
-      <c r="E511" t="str">
-        <v>Missing in WP</v>
-      </c>
-    </row>
-    <row r="512">
-      <c r="A512" t="str">
-        <v>web-accessibility</v>
-      </c>
-      <c r="B512" t="str">
-        <v>MENU</v>
-      </c>
-      <c r="C512" t="str">
-        <v>Web Accessibility                    [Menu ID: web-accessibility]</v>
-      </c>
-      <c r="D512" t="str">
-        <v>web-accessibility                    [Term ID: 1748]</v>
-      </c>
-      <c r="E512" t="str">
-        <v>OK</v>
-      </c>
-    </row>
-    <row r="513">
-      <c r="A513" t="str">
-        <v>wgsu</v>
-      </c>
-      <c r="B513" t="str">
-        <v>MENU</v>
-      </c>
-      <c r="C513" t="str">
-        <v>WGSU-FM                    [Menu ID: wgsu]</v>
-      </c>
-      <c r="D513" t="str">
-        <v>wgsu                    [Term ID: 1585]</v>
-      </c>
-      <c r="E513" t="str">
-        <v>OK</v>
-      </c>
-    </row>
-    <row r="514">
-      <c r="A514" t="str">
-        <v>who-are-we-</v>
-      </c>
-      <c r="B514" t="str">
-        <v>MENU</v>
-      </c>
-      <c r="C514" t="str">
-        <v>Who Are We?                    [Menu ID: who-are-we-]</v>
-      </c>
-      <c r="D514" t="str">
-        <v/>
-      </c>
-      <c r="E514" t="str">
         <v>Missing in WP</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:E514"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:E359"/>
   </ignoredErrors>
 </worksheet>
 </file>